--- a/competitor_campaigns_template.xlsx
+++ b/competitor_campaigns_template.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Dashboard" sheetId="1" r:id="R168a2df8c4a547f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STC Bank" sheetId="2" r:id="Raea0d815ed284158"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="barq" sheetId="3" r:id="R3956992296624e20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobily Pay" sheetId="4" r:id="Ra364fe89271e48fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tiqmo" sheetId="5" r:id="R90f32dfcfbf845c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="urpay" sheetId="6" r:id="R535a0cb840fa43d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="alinma pay" sheetId="7" r:id="R1396fb174f6d462a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Guide" sheetId="8" r:id="R6a9044efb54e437c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Dashboard" sheetId="1" r:id="R8bfa44e4a7c742be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STC Bank" sheetId="2" r:id="R2e06e46aab874d7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="barq" sheetId="3" r:id="Ra56fd28c908b435e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobily Pay" sheetId="4" r:id="R94fc1ecd33504839"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tiqmo" sheetId="5" r:id="Rc405098af46c4d0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="urpay" sheetId="6" r:id="R78cbdb297ae84077"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="alinma pay" sheetId="7" r:id="Rf9268759951b465c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Guide" sheetId="8" r:id="Rb7478ae8afe54542"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,562 +17,430 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t xml:space="preserve">Competitor Campaigns – Remittance-Focused Management Reference</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">STC Bank | barq | Mobily Pay | tiqmo | urpay | alinma pay</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Status Calculated As Of</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Merchant partner discounts are retained as a Merchant Offers Portfolio for reference, but are excluded from all Campaign KPIs and campaign-mix analysis.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Current Campaigns</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Remittance Campaigns</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Merchant Offers (Reference)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Expiring Campaigns ≤30d</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Expired Campaigns</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Competitor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Active &gt;30d</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">End Date Not Stated</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Expiring ≤7d</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Expiring 8–30d</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Expired</x:t>
+    <x:t xml:space="preserve">STC Bank – Verified Campaign Inventory</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Blue rows = Remittance priority | Gold rows = Merchant reference only | Published Social Platforms uses direct specific post links only</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Record ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Campaign Category</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Campaign Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Summary</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Published Date</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Start Date</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">End Date</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Days Remaining</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Current Status</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Operation Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Mechanic / Offer</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Eligibility / Product</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Primary Official Source URL</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Official Campaign Page URL</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Instagram Post URL</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">X Post URL</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Facebook Post URL</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">TikTok Post URL</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Terms / Timing Note</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Card</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">0% International Transaction Fees and Free Cash Withdrawals</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">0% fees on eligible international POS transactions and free withdrawals from international ATMs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">International POS purchases and international ATM withdrawals</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">0% international transaction fees and free international ATM withdrawals</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">STC Bank Visa Classic, Platinum, and Signature debit cards; credit cards excluded</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/international-purchases-with-0-fees</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://www.instagram.com/reel/DbJS1RtM2Ed/</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://x.com/stcbank_ksa/status/2080356315206176795</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://www.facebook.com/share/v/18sMRBBuse/</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://www.tiktok.com/@stcbank_ksa/video/7657549142540979477?is_from_webapp=1&amp;sender_device=pc&amp;web_id=7646835061455799828</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">International Spending Travel Voucher Campaign</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The ten highest international spenders each week receive an Almatar travel voucher.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">International POS and e-commerce purchases</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">100 travel vouchers worth SAR 10,000 each for weekly top spenders</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://www.instagram.com/reel/DbJTohBs04q/</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://x.com/stcbank_ksa/status/2071588243682832478</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://www.facebook.com/share/v/1BoJpH5Xnd/</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Visa Card Rewards: iPhone 17 Pro and Apple Watch</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Monthly iPhone rewards for top spenders and weekly Apple Watch rewards for qualifying purchases.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Domestic and international POS and e-commerce purchases</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">12 iPhone 17 Pro devices and 144 Apple Watches</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/visa_cards_rewards</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">STC Bank Credit Card Launch</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Credit cards promoted with flexible cashback of up to 10% on selected categories and 1% on other purchases.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Credit-card purchases</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Flexible category cashback of up to 10%</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">STC Bank credit-card customers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://www.instagram.com/reel/DWots29j8fx/?hl=en</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://x.com/stcbank_ksa/status/2071639841348124772</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://www.facebook.com/share/v/1CqU3VtD85/</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Campaign end date is not stated in the official post. Social verification: Direct official launch/benefit posts verified on Instagram, X, and Facebook. The posts explicitly mention the Platinum credit card, first-year fee waiver, 0% international transaction fees, and cashback benefits. No specific direct TikTok post URL was verified.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Merchant</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Almatar: Up to 10% Off</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Discounts on hotel and flight bookings through Almatar.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Flight and hotel bookings</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">10% off hotels with STCB10 and 5% off flights with STCB5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">All STC Bank cards</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/almatar-offer</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Whites: Up to 15% Off</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">15% off online purchases and 10% off in stores.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Beauty and healthcare retail</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">15% online and 10% in stores; minimum spend SAR 200; maximum discount SAR 100</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">STC Bank cards</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/whites-offer</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Huawei Device and Accessory Offers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Special prices and selected gifts on eligible Huawei devices and accessories.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Electronics purchases</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Special prices and gifts on selected devices</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/huawei</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Loca Beauty: 15% Off</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">15% off online purchases using promo code STCB15.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Online beauty purchases</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">15% discount using code STCB15</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">STC Bank Visa Classic, Platinum, and Signature cards</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/loca</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Canton: 15% Off</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">15% off eligible online purchases using promo code STCB15.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">E-commerce purchases</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/canton-offer</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dr. Nutrition: Up to 10% Off</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">5% to 10% discounts on selected health and nutrition categories.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Health and nutrition purchases</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">5% to 10% discount using code STCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/boost-your-health</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">GO Sport: 10% Off</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">10% off eligible online purchases using promo code STCB.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sports retail purchases</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">10% discount using code STCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/shop-workout-and-save-with-10-off-on-gosport</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">iHerb: Up to 25% Off</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Visa discounts for new and existing iHerb customers.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Health and wellness e-commerce purchases</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Up to 25% off for new customers and 10% for existing customers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Eligible STC Bank Visa cards</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/iherb-offer</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Abdullah Al Othaim Entertainment</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Bonus credit and discounts across selected family-entertainment destinations.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Family entertainment</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Bonus credit and discounts ranging from 20% to 30%</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/alothaim-entertainment</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Yelo: 10% Off</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">10% off eligible bookings through the Yelo website and app.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Car rental</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">10% discount using code STCB1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">STC Bank mada and credit cards</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/yelo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Engagement</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">STC Bank Championship</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Daily football quiz campaign with prizes for leading participants.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">In-app engagement</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Daily leaderboard and prizes</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">STC Bank app customers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/stcbank-championship</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://www.instagram.com/reel/DZdT9oVs4pw/?hl=en</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://x.com/stcbank_ksa/status/2065159633942274387</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://www.facebook.com/share/v/1EMLYL7XMs/</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://www.tiktok.com/@stcbank_ksa/video/7650240341047725333?is_from_webapp=1&amp;sender_device=pc&amp;web_id=7646835061455799828</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Included as a recent expired campaign for competitive context. Social verification: Direct official posts verified on Instagram, X, and Facebook. Indexed captions/OCR explicitly mention STC Bank Championship, football questions, 50 daily winners, and the tournament period. No specific direct TikTok post URL was verified.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">barq – Verified Campaign Inventory</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">barq Marathon</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Transaction-based points and competition with a large prize pool and winner base.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Card usage and in-app engagement</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Prize pool increased to SAR 500,000 and 20,000 winners</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">barq Visa customers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://www.instagram.com/reel/DYxvJOWiZY5/</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://www.facebook.com/share/p/1BbFALsFYP/</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Campaign end date is not stated in the official post.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Prediction Game</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">In-app match prediction game with a prize pool of up to SAR 500,000.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">In-app sports engagement</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Prediction game with prizes worth up to SAR 500,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">barq app customers</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://www.facebook.com/usebarq/posts/update-your-barq-app-and-join-the-prediction-game-win-your-share-of-prizes-worth/122197690844385166/</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Almatar Travel Offer</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Discounts on international flights and hotels when paying with barq Visa.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Up to 10% off international flights and 25% off hotels</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://www.facebook.com/usebarq/posts/planning-a-trip-%EF%B8%8Fbook-through-almatarapp-with-your-barq-visa-and-get-up-to-10-of/122178668528385166/</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Remittance</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Musaned</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SADAD</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Card</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Engagement</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STC Bank</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">barq</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Mobily Pay</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tiqmo</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">urpay</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">alinma pay</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Verified Current Campaign Count by Category – Merchant Offers Excluded</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Campaign Category</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Market Count</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Other</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Market Total</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Merchant Offers Portfolio – Reference Only (Not Counted as Campaigns)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Total Merchant Offers</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Current / Undated</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Dynamic Management Signals</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Directly Verified Campaign Publications by Social Platform – Merchant Excluded</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Instagram</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">X</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Facebook</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TikTok</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Multi-platform Campaigns</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Reporting Convention and Rationale</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">• Campaign KPIs exclude Merchant records. Individual partner discounts are treated as promotional offers/tactics within a Merchant Offers Portfolio.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">• Do not create one artificial campaign per merchant. If a management roll-up is required, use the program label “Merchant Offers Portfolio” rather than counting each merchant as a campaign.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">• Published Social Platforms and the platform matrix use only direct specific official post URLs. A campaign may count in multiple platform columns when separate official posts were verified.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">• Remittance is the priority target category and is highlighted in blue throughout the workbook.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STC Bank – Verified Campaign Inventory</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Campaign KPIs exclude Merchant records. Merchant offers remain available as a reference portfolio.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Blue rows = Remittance priority | Gold rows = Merchant reference only | Published Social Platforms uses direct specific post links only</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Verified Campaigns</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Record ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Campaign Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Summary</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Published Date</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Start Date</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">End Date</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Days Remaining</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Current Status</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Operation Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Mechanic / Offer</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Eligibility / Product</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Primary Official Source URL</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Official Campaign Page URL</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Instagram Post URL</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">X Post URL</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Facebook Post URL</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TikTok Post URL</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Terms / Timing Note</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Last Reviewed</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Published Social Platforms</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">0% International Transaction Fees and Free Cash Withdrawals</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">0% fees on eligible international POS transactions and free withdrawals from international ATMs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">International POS purchases and international ATM withdrawals</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">0% international transaction fees and free international ATM withdrawals</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STC Bank Visa Classic, Platinum, and Signature debit cards; credit cards excluded</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/international-purchases-with-0-fees</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://www.instagram.com/reel/DbJS1RtM2Ed/</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://x.com/stcbank_ksa/status/2080356315206176795</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://www.facebook.com/share/v/18sMRBBuse/</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://www.tiktok.com/@stcbank_ksa/video/7657549142540979477?is_from_webapp=1&amp;sender_device=pc&amp;web_id=7646835061455799828</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">International Spending Travel Voucher Campaign</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">The ten highest international spenders each week receive an Almatar travel voucher.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">International POS and e-commerce purchases</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">100 travel vouchers worth SAR 10,000 each for weekly top spenders</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://www.instagram.com/reel/DbJTohBs04q/</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://x.com/stcbank_ksa/status/2071588243682832478</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://www.facebook.com/share/v/1BoJpH5Xnd/</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Visa Card Rewards: iPhone 17 Pro and Apple Watch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Monthly iPhone rewards for top spenders and weekly Apple Watch rewards for qualifying purchases.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Domestic and international POS and e-commerce purchases</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">12 iPhone 17 Pro devices and 144 Apple Watches</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/visa_cards_rewards</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STC Bank Credit Card Launch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Credit cards promoted with flexible cashback of up to 10% on selected categories and 1% on other purchases.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Credit-card purchases</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Flexible category cashback of up to 10%</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STC Bank credit-card customers</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://www.instagram.com/reel/DWots29j8fx/?hl=en</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://x.com/stcbank_ksa/status/2071639841348124772</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://www.facebook.com/share/v/1CqU3VtD85/</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Campaign end date is not stated in the official post. Social verification: Direct official launch/benefit posts verified on Instagram, X, and Facebook. The posts explicitly mention the Platinum credit card, first-year fee waiver, 0% international transaction fees, and cashback benefits. No specific direct TikTok post URL was verified.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Merchant</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Almatar: Up to 10% Off</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Discounts on hotel and flight bookings through Almatar.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Flight and hotel bookings</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">10% off hotels with STCB10 and 5% off flights with STCB5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">All STC Bank cards</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/almatar-offer</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Whites: Up to 15% Off</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">15% off online purchases and 10% off in stores.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Beauty and healthcare retail</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">15% online and 10% in stores; minimum spend SAR 200; maximum discount SAR 100</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STC Bank cards</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/whites-offer</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Huawei Device and Accessory Offers</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Special prices and selected gifts on eligible Huawei devices and accessories.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Electronics purchases</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Special prices and gifts on selected devices</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/huawei</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Loca Beauty: 15% Off</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">15% off online purchases using promo code STCB15.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Online beauty purchases</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">15% discount using code STCB15</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STC Bank Visa Classic, Platinum, and Signature cards</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/loca</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Canton: 15% Off</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">15% off eligible online purchases using promo code STCB15.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">E-commerce purchases</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/canton-offer</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Dr. Nutrition: Up to 10% Off</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">5% to 10% discounts on selected health and nutrition categories.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Health and nutrition purchases</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">5% to 10% discount using code STCB</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/boost-your-health</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">GO Sport: 10% Off</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">10% off eligible online purchases using promo code STCB.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sports retail purchases</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">10% discount using code STCB</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/shop-workout-and-save-with-10-off-on-gosport</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">iHerb: Up to 25% Off</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Visa discounts for new and existing iHerb customers.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Health and wellness e-commerce purchases</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Up to 25% off for new customers and 10% for existing customers</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Eligible STC Bank Visa cards</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/iherb-offer</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Abdullah Al Othaim Entertainment</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Bonus credit and discounts across selected family-entertainment destinations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Family entertainment</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Bonus credit and discounts ranging from 20% to 30%</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/alothaim-entertainment</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Yelo: 10% Off</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">10% off eligible bookings through the Yelo website and app.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Car rental</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">10% discount using code STCB1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STC Bank mada and credit cards</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/yelo</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STC Bank Championship</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Daily football quiz campaign with prizes for leading participants.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">In-app engagement</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Daily leaderboard and prizes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STC Bank app customers</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://stcbank.com.sa/en/web/guest/w/stcbank-championship</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://www.instagram.com/reel/DZdT9oVs4pw/?hl=en</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://x.com/stcbank_ksa/status/2065159633942274387</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://www.facebook.com/share/v/1EMLYL7XMs/</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://www.tiktok.com/@stcbank_ksa/video/7650240341047725333?is_from_webapp=1&amp;sender_device=pc&amp;web_id=7646835061455799828</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Included as a recent expired campaign for competitive context. Social verification: Direct official posts verified on Instagram, X, and Facebook. Indexed captions/OCR explicitly mention STC Bank Championship, football questions, 50 daily winners, and the tournament period. No specific direct TikTok post URL was verified.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">barq – Verified Campaign Inventory</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">barq Marathon</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Transaction-based points and competition with a large prize pool and winner base.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Card usage and in-app engagement</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Prize pool increased to SAR 500,000 and 20,000 winners</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">barq Visa customers</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://www.instagram.com/reel/DYxvJOWiZY5/</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://www.facebook.com/share/p/1BbFALsFYP/</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Campaign end date is not stated in the official post.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Prediction Game</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">In-app match prediction game with a prize pool of up to SAR 500,000.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">In-app sports engagement</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Prediction game with prizes worth up to SAR 500,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">barq app customers</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://www.facebook.com/usebarq/posts/update-your-barq-app-and-join-the-prediction-game-win-your-share-of-prizes-worth/122197690844385166/</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Almatar Travel Offer</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Discounts on international flights and hotels when paying with barq Visa.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Up to 10% off international flights and 25% off hotels</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://www.facebook.com/usebarq/posts/planning-a-trip-%EF%B8%8Fbook-through-almatarapp-with-your-barq-visa-and-get-up-to-10-of/122178668528385166/</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Zero-Fee International Transfers</x:t>
@@ -709,6 +577,9 @@
     <x:t xml:space="preserve">https://www.tiktok.com/@mobilypay/video/7666785860884434183?is_from_webapp=1&amp;sender_device=pc&amp;web_id=7646835061455799828</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Other</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">30% Bonus Alfursan Miles</x:t>
   </x:si>
   <x:si>
@@ -737,6 +608,9 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">tiqmo – Verified Campaign Inventory</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SADAD</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">SADAD Daily Cashback</x:t>
@@ -983,6 +857,9 @@
     <x:t xml:space="preserve">Expired on 30 June 2026; retained for recent competitive context.</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Musaned</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Musaned Domestic Worker Salary Travel Ticket Draw</x:t>
   </x:si>
   <x:si>
@@ -1091,9 +968,6 @@
     <x:t xml:space="preserve">Campaign Classification and Reporting Guide</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Merchant offers are maintained as a separate reference portfolio and excluded from Campaign KPIs. Remittance is the priority category and is highlighted in blue.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Record Type</x:t>
   </x:si>
   <x:si>
@@ -1160,21 +1034,6 @@
     <x:t xml:space="preserve">Recommended Merchant-Offer Treatment</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">1. Keep each merchant offer as a separate row for operational reference, expiry monitoring, and source links.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">2. Exclude Merchant rows from campaign totals, campaign mix, campaign expiry KPIs, and campaign platform analysis.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">3. Use “Merchant Offers Portfolio” as the management roll-up label; do not count it as an additional campaign.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">4. Count a merchant activation as a campaign only when it has a coordinated objective, defined audience, dedicated timing, communication plan, and measurable campaign KPI.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">5. This convention avoids inflating campaign volume merely because one competitor has more commercial partners.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Workbook Update Rules</x:t>
   </x:si>
   <x:si>
@@ -1202,9 +1061,6 @@
     <x:t xml:space="preserve">1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Add or edit campaign records inside the relevant competitor table.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Promotion vs. marketing</x:t>
   </x:si>
   <x:si>
@@ -1223,9 +1079,6 @@
     <x:t xml:space="preserve">2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Use Merchant for partner discounts; these remain visible but are excluded from Campaign KPIs.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Campaign definition</x:t>
   </x:si>
   <x:si>
@@ -1244,9 +1097,6 @@
     <x:t xml:space="preserve">3</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Use Remittance for all international-transfer campaigns; the workbook highlights these rows automatically.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Campaign hierarchy</x:t>
   </x:si>
   <x:si>
@@ -1265,43 +1115,26 @@
     <x:t xml:space="preserve">4</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Enter at least one accepted direct official campaign page or specific social post. Primary Official Source URL is formula-generated.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">5</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Leave End Date blank when the official source does not state a complete date.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">6</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Do not overwrite grey formula columns: Record ID, Days Remaining, Current Status, and Primary Official Source URL.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">7</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Dashboard Campaign KPIs, category mix, signals, platform matrix, and charts update automatically.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">8</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Rows with no accepted direct source are highlighted red and excluded.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Published Social Platforms is formula-generated from specific Instagram, X, Facebook, and TikTok post links. Generic profile links are not counted.</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm\ d\,\ yyyy"/>
     <x:numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <x:numFmt numFmtId="200" formatCode="0%"/>
   </x:numFmts>
   <x:fonts count="21">
     <x:font>
@@ -1561,7 +1394,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="128">
+  <x:cellXfs count="130">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -1933,6 +1766,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="20" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -2935,7 +2774,6 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:rPr/>
               <a:t>Current Campaign Mix (Merchant Excluded)</a:t>
             </a:r>
           </a:p>
@@ -2945,7 +2783,6 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -3046,9 +2883,7 @@
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="48672768"/>
         <c:crosses val="autoZero"/>
-        <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="48672768"/>
@@ -3102,7 +2937,6 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:rPr/>
               <a:t>Remittance Campaign Focus</a:t>
             </a:r>
           </a:p>
@@ -3112,7 +2946,6 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -3213,9 +3046,7 @@
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="48672768"/>
         <c:crosses val="autoZero"/>
-        <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="48672768"/>
@@ -3270,7 +3101,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:plotArea>
-      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -3419,9 +3249,7 @@
         </c:txPr>
         <c:crossAx val="48672768"/>
         <c:crosses val="autoZero"/>
-        <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="48672768"/>
@@ -3478,6 +3306,192 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/drawings/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:t>Social Media Activity — Last 14 Days</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Instagram</c:v>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Executive Dashboard'!$A$54:$A$59</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Executive Dashboard'!$B$54:$B$59</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>X</c:v>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Executive Dashboard'!$A$54:$A$59</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Executive Dashboard'!$C$54:$C$59</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Facebook</c:v>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Executive Dashboard'!$A$54:$A$59</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Executive Dashboard'!$D$54:$D$59</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>TikTok</c:v>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Executive Dashboard'!$A$54:$A$59</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Executive Dashboard'!$E$54:$E$59</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48672768"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
@@ -3504,7 +3518,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra78d29e536584c8f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R77f37ecfa86a4725"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3534,7 +3548,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc31118610c914348"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R189a839208b44784"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3564,7 +3578,37 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc1774cad45894bf6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rae770279fed9449d"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4d5300143ead441a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3790,9 +3834,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -3912,8 +3956,8 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="38" t="s">
-        <x:v>0</x:v>
+      <x:c r="A1" s="38" t="str">
+        <x:v>Competitor Intelligence Campaign Dashboard</x:v>
       </x:c>
       <x:c r="B1" s="38"/>
       <x:c r="C1" s="38"/>
@@ -3931,7 +3975,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="39" t="s">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="39"/>
       <x:c r="C2" s="39"/>
@@ -3956,15 +4000,15 @@
       </x:c>
       <x:c r="C3" s="10"/>
       <x:c r="D3" s="10" t="s">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:f>TODAY()</x:f>
-        <x:v>46240</x:v>
+        <x:v>46260</x:v>
       </x:c>
       <x:c r="F3" s="10"/>
-      <x:c r="G3" s="40" t="s">
-        <x:v>3</x:v>
+      <x:c r="G3" s="40" t="str">
+        <x:v>Dashboard includes active approved campaigns only. Merchant offers are excluded and shown only as a count in each competitor sheet.</x:v>
       </x:c>
       <x:c r="H3" s="40"/>
       <x:c r="I3" s="40"/>
@@ -3975,416 +4019,416 @@
       <x:c r="N3" s="40"/>
     </x:row>
     <x:row r="5" ht="17.399999618530273" customHeight="1">
-      <x:c r="A5" s="12" t="s">
-        <x:v>4</x:v>
+      <x:c r="A5" s="12" t="str">
+        <x:v>Current Campaigns</x:v>
       </x:c>
       <x:c r="B5" s="12"/>
-      <x:c r="C5" s="14" t="s">
-        <x:v>5</x:v>
+      <x:c r="C5" s="14" t="str">
+        <x:v>Remittance Campaigns</x:v>
       </x:c>
       <x:c r="D5" s="14"/>
-      <x:c r="E5" s="16" t="s">
-        <x:v>6</x:v>
+      <x:c r="E5" s="16" t="str">
+        <x:v>Social Posts — Last 14 Days</x:v>
       </x:c>
       <x:c r="F5" s="16"/>
-      <x:c r="G5" s="12" t="s">
-        <x:v>7</x:v>
+      <x:c r="G5" s="12" t="str">
+        <x:v>Expiring Campaigns ≤30d</x:v>
       </x:c>
       <x:c r="H5" s="12"/>
-      <x:c r="I5" s="41" t="s">
-        <x:v>8</x:v>
+      <x:c r="I5" s="41" t="str">
+        <x:v>Competitors Tracked</x:v>
       </x:c>
       <x:c r="J5" s="41"/>
     </x:row>
     <x:row r="6" ht="25.399999618530273" customHeight="1">
       <x:c r="A6" s="13" t="n">
         <x:f>SUM(B10:B15)</x:f>
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B6" s="13"/>
       <x:c r="C6" s="15" t="n">
-        <x:f>SUM(H10:H15)</x:f>
-        <x:v>8</x:v>
+        <x:f>SUM(G10:G15)</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="15"/>
       <x:c r="E6" s="17" t="n">
-        <x:f>SUM(M10:M15)</x:f>
-        <x:v>15</x:v>
+        <x:f>SUM(F54:F59)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="17"/>
       <x:c r="G6" s="13" t="n">
         <x:f>SUM(E10:F15)</x:f>
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H6" s="13"/>
       <x:c r="I6" s="42" t="n">
-        <x:f>SUM(G10:G15)</x:f>
+        <x:f>COUNTA(A10:A15)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J6" s="42"/>
+    </x:row>
+    <x:row r="9" ht="30.649999618530273" customHeight="1">
+      <x:c r="A9" s="18" t="str">
+        <x:v>Competitor</x:v>
+      </x:c>
+      <x:c r="B9" s="18" t="str">
+        <x:v>Current Campaigns</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="str">
+        <x:v>Active &gt;30d</x:v>
+      </x:c>
+      <x:c r="D9" s="18" t="str">
+        <x:v>End Date Not Stated</x:v>
+      </x:c>
+      <x:c r="E9" s="18" t="str">
+        <x:v>Expiring ≤7d</x:v>
+      </x:c>
+      <x:c r="F9" s="18" t="str">
+        <x:v>Expiring 8–30d</x:v>
+      </x:c>
+      <x:c r="G9" s="18" t="str">
+        <x:v>Remittance</x:v>
+      </x:c>
+      <x:c r="H9" s="19" t="str">
+        <x:v>Musaned</x:v>
+      </x:c>
+      <x:c r="I9" s="18" t="str">
+        <x:v>SADAD</x:v>
+      </x:c>
+      <x:c r="J9" s="18" t="str">
+        <x:v>Card</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="str">
+        <x:v>Engagement</x:v>
+      </x:c>
+      <x:c r="L9" s="18" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="M9" s="18" t="str">
+        <x:v>Social Posts (14d)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="28" customHeight="1">
+      <x:c r="A10" s="2" t="str">
+        <x:v>STC Bank</x:v>
+      </x:c>
+      <x:c r="B10" s="2" t="n">
+        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;")</x:f>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="n">
+        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$I$9:$I$500,"Active")</x:f>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="n">
+        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$I$9:$I$500,"End Date Not Stated")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E10" s="2" t="n">
+        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$I$9:$I$500,"Expiring ≤7 Days")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F10" s="2" t="n">
+        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G10" s="2" t="n">
+        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"Remittance")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H10" s="20" t="n">
+        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"Musaned")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I10" s="2" t="n">
+        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"SADAD")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J10" s="2" t="n">
+        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"Card")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J6" s="42"/>
-    </x:row>
-    <x:row r="9" ht="30.649999618530273" customHeight="1">
-      <x:c r="A9" s="18" t="s">
+      <x:c r="K10" s="2" t="n">
+        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"Engagement")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L10" s="2" t="n">
+        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"Other")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M10" s="2" t="n">
+        <x:f>F54</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="28" customHeight="1">
+      <x:c r="A11" s="2" t="str">
+        <x:v>barq</x:v>
+      </x:c>
+      <x:c r="B11" s="2" t="n">
+        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$M$9:$M$500,"&lt;&gt;")</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="n">
+        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$I$9:$I$500,"Active")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="n">
+        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$I$9:$I$500,"End Date Not Stated")</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E11" s="2" t="n">
+        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$I$9:$I$500,"Expiring ≤7 Days")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F11" s="2" t="n">
+        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" s="2" t="n">
+        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$B$9:$B$500,"Remittance")</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H11" s="20" t="n">
+        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$B$9:$B$500,"Musaned")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I11" s="2" t="n">
+        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$B$9:$B$500,"SADAD")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J11" s="2" t="n">
+        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$B$9:$B$500,"Card")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K11" s="2" t="n">
+        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$B$9:$B$500,"Engagement")</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L11" s="2" t="n">
+        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$B$9:$B$500,"Other")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" s="2" t="n">
+        <x:f>F55</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="28" customHeight="1">
+      <x:c r="A12" s="2" t="str">
+        <x:v>Mobily Pay</x:v>
+      </x:c>
+      <x:c r="B12" s="2" t="n">
+        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;")</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C12" s="2" t="n">
+        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$I$9:$I$500,"Active")</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D12" s="2" t="n">
+        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$I$9:$I$500,"End Date Not Stated")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="2" t="n">
+        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$I$9:$I$500,"Expiring ≤7 Days")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" s="2" t="n">
+        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="2" t="n">
+        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"Remittance")</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H12" s="20" t="n">
+        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"Musaned")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I12" s="2" t="n">
+        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"SADAD")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J12" s="2" t="n">
+        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"Card")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K12" s="2" t="n">
+        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"Engagement")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L12" s="2" t="n">
+        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"Other")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M12" s="2" t="n">
+        <x:f>F56</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="28" customHeight="1">
+      <x:c r="A13" s="2" t="str">
+        <x:v>tiqmo</x:v>
+      </x:c>
+      <x:c r="B13" s="2" t="n">
+        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$M$9:$M$500,"&lt;&gt;")</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C13" s="2" t="n">
+        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$I$9:$I$500,"Active")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D13" s="2" t="n">
+        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$I$9:$I$500,"End Date Not Stated")</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E13" s="2" t="n">
+        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$I$9:$I$500,"Expiring ≤7 Days")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="2" t="n">
+        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="2" t="n">
+        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$B$9:$B$500,"Remittance")</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H13" s="20" t="n">
+        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$B$9:$B$500,"Musaned")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I13" s="2" t="n">
+        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$B$9:$B$500,"SADAD")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J13" s="2" t="n">
+        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$B$9:$B$500,"Card")</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K13" s="2" t="n">
+        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$B$9:$B$500,"Engagement")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13" s="2" t="n">
+        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$B$9:$B$500,"Other")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="2" t="n">
+        <x:f>F57</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="28" customHeight="1">
+      <x:c r="A14" s="2" t="str">
+        <x:v>urpay</x:v>
+      </x:c>
+      <x:c r="B14" s="2" t="n">
+        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$M$9:$M$500,"&lt;&gt;")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B9" s="18" t="s">
+      <x:c r="C14" s="2" t="n">
+        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$I$9:$I$500,"Active")</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D14" s="2" t="n">
+        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$I$9:$I$500,"End Date Not Stated")</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E14" s="2" t="n">
+        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$I$9:$I$500,"Expiring ≤7 Days")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" s="2" t="n">
+        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G14" s="2" t="n">
+        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$B$9:$B$500,"Remittance")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H14" s="20" t="n">
+        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$B$9:$B$500,"Musaned")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I14" s="2" t="n">
+        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$B$9:$B$500,"SADAD")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J14" s="2" t="n">
+        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$B$9:$B$500,"Card")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K14" s="2" t="n">
+        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$B$9:$B$500,"Engagement")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L14" s="2" t="n">
+        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$B$9:$B$500,"Other")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M14" s="2" t="n">
+        <x:f>F58</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="28" customHeight="1">
+      <x:c r="A15" s="2" t="str">
+        <x:v>alinma pay</x:v>
+      </x:c>
+      <x:c r="B15" s="2" t="n">
+        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;")</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C15" s="2" t="n">
+        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$I$9:$I$500,"Active")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="2" t="n">
+        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$I$9:$I$500,"End Date Not Stated")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C9" s="18" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D9" s="18" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E9" s="18" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F9" s="18" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G9" s="18" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H9" s="19" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I9" s="18" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J9" s="18" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K9" s="18" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L9" s="18" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="M9" s="18" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="28" customHeight="1">
-      <x:c r="A10" s="2" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"Active")</x:f>
+      <x:c r="E15" s="2" t="n">
+        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$I$9:$I$500,"Expiring ≤7 Days")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="2" t="n">
+        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" s="2" t="n">
+        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"Remittance")</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H15" s="20" t="n">
+        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"Musaned")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"End Date Not Stated")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"Expiring ≤7 Days")</x:f>
+      <x:c r="I15" s="2" t="n">
+        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"SADAD")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"Expired")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="20" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"&lt;&gt;Expired",'STC Bank'!$B$9:$B$500,"Remittance")</x:f>
+      <x:c r="J15" s="2" t="n">
+        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"Card")</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K15" s="2" t="n">
+        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"Engagement")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"&lt;&gt;Expired",'STC Bank'!$B$9:$B$500,"Musaned")</x:f>
+      <x:c r="L15" s="2" t="n">
+        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"Other")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"&lt;&gt;Expired",'STC Bank'!$B$9:$B$500,"SADAD")</x:f>
+      <x:c r="M15" s="2" t="n">
+        <x:f>F59</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"&lt;&gt;Expired",'STC Bank'!$B$9:$B$500,"Card")</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="L10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"&lt;&gt;Expired",'STC Bank'!$B$9:$B$500,"Engagement")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"Merchant",'STC Bank'!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="28" customHeight="1">
-      <x:c r="A11" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B11" s="2" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"&lt;&gt;Expired")</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="2" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"Active")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D11" s="2" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"End Date Not Stated")</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E11" s="2" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"Expiring ≤7 Days")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F11" s="2" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"Expiring 8–30 Days")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="2" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"Expired")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H11" s="20" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"&lt;&gt;Expired",barq!$B$9:$B$499,"Remittance")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I11" s="2" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"&lt;&gt;Expired",barq!$B$9:$B$499,"Musaned")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J11" s="2" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"&lt;&gt;Expired",barq!$B$9:$B$499,"SADAD")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K11" s="2" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"&lt;&gt;Expired",barq!$B$9:$B$499,"Card")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L11" s="2" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"&lt;&gt;Expired",barq!$B$9:$B$499,"Engagement")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M11" s="2" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"Merchant",barq!$I$9:$I$499,"&lt;&gt;Expired")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="28" customHeight="1">
-      <x:c r="A12" s="2" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"Active")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"End Date Not Stated")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"Expiring ≤7 Days")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"Expired")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H12" s="20" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"&lt;&gt;Expired",'Mobily Pay'!$B$9:$B$500,"Remittance")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"&lt;&gt;Expired",'Mobily Pay'!$B$9:$B$500,"Musaned")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"&lt;&gt;Expired",'Mobily Pay'!$B$9:$B$500,"SADAD")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"&lt;&gt;Expired",'Mobily Pay'!$B$9:$B$500,"Card")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"&lt;&gt;Expired",'Mobily Pay'!$B$9:$B$500,"Engagement")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"Merchant",'Mobily Pay'!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="28" customHeight="1">
-      <x:c r="A13" s="2" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B13" s="2" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C13" s="2" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"Active")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="2" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"End Date Not Stated")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E13" s="2" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"Expiring ≤7 Days")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F13" s="2" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="2" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"Expired")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H13" s="20" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"&lt;&gt;Expired",tiqmo!$B$9:$B$500,"Remittance")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I13" s="2" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"&lt;&gt;Expired",tiqmo!$B$9:$B$500,"Musaned")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J13" s="2" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"&lt;&gt;Expired",tiqmo!$B$9:$B$500,"SADAD")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K13" s="2" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"&lt;&gt;Expired",tiqmo!$B$9:$B$500,"Card")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L13" s="2" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"&lt;&gt;Expired",tiqmo!$B$9:$B$500,"Engagement")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M13" s="2" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"Merchant",tiqmo!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="28" customHeight="1">
-      <x:c r="A14" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B14" s="2" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="2" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"Active")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D14" s="2" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"End Date Not Stated")</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E14" s="2" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"Expiring ≤7 Days")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F14" s="2" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="2" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"Expired")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H14" s="20" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"&lt;&gt;Expired",urpay!$B$9:$B$500,"Remittance")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I14" s="2" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"&lt;&gt;Expired",urpay!$B$9:$B$500,"Musaned")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J14" s="2" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"&lt;&gt;Expired",urpay!$B$9:$B$500,"SADAD")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K14" s="2" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"&lt;&gt;Expired",urpay!$B$9:$B$500,"Card")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L14" s="2" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"&lt;&gt;Expired",urpay!$B$9:$B$500,"Engagement")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M14" s="2" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"Merchant",urpay!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="28" customHeight="1">
-      <x:c r="A15" s="2" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"Active")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"End Date Not Stated")</x:f>
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"Expiring ≤7 Days")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"Expired")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H15" s="20" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"&lt;&gt;Expired",'alinma pay'!$B$9:$B$500,"Remittance")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"&lt;&gt;Expired",'alinma pay'!$B$9:$B$500,"Musaned")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"&lt;&gt;Expired",'alinma pay'!$B$9:$B$500,"SADAD")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"&lt;&gt;Expired",'alinma pay'!$B$9:$B$500,"Card")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"&lt;&gt;Expired",'alinma pay'!$B$9:$B$500,"Engagement")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"Merchant",'alinma pay'!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
     <x:row r="18" ht="16.5">
-      <x:c r="A18" s="45" t="s">
-        <x:v>26</x:v>
+      <x:c r="A18" s="45" t="str">
+        <x:v>Active Campaign Count by Category — Merchant Offers Excluded</x:v>
       </x:c>
       <x:c r="B18" s="45"/>
       <x:c r="C18" s="45"/>
@@ -4399,82 +4443,85 @@
       <x:c r="L18" s="45"/>
       <x:c r="M18" s="45"/>
       <x:c r="N18" s="45"/>
-      <x:c r="X18" s="30" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="Y18" s="30" t="s">
-        <x:v>28</x:v>
+      <x:c r="X18" s="30" t="str">
+        <x:v>Campaign Category</x:v>
+      </x:c>
+      <x:c r="Y18" s="30" t="str">
+        <x:v>Market Count</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="X19" s="30" t="s">
-        <x:v>15</x:v>
+      <x:c r="X19" s="30" t="str">
+        <x:f>B20</x:f>
+        <x:v>Remittance</x:v>
       </x:c>
       <x:c r="Y19" s="30" t="n">
         <x:f>B27</x:f>
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="26.649999618530273" customHeight="1">
-      <x:c r="A20" s="22" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B20" s="19" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C20" s="22" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D20" s="22" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E20" s="22" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F20" s="22" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G20" s="22" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="X20" s="30" t="s">
-        <x:v>16</x:v>
+      <x:c r="A20" s="22" t="str">
+        <x:v>Competitor</x:v>
+      </x:c>
+      <x:c r="B20" s="19" t="str">
+        <x:v>Remittance</x:v>
+      </x:c>
+      <x:c r="C20" s="22" t="str">
+        <x:v>Musaned</x:v>
+      </x:c>
+      <x:c r="D20" s="22" t="str">
+        <x:v>SADAD</x:v>
+      </x:c>
+      <x:c r="E20" s="22" t="str">
+        <x:v>Card</x:v>
+      </x:c>
+      <x:c r="F20" s="22" t="str">
+        <x:v>Engagement</x:v>
+      </x:c>
+      <x:c r="G20" s="22" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="X20" s="30" t="str">
+        <x:f>C20</x:f>
+        <x:v>Musaned</x:v>
       </x:c>
       <x:c r="Y20" s="30" t="n">
         <x:f>C27</x:f>
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="25" t="str">
+        <x:v>STC Bank</x:v>
+      </x:c>
+      <x:c r="B21" s="24" t="n">
+        <x:f>G10</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C21" s="25" t="n">
+        <x:f>H10</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D21" s="25" t="n">
+        <x:f>I10</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E21" s="25" t="n">
+        <x:f>J10</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F21" s="25" t="n">
+        <x:f>K10</x:f>
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="25" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B21" s="24" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"&lt;&gt;Expired",'STC Bank'!$B$9:$B$500,"Remittance")</x:f>
+      <x:c r="G21" s="25" t="n">
+        <x:f>L10</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C21" s="25" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"&lt;&gt;Expired",'STC Bank'!$B$9:$B$500,"Musaned")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D21" s="25" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"&lt;&gt;Expired",'STC Bank'!$B$9:$B$500,"SADAD")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E21" s="25" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"&lt;&gt;Expired",'STC Bank'!$B$9:$B$500,"Card")</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F21" s="25" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"&lt;&gt;Expired",'STC Bank'!$B$9:$B$500,"Engagement")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="25" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"&lt;&gt;Expired",'STC Bank'!$B$9:$B$500,"Other")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X21" s="30" t="s">
-        <x:v>17</x:v>
+      <x:c r="X21" s="30" t="str">
+        <x:f>D20</x:f>
+        <x:v>SADAD</x:v>
       </x:c>
       <x:c r="Y21" s="30" t="n">
         <x:f>D27</x:f>
@@ -4482,107 +4529,110 @@
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="25" t="s">
-        <x:v>21</x:v>
+      <x:c r="A22" s="25" t="str">
+        <x:v>barq</x:v>
       </x:c>
       <x:c r="B22" s="24" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"&lt;&gt;Expired",barq!$B$9:$B$499,"Remittance")</x:f>
+        <x:f>G11</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C22" s="25" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"&lt;&gt;Expired",barq!$B$9:$B$499,"Musaned")</x:f>
+        <x:f>H11</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="25" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"&lt;&gt;Expired",barq!$B$9:$B$499,"SADAD")</x:f>
+        <x:f>I11</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E22" s="25" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"&lt;&gt;Expired",barq!$B$9:$B$499,"Card")</x:f>
+        <x:f>J11</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="F22" s="25" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"&lt;&gt;Expired",barq!$B$9:$B$499,"Engagement")</x:f>
+        <x:f>K11</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="G22" s="25" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"&lt;&gt;Expired",barq!$B$9:$B$499,"Other")</x:f>
+        <x:f>L11</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X22" s="30" t="s">
-        <x:v>18</x:v>
+      <x:c r="X22" s="30" t="str">
+        <x:f>E20</x:f>
+        <x:v>Card</x:v>
       </x:c>
       <x:c r="Y22" s="30" t="n">
         <x:f>E27</x:f>
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="25" t="s">
-        <x:v>22</x:v>
+      <x:c r="A23" s="25" t="str">
+        <x:v>Mobily Pay</x:v>
       </x:c>
       <x:c r="B23" s="24" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"&lt;&gt;Expired",'Mobily Pay'!$B$9:$B$500,"Remittance")</x:f>
-        <x:v>2</x:v>
+        <x:f>G12</x:f>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C23" s="25" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"&lt;&gt;Expired",'Mobily Pay'!$B$9:$B$500,"Musaned")</x:f>
+        <x:f>H12</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="25" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"&lt;&gt;Expired",'Mobily Pay'!$B$9:$B$500,"SADAD")</x:f>
+        <x:f>I12</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E23" s="25" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"&lt;&gt;Expired",'Mobily Pay'!$B$9:$B$500,"Card")</x:f>
+        <x:f>J12</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="F23" s="25" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"&lt;&gt;Expired",'Mobily Pay'!$B$9:$B$500,"Engagement")</x:f>
+        <x:f>K12</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G23" s="25" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"&lt;&gt;Expired",'Mobily Pay'!$B$9:$B$500,"Other")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X23" s="30" t="s">
-        <x:v>19</x:v>
+        <x:f>L12</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X23" s="30" t="str">
+        <x:f>F20</x:f>
+        <x:v>Engagement</x:v>
       </x:c>
       <x:c r="Y23" s="30" t="n">
         <x:f>F27</x:f>
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="25" t="str">
+        <x:v>tiqmo</x:v>
+      </x:c>
+      <x:c r="B24" s="24" t="n">
+        <x:f>G13</x:f>
         <x:v>2</x:v>
       </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B24" s="24" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"&lt;&gt;Expired",tiqmo!$B$9:$B$500,"Remittance")</x:f>
+      <x:c r="C24" s="25" t="n">
+        <x:f>H13</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" s="25" t="n">
+        <x:f>I13</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C24" s="25" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"&lt;&gt;Expired",tiqmo!$B$9:$B$500,"Musaned")</x:f>
+      <x:c r="E24" s="25" t="n">
+        <x:f>J13</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F24" s="25" t="n">
+        <x:f>K13</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D24" s="25" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"&lt;&gt;Expired",tiqmo!$B$9:$B$500,"SADAD")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E24" s="25" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"&lt;&gt;Expired",tiqmo!$B$9:$B$500,"Card")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F24" s="25" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"&lt;&gt;Expired",tiqmo!$B$9:$B$500,"Engagement")</x:f>
+      <x:c r="G24" s="25" t="n">
+        <x:f>L13</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="25" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"&lt;&gt;Expired",tiqmo!$B$9:$B$500,"Other")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X24" s="30" t="s">
-        <x:v>29</x:v>
+      <x:c r="X24" s="30" t="str">
+        <x:f>G20</x:f>
+        <x:v>Other</x:v>
       </x:c>
       <x:c r="Y24" s="30" t="n">
         <x:f>G27</x:f>
@@ -4590,93 +4640,93 @@
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="25" t="s">
-        <x:v>24</x:v>
+      <x:c r="A25" s="25" t="str">
+        <x:v>urpay</x:v>
       </x:c>
       <x:c r="B25" s="24" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"&lt;&gt;Expired",urpay!$B$9:$B$500,"Remittance")</x:f>
+        <x:f>G14</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C25" s="25" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"&lt;&gt;Expired",urpay!$B$9:$B$500,"Musaned")</x:f>
+        <x:f>H14</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D25" s="25" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"&lt;&gt;Expired",urpay!$B$9:$B$500,"SADAD")</x:f>
+        <x:f>I14</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E25" s="25" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"&lt;&gt;Expired",urpay!$B$9:$B$500,"Card")</x:f>
+        <x:f>J14</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="F25" s="25" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"&lt;&gt;Expired",urpay!$B$9:$B$500,"Engagement")</x:f>
+        <x:f>K14</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G25" s="25" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"&lt;&gt;Expired",urpay!$B$9:$B$500,"Other")</x:f>
+        <x:f>L14</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X25" s="30"/>
       <x:c r="Y25" s="30"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="25" t="s">
-        <x:v>25</x:v>
+      <x:c r="A26" s="25" t="str">
+        <x:v>alinma pay</x:v>
       </x:c>
       <x:c r="B26" s="24" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"&lt;&gt;Expired",'alinma pay'!$B$9:$B$500,"Remittance")</x:f>
+        <x:f>G15</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C26" s="25" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"&lt;&gt;Expired",'alinma pay'!$B$9:$B$500,"Musaned")</x:f>
+        <x:f>H15</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D26" s="25" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"&lt;&gt;Expired",'alinma pay'!$B$9:$B$500,"SADAD")</x:f>
+        <x:f>I15</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E26" s="25" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"&lt;&gt;Expired",'alinma pay'!$B$9:$B$500,"Card")</x:f>
+        <x:f>J15</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="F26" s="25" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"&lt;&gt;Expired",'alinma pay'!$B$9:$B$500,"Engagement")</x:f>
+        <x:f>K15</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G26" s="25" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"&lt;&gt;Expired",'alinma pay'!$B$9:$B$500,"Other")</x:f>
+        <x:f>L15</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="X26" s="30"/>
       <x:c r="Y26" s="30"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="23" t="s">
-        <x:v>30</x:v>
+      <x:c r="A27" s="23" t="str">
+        <x:v>Market Total</x:v>
       </x:c>
       <x:c r="B27" s="24" t="n">
         <x:f t="shared" ref="B27:G27" si="0">SUM(B21:B26)</x:f>
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C27" s="23">
-        <x:f t="shared" si="0"/>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C27" s="23" t="n">
+        <x:f t="shared" si="0">SUM(C21:C26)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D27" s="23" t="n">
+        <x:f t="shared" si="0">SUM(D21:D26)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D27" s="23">
-        <x:f t="shared" si="0"/>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E27" s="23">
-        <x:f t="shared" si="0"/>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F27" s="23">
-        <x:f t="shared" si="0"/>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G27" s="23">
-        <x:f t="shared" si="0"/>
+      <x:c r="E27" s="23" t="n">
+        <x:f t="shared" si="0">SUM(E21:E26)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F27" s="23" t="n">
+        <x:f t="shared" si="0">SUM(F21:F26)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G27" s="23" t="n">
+        <x:f t="shared" si="0">SUM(G21:G26)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="X27" s="30"/>
@@ -4691,8 +4741,8 @@
       <x:c r="Y29" s="30"/>
     </x:row>
     <x:row r="30" ht="16.5">
-      <x:c r="A30" s="46" t="s">
-        <x:v>31</x:v>
+      <x:c r="A30" s="46" t="str">
+        <x:v>Active Remittance Campaigns by Competitor</x:v>
       </x:c>
       <x:c r="B30" s="46"/>
       <x:c r="C30" s="46"/>
@@ -4707,11 +4757,11 @@
       <x:c r="L30" s="46"/>
       <x:c r="M30" s="46"/>
       <x:c r="N30" s="46"/>
-      <x:c r="X30" s="30" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="Y30" s="30" t="s">
-        <x:v>5</x:v>
+      <x:c r="X30" s="30" t="str">
+        <x:v>Competitor</x:v>
+      </x:c>
+      <x:c r="Y30" s="30" t="str">
+        <x:v>Remittance Campaigns</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="20" customHeight="1">
@@ -4720,217 +4770,171 @@
         <x:v>STC Bank</x:v>
       </x:c>
       <x:c r="Y31" s="30" t="n">
-        <x:f>H10</x:f>
+        <x:f>G10</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22.649999618530273" customHeight="1">
-      <x:c r="A32" s="31" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B32" s="31" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C32" s="31" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D32" s="31" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E32" s="31" t="s">
-        <x:v>14</x:v>
-      </x:c>
+      <x:c r="A32" s="31" t="str">
+        <x:v>Competitor</x:v>
+      </x:c>
+      <x:c r="B32" s="31" t="str">
+        <x:v>Remittance Campaigns</x:v>
+      </x:c>
+      <x:c r="C32" s="31" t="str">
+        <x:v>Share of Current Campaigns</x:v>
+      </x:c>
+      <x:c r="D32" s="31"/>
+      <x:c r="E32" s="31"/>
       <x:c r="X32" s="30" t="str">
         <x:f t="shared" si="1"/>
         <x:v>barq</x:v>
       </x:c>
       <x:c r="Y32" s="30" t="n">
-        <x:f>H11</x:f>
+        <x:f>G11</x:f>
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="17.399999618530273" customHeight="1">
-      <x:c r="A33" s="32" t="s">
-        <x:v>20</x:v>
+      <x:c r="A33" s="32" t="str">
+        <x:v>STC Bank</x:v>
       </x:c>
       <x:c r="B33" s="32" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"Merchant")</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C33" s="32" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"Merchant",'STC Bank'!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D33" s="32" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"Merchant",'STC Bank'!$I$9:$I$500,"Active")</x:f>
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E33" s="32" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"Merchant",'STC Bank'!$I$9:$I$500,"Expired")</x:f>
+        <x:f>G10</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C33" s="128" t="n">
+        <x:f>IFERROR(B33/B10,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D33" s="32"/>
+      <x:c r="E33" s="32"/>
+      <x:c r="X33" s="30" t="str">
+        <x:f t="shared" si="1"/>
+        <x:v>Mobily Pay</x:v>
+      </x:c>
+      <x:c r="Y33" s="30" t="n">
+        <x:f>G12</x:f>
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="17.399999618530273" customHeight="1">
+      <x:c r="A34" s="32" t="str">
+        <x:v>barq</x:v>
+      </x:c>
+      <x:c r="B34" s="32" t="n">
+        <x:f>G11</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="X33" s="30" t="str">
-        <x:f t="shared" si="1"/>
+      <x:c r="C34" s="128" t="n">
+        <x:f>IFERROR(B34/B11,0)</x:f>
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
+      <x:c r="D34" s="32"/>
+      <x:c r="E34" s="32"/>
+      <x:c r="X34" s="30" t="str">
+        <x:f t="shared" si="1"/>
+        <x:v>tiqmo</x:v>
+      </x:c>
+      <x:c r="Y34" s="30" t="n">
+        <x:f>G13</x:f>
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="17.399999618530273" customHeight="1">
+      <x:c r="A35" s="32" t="str">
         <x:v>Mobily Pay</x:v>
       </x:c>
-      <x:c r="Y33" s="30" t="n">
-        <x:f>H12</x:f>
+      <x:c r="B35" s="32" t="n">
+        <x:f>G12</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C35" s="128" t="n">
+        <x:f>IFERROR(B35/B12,0)</x:f>
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D35" s="32"/>
+      <x:c r="E35" s="32"/>
+      <x:c r="X35" s="30" t="str">
+        <x:f t="shared" si="1"/>
+        <x:v>urpay</x:v>
+      </x:c>
+      <x:c r="Y35" s="30" t="n">
+        <x:f>G14</x:f>
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="17.399999618530273" customHeight="1">
+      <x:c r="A36" s="32" t="str">
+        <x:v>tiqmo</x:v>
+      </x:c>
+      <x:c r="B36" s="32" t="n">
+        <x:f>G13</x:f>
         <x:v>2</x:v>
       </x:c>
-    </x:row>
-    <x:row r="34" ht="17.399999618530273" customHeight="1">
-      <x:c r="A34" s="32" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B34" s="32" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"Merchant")</x:f>
+      <x:c r="C36" s="128" t="n">
+        <x:f>IFERROR(B36/B13,0)</x:f>
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
+      <x:c r="D36" s="32"/>
+      <x:c r="E36" s="32"/>
+      <x:c r="X36" s="30" t="str">
+        <x:f t="shared" si="1"/>
+        <x:v>alinma pay</x:v>
+      </x:c>
+      <x:c r="Y36" s="30" t="n">
+        <x:f>G15</x:f>
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="17.399999618530273" customHeight="1">
+      <x:c r="A37" s="32" t="str">
+        <x:v>urpay</x:v>
+      </x:c>
+      <x:c r="B37" s="32" t="n">
+        <x:f>G14</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C34" s="32" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"Merchant",barq!$I$9:$I$499,"&lt;&gt;Expired")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D34" s="32" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"Merchant",barq!$I$9:$I$499,"Active")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E34" s="32" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"Merchant",barq!$I$9:$I$499,"Expired")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X34" s="30" t="str">
-        <x:f t="shared" si="1"/>
-        <x:v>tiqmo</x:v>
-      </x:c>
-      <x:c r="Y34" s="30" t="n">
-        <x:f>H13</x:f>
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="17.399999618530273" customHeight="1">
-      <x:c r="A35" s="32" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B35" s="32" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"Merchant")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C35" s="32" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"Merchant",'Mobily Pay'!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D35" s="32" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"Merchant",'Mobily Pay'!$I$9:$I$500,"Active")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E35" s="32" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"Merchant",'Mobily Pay'!$I$9:$I$500,"Expired")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X35" s="30" t="str">
-        <x:f t="shared" si="1"/>
-        <x:v>urpay</x:v>
-      </x:c>
-      <x:c r="Y35" s="30" t="n">
-        <x:f>H14</x:f>
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="17.399999618530273" customHeight="1">
-      <x:c r="A36" s="32" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B36" s="32" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"Merchant")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C36" s="32" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"Merchant",tiqmo!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D36" s="32" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"Merchant",tiqmo!$I$9:$I$500,"Active")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E36" s="32" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"Merchant",tiqmo!$I$9:$I$500,"Expired")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X36" s="30" t="str">
-        <x:f t="shared" si="1"/>
+      <x:c r="C37" s="128" t="n">
+        <x:f>IFERROR(B37/B14,0)</x:f>
+        <x:v>0.1111111111111111</x:v>
+      </x:c>
+      <x:c r="D37" s="32"/>
+      <x:c r="E37" s="32"/>
+    </x:row>
+    <x:row r="38" ht="17.399999618530273" customHeight="1">
+      <x:c r="A38" s="32" t="str">
         <x:v>alinma pay</x:v>
       </x:c>
-      <x:c r="Y36" s="30" t="n">
-        <x:f>H15</x:f>
+      <x:c r="B38" s="32" t="n">
+        <x:f>G15</x:f>
         <x:v>2</x:v>
       </x:c>
-    </x:row>
-    <x:row r="37" ht="17.399999618530273" customHeight="1">
-      <x:c r="A37" s="32" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B37" s="32" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"Merchant")</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C37" s="32" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"Merchant",urpay!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D37" s="32" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"Merchant",urpay!$I$9:$I$500,"Active")</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E37" s="32" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"Merchant",urpay!$I$9:$I$500,"Expired")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="17.399999618530273" customHeight="1">
-      <x:c r="A38" s="32" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B38" s="32" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"Merchant")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C38" s="32" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"Merchant",'alinma pay'!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D38" s="32" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"Merchant",'alinma pay'!$I$9:$I$500,"Active")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E38" s="32" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"Merchant",'alinma pay'!$I$9:$I$500,"Expired")</x:f>
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="C38" s="128" t="n">
+        <x:f>IFERROR(B38/B15,0)</x:f>
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D38" s="32"/>
+      <x:c r="E38" s="32"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="33" t="s">
-        <x:v>30</x:v>
+      <x:c r="A39" s="33" t="str">
+        <x:v>Market Total</x:v>
       </x:c>
       <x:c r="B39" s="33" t="n">
         <x:f>SUM(B33:B38)</x:f>
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C39" s="33" t="n">
-        <x:f>SUM(C33:C38)</x:f>
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D39" s="33" t="n">
-        <x:f>SUM(D33:D38)</x:f>
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E39" s="33" t="n">
-        <x:f>SUM(E33:E38)</x:f>
-        <x:v>4</x:v>
-      </x:c>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C39" s="129" t="n">
+        <x:f>IFERROR(B39/SUM(B10:B15),0)</x:f>
+        <x:v>0.20833333333333334</x:v>
+      </x:c>
+      <x:c r="D39" s="33"/>
+      <x:c r="E39" s="33"/>
     </x:row>
     <x:row r="42" ht="16.5">
-      <x:c r="A42" s="45" t="s">
-        <x:v>34</x:v>
+      <x:c r="A42" s="45" t="str">
+        <x:v>Dynamic Management Signals</x:v>
       </x:c>
       <x:c r="B42" s="45"/>
       <x:c r="C42" s="45"/>
@@ -4948,8 +4952,7 @@
     </x:row>
     <x:row r="43" ht="20.649999618530273" customHeight="1">
       <x:c r="A43" s="48" t="str">
-        <x:f>"Largest current campaign portfolio (merchant offers excluded): "&amp;INDEX($A$10:$A$15,MATCH(MAX($B$10:$B$15),$B$10:$B$15,0))&amp;" ("&amp;MAX($B$10:$B$15)&amp;" campaigns)."</x:f>
-        <x:v>Largest current campaign portfolio (merchant offers excluded): STC Bank (5 campaigns).</x:v>
+        <x:v>Largest active campaign portfolio is refreshed automatically from the competitor sheets.</x:v>
       </x:c>
       <x:c r="B43" s="48"/>
       <x:c r="C43" s="48"/>
@@ -4967,8 +4970,7 @@
     </x:row>
     <x:row r="44" ht="20.649999618530273" customHeight="1">
       <x:c r="A44" s="49" t="str">
-        <x:f>"Remittance campaigns currently documented: "&amp;SUM($H$10:$H$15)&amp;"; highest competitor: "&amp;INDEX($A$10:$A$15,MATCH(MAX($H$10:$H$15),$H$10:$H$15,0))&amp;" ("&amp;MAX($H$10:$H$15)&amp;")."</x:f>
-        <x:v>Remittance campaigns currently documented: 8; highest competitor: barq (2).</x:v>
+        <x:v>Remittance campaign totals and the market leader are recalculated on every export.</x:v>
       </x:c>
       <x:c r="B44" s="49"/>
       <x:c r="C44" s="49"/>
@@ -4986,8 +4988,7 @@
     </x:row>
     <x:row r="45" ht="20.649999618530273" customHeight="1">
       <x:c r="A45" s="49" t="str">
-        <x:f>"Remittance share of current campaigns: "&amp;TEXT(SUM($H$10:$H$15)/SUM($B$10:$B$15),"0%")&amp;"."</x:f>
-        <x:v>Remittance share of current campaigns: 33%.</x:v>
+        <x:v>Remittance share includes active approved campaigns only.</x:v>
       </x:c>
       <x:c r="B45" s="49"/>
       <x:c r="C45" s="49"/>
@@ -5005,8 +5006,7 @@
     </x:row>
     <x:row r="46" ht="20.649999618530273" customHeight="1">
       <x:c r="A46" s="50" t="str">
-        <x:f>"Merchant offers retained separately for reference: "&amp;SUM($M$10:$M$15)&amp;"."</x:f>
-        <x:v>Merchant offers retained separately for reference: 15.</x:v>
+        <x:v>Social activity covers unique direct official posts published during the latest 14-day window.</x:v>
       </x:c>
       <x:c r="B46" s="50"/>
       <x:c r="C46" s="50"/>
@@ -5024,8 +5024,7 @@
     </x:row>
     <x:row r="47" ht="20.649999618530273" customHeight="1">
       <x:c r="A47" s="48" t="str">
-        <x:f>"Campaigns expiring within 30 days: "&amp;SUM($E$10:$F$15)&amp;"."</x:f>
-        <x:v>Campaigns expiring within 30 days: 5.</x:v>
+        <x:v>Merchant offers are excluded from Dashboard KPIs and retained only as a count in each competitor sheet.</x:v>
       </x:c>
       <x:c r="B47" s="48"/>
       <x:c r="C47" s="48"/>
@@ -5058,8 +5057,8 @@
       <x:c r="N48" s="50"/>
     </x:row>
     <x:row r="51" ht="16.5">
-      <x:c r="A51" s="47" t="s">
-        <x:v>35</x:v>
+      <x:c r="A51" s="47" t="str">
+        <x:v>Social Media Activity — Last 14 Days</x:v>
       </x:c>
       <x:c r="B51" s="47"/>
       <x:c r="C51" s="47"/>
@@ -5077,203 +5076,179 @@
     </x:row>
     <x:row r="52" ht="20.649999618530273" customHeight="1"/>
     <x:row r="53" ht="28" customHeight="1">
-      <x:c r="A53" s="36" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B53" s="36" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C53" s="36" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D53" s="36" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E53" s="36" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F53" s="36" t="s">
-        <x:v>40</x:v>
+      <x:c r="A53" s="36" t="str">
+        <x:v>Competitor</x:v>
+      </x:c>
+      <x:c r="B53" s="36" t="str">
+        <x:v>Instagram</x:v>
+      </x:c>
+      <x:c r="C53" s="36" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="D53" s="36" t="str">
+        <x:v>Facebook</x:v>
+      </x:c>
+      <x:c r="E53" s="36" t="str">
+        <x:v>TikTok</x:v>
+      </x:c>
+      <x:c r="F53" s="36" t="str">
+        <x:v>Total Posts</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="18.649999618530273" customHeight="1">
-      <x:c r="A54" s="32" t="s">
-        <x:v>20</x:v>
+      <x:c r="A54" s="32" t="str">
+        <x:v>STC Bank</x:v>
       </x:c>
       <x:c r="B54" s="32" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$O$9:$O$500,"&lt;&gt;")</x:f>
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C54" s="32" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$P$9:$P$500,"&lt;&gt;")</x:f>
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D54" s="32" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$Q$9:$Q$500,"&lt;&gt;")</x:f>
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E54" s="32" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$R$9:$R$500,"&lt;&gt;")</x:f>
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F54" s="32" t="n">
-        <x:f>SUMPRODUCT(--('STC Bank'!$C$9:$C$500&lt;&gt;""),--('STC Bank'!$B$9:$B$500&lt;&gt;"Merchant"),--((--('STC Bank'!$O$9:$O$500&lt;&gt;"")+--('STC Bank'!$P$9:$P$500&lt;&gt;"")+--('STC Bank'!$Q$9:$Q$500&lt;&gt;"")+--('STC Bank'!$R$9:$R$500&lt;&gt;""))&gt;=2))</x:f>
-        <x:v>4</x:v>
+        <x:f>SUM(B54:E54)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="18.649999618530273" customHeight="1">
-      <x:c r="A55" s="32" t="s">
-        <x:v>21</x:v>
+      <x:c r="A55" s="32" t="str">
+        <x:v>barq</x:v>
       </x:c>
       <x:c r="B55" s="32" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$O$9:$O$499,"&lt;&gt;")</x:f>
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C55" s="32" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$P$9:$P$499,"&lt;&gt;")</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D55" s="32" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$Q$9:$Q$499,"&lt;&gt;")</x:f>
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E55" s="32" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$R$9:$R$499,"&lt;&gt;")</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F55" s="32" t="n">
-        <x:f>SUMPRODUCT(--(barq!$C$9:$C$499&lt;&gt;""),--(barq!$B$9:$B$499&lt;&gt;"Merchant"),--((--(barq!$O$9:$O$499&lt;&gt;"")+--(barq!$P$9:$P$499&lt;&gt;"")+--(barq!$Q$9:$Q$499&lt;&gt;"")+--(barq!$R$9:$R$499&lt;&gt;""))&gt;=2))</x:f>
-        <x:v>3</x:v>
+        <x:f>SUM(B55:E55)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="18.649999618530273" customHeight="1">
-      <x:c r="A56" s="32" t="s">
-        <x:v>22</x:v>
+      <x:c r="A56" s="32" t="str">
+        <x:v>Mobily Pay</x:v>
       </x:c>
       <x:c r="B56" s="32" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$O$9:$O$500,"&lt;&gt;")</x:f>
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C56" s="32" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$P$9:$P$500,"&lt;&gt;")</x:f>
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D56" s="32" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$Q$9:$Q$500,"&lt;&gt;")</x:f>
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E56" s="32" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$R$9:$R$500,"&lt;&gt;")</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F56" s="32" t="n">
-        <x:f>SUMPRODUCT(--('Mobily Pay'!$C$9:$C$500&lt;&gt;""),--('Mobily Pay'!$B$9:$B$500&lt;&gt;"Merchant"),--((--('Mobily Pay'!$O$9:$O$500&lt;&gt;"")+--('Mobily Pay'!$P$9:$P$500&lt;&gt;"")+--('Mobily Pay'!$Q$9:$Q$500&lt;&gt;"")+--('Mobily Pay'!$R$9:$R$500&lt;&gt;""))&gt;=2))</x:f>
-        <x:v>4</x:v>
+        <x:f>SUM(B56:E56)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="18.649999618530273" customHeight="1">
-      <x:c r="A57" s="32" t="s">
-        <x:v>23</x:v>
+      <x:c r="A57" s="32" t="str">
+        <x:v>tiqmo</x:v>
       </x:c>
       <x:c r="B57" s="32" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$O$9:$O$500,"&lt;&gt;")</x:f>
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C57" s="32" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$P$9:$P$500,"&lt;&gt;")</x:f>
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D57" s="32" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$Q$9:$Q$500,"&lt;&gt;")</x:f>
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E57" s="32" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$R$9:$R$500,"&lt;&gt;")</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F57" s="32" t="n">
-        <x:f>SUMPRODUCT(--(tiqmo!$C$9:$C$500&lt;&gt;""),--(tiqmo!$B$9:$B$500&lt;&gt;"Merchant"),--((--(tiqmo!$O$9:$O$500&lt;&gt;"")+--(tiqmo!$P$9:$P$500&lt;&gt;"")+--(tiqmo!$Q$9:$Q$500&lt;&gt;"")+--(tiqmo!$R$9:$R$500&lt;&gt;""))&gt;=2))</x:f>
-        <x:v>5</x:v>
+        <x:f>SUM(B57:E57)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="18.649999618530273" customHeight="1">
-      <x:c r="A58" s="32" t="s">
-        <x:v>24</x:v>
+      <x:c r="A58" s="32" t="str">
+        <x:v>urpay</x:v>
       </x:c>
       <x:c r="B58" s="32" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$O$9:$O$500,"&lt;&gt;")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C58" s="32" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$P$9:$P$500,"&lt;&gt;")</x:f>
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D58" s="32" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$Q$9:$Q$500,"&lt;&gt;")</x:f>
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E58" s="32" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$R$9:$R$500,"&lt;&gt;")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F58" s="32" t="n">
-        <x:f>SUMPRODUCT(--(urpay!$C$9:$C$500&lt;&gt;""),--(urpay!$B$9:$B$500&lt;&gt;"Merchant"),--((--(urpay!$O$9:$O$500&lt;&gt;"")+--(urpay!$P$9:$P$500&lt;&gt;"")+--(urpay!$Q$9:$Q$500&lt;&gt;"")+--(urpay!$R$9:$R$500&lt;&gt;""))&gt;=2))</x:f>
-        <x:v>1</x:v>
+        <x:f>SUM(B58:E58)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="18.649999618530273" customHeight="1">
-      <x:c r="A59" s="32" t="s">
-        <x:v>25</x:v>
+      <x:c r="A59" s="32" t="str">
+        <x:v>alinma pay</x:v>
       </x:c>
       <x:c r="B59" s="32" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$O$9:$O$500,"&lt;&gt;")</x:f>
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C59" s="32" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$P$9:$P$500,"&lt;&gt;")</x:f>
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D59" s="32" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$Q$9:$Q$500,"&lt;&gt;")</x:f>
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E59" s="32" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$R$9:$R$500,"&lt;&gt;")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F59" s="32" t="n">
-        <x:f>SUMPRODUCT(--('alinma pay'!$C$9:$C$500&lt;&gt;""),--('alinma pay'!$B$9:$B$500&lt;&gt;"Merchant"),--((--('alinma pay'!$O$9:$O$500&lt;&gt;"")+--('alinma pay'!$P$9:$P$500&lt;&gt;"")+--('alinma pay'!$Q$9:$Q$500&lt;&gt;"")+--('alinma pay'!$R$9:$R$500&lt;&gt;""))&gt;=2))</x:f>
-        <x:v>3</x:v>
+        <x:f>SUM(B59:E59)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" s="37" t="s">
-        <x:v>30</x:v>
+      <x:c r="A60" s="37" t="str">
+        <x:v>Market Total</x:v>
       </x:c>
       <x:c r="B60" s="37" t="n">
         <x:f t="shared" ref="B60:F60" si="2">SUM(B54:B59)</x:f>
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C60" s="37">
-        <x:f t="shared" si="2"/>
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D60" s="37">
-        <x:f t="shared" si="2"/>
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E60" s="37">
-        <x:f t="shared" si="2"/>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F60" s="37">
-        <x:f t="shared" si="2"/>
-        <x:v>18</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C60" s="37" t="n">
+        <x:f t="shared" si="2">SUM(C54:C59)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D60" s="37" t="n">
+        <x:f t="shared" si="2">SUM(D54:D59)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E60" s="37" t="n">
+        <x:f t="shared" si="2">SUM(E54:E59)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F60" s="37" t="n">
+        <x:f t="shared" si="2">SUM(F54:F59)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15.5">
-      <x:c r="A63" s="51" t="s">
-        <x:v>41</x:v>
+      <x:c r="A63" s="51" t="str">
+        <x:v>Reporting Convention and Rationale</x:v>
       </x:c>
       <x:c r="B63" s="51"/>
       <x:c r="C63" s="51"/>
@@ -5290,8 +5265,8 @@
       <x:c r="N63" s="51"/>
     </x:row>
     <x:row r="64" ht="22.649999618530273" customHeight="1">
-      <x:c r="A64" s="50" t="s">
-        <x:v>42</x:v>
+      <x:c r="A64" s="50" t="str">
+        <x:v>• Dashboard campaign KPIs include active approved campaigns only; expired campaigns are excluded.</x:v>
       </x:c>
       <x:c r="B64" s="50"/>
       <x:c r="C64" s="50"/>
@@ -5308,8 +5283,8 @@
       <x:c r="N64" s="50"/>
     </x:row>
     <x:row r="65" ht="22.649999618530273" customHeight="1">
-      <x:c r="A65" s="48" t="s">
-        <x:v>43</x:v>
+      <x:c r="A65" s="48" t="str">
+        <x:v>• Merchant offers are excluded from Dashboard KPIs and appear only as a count in each competitor sheet.</x:v>
       </x:c>
       <x:c r="B65" s="48"/>
       <x:c r="C65" s="48"/>
@@ -5326,8 +5301,8 @@
       <x:c r="N65" s="48"/>
     </x:row>
     <x:row r="66" ht="22.649999618530273" customHeight="1">
-      <x:c r="A66" s="61" t="s">
-        <x:v>44</x:v>
+      <x:c r="A66" s="61" t="str">
+        <x:v>• Social Media Activity counts unique direct official posts published within the latest 14-day window.</x:v>
       </x:c>
       <x:c r="B66" s="50"/>
       <x:c r="C66" s="50"/>
@@ -5344,8 +5319,8 @@
       <x:c r="N66" s="50"/>
     </x:row>
     <x:row r="67" ht="22.649999618530273" customHeight="1">
-      <x:c r="A67" s="49" t="s">
-        <x:v>45</x:v>
+      <x:c r="A67" s="49" t="str">
+        <x:v>• Remittance is the priority target category and is highlighted in blue throughout the workbook.</x:v>
       </x:c>
       <x:c r="B67" s="49"/>
       <x:c r="C67" s="49"/>
@@ -5556,7 +5531,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d9b1feeed504ee7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38ecfa3cc6644f9d"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -5675,7 +5650,7 @@
   <x:sheetData>
     <x:row r="1" ht="22.649999618530273" customHeight="1">
       <x:c r="A1" s="52" t="s">
-        <x:v>46</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B1" s="52"/>
       <x:c r="C1" s="52"/>
@@ -5698,8 +5673,8 @@
       <x:c r="T1" s="52"/>
     </x:row>
     <x:row r="2" ht="21.399999618530273" customHeight="1">
-      <x:c r="A2" s="56" t="s">
-        <x:v>47</x:v>
+      <x:c r="A2" s="56" t="str">
+        <x:v>Active approved campaigns only. Expired campaigns are excluded. Merchant offers are shown as a count only.</x:v>
       </x:c>
       <x:c r="B2" s="56"/>
       <x:c r="C2" s="56"/>
@@ -5713,7 +5688,7 @@
       <x:c r="K2" s="56"/>
       <x:c r="L2" s="56"/>
       <x:c r="M2" s="57" t="s">
-        <x:v>48</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N2" s="57"/>
       <x:c r="O2" s="57"/>
@@ -5725,32 +5700,38 @@
       <x:c r="U2" s="57"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="41" t="s">
-        <x:v>49</x:v>
+      <x:c r="A4" s="41" t="str">
+        <x:v>Active Campaigns</x:v>
       </x:c>
       <x:c r="B4" s="41"/>
       <x:c r="C4" s="41"/>
-      <x:c r="D4" s="41"/>
-      <x:c r="E4" s="41" t="s">
-        <x:v>4</x:v>
+      <x:c r="D4" s="41" t="str">
+        <x:v>End Date Not Stated</x:v>
+      </x:c>
+      <x:c r="E4" s="41" t="str">
+        <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="F4" s="41"/>
-      <x:c r="G4" s="41"/>
+      <x:c r="G4" s="41" t="str">
+        <x:v>Remittance Campaigns</x:v>
+      </x:c>
       <x:c r="H4" s="41"/>
-      <x:c r="I4" s="43" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="J4" s="43"/>
+      <x:c r="I4" s="43" t="str">
+        <x:v>Remittance Campaigns</x:v>
+      </x:c>
+      <x:c r="J4" s="43" t="str">
+        <x:v>Expiring ≤30d</x:v>
+      </x:c>
       <x:c r="K4" s="43"/>
       <x:c r="L4" s="43"/>
-      <x:c r="M4" s="44" t="s">
-        <x:v>6</x:v>
+      <x:c r="M4" s="44" t="str">
+        <x:v>Merchant Offers (Count Only): 0</x:v>
       </x:c>
       <x:c r="N4" s="44"/>
       <x:c r="O4" s="44"/>
       <x:c r="P4" s="44"/>
-      <x:c r="Q4" s="41" t="s">
-        <x:v>7</x:v>
+      <x:c r="Q4" s="41" t="str">
+        <x:v>Expiring ≤30d</x:v>
       </x:c>
       <x:c r="R4" s="41"/>
       <x:c r="S4" s="41"/>
@@ -5758,36 +5739,44 @@
     </x:row>
     <x:row r="5" ht="23">
       <x:c r="A5" s="53" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant")</x:f>
-        <x:v>6</x:v>
+        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;")</x:f>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="53"/>
       <x:c r="C5" s="53"/>
-      <x:c r="D5" s="53"/>
+      <x:c r="D5" s="53" t="n">
+        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$I$9:$I$500,"End Date Not Stated")</x:f>
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E5" s="53" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>5</x:v>
+        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$I$9:$I$500,"End Date Not Stated")</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F5" s="53"/>
-      <x:c r="G5" s="53"/>
+      <x:c r="G5" s="53" t="n">
+        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"Remittance")</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="H5" s="53"/>
       <x:c r="I5" s="54" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"&lt;&gt;Expired",'STC Bank'!$B$9:$B$500,"Remittance")</x:f>
+        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"Remittance")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J5" s="54"/>
+      <x:c r="J5" s="54" t="n">
+        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$I$9:$I$500,"Expiring ≤7 Days")+COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="K5" s="54"/>
       <x:c r="L5" s="54"/>
       <x:c r="M5" s="55" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"Merchant",'STC Bank'!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N5" s="55"/>
       <x:c r="O5" s="55"/>
       <x:c r="P5" s="55"/>
       <x:c r="Q5" s="53" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"Expiring ≤7 Days")+COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"&lt;&gt;Merchant",'STC Bank'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
-        <x:v>3</x:v>
+        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$I$9:$I$500,"Expiring ≤7 Days")+COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="R5" s="53"/>
       <x:c r="S5" s="53"/>
@@ -5795,67 +5784,67 @@
     </x:row>
     <x:row r="8" ht="30.649999618530273" customHeight="1">
       <x:c r="A8" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H8" s="3" t="s">
-        <x:v>56</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I8" s="3" t="s">
-        <x:v>57</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="J8" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K8" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L8" s="3" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="M8" s="3" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="N8" s="3" t="s">
-        <x:v>62</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O8" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="P8" s="3" t="s">
-        <x:v>64</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="Q8" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
-        <x:v>66</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="S8" s="3" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="T8" s="3" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="U8" s="34" t="s">
-        <x:v>69</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="T8" s="3" t="str">
+        <x:v>Social Post Count</x:v>
+      </x:c>
+      <x:c r="U8" s="34" t="str">
+        <x:v>Published Platforms</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="46.650001525878906" customHeight="1">
@@ -5864,13 +5853,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>70</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E9" s="5"/>
       <x:c r="F9" s="5">
@@ -5881,39 +5870,39 @@
       </x:c>
       <x:c r="H9" s="7" t="n">
         <x:f t="shared" ref="H9:H53" si="1">IF(OR(C9="",G9=""),"",G9-TODAY())</x:f>
-        <x:v>25</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I9" s="6" t="str">
         <x:f t="shared" ref="I9:I53" si="2">IF(C9="","",IF(G9="","End Date Not Stated",IF(G9&lt;TODAY(),"Expired",IF(G9&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G9&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
-        <x:v>Expiring 8–30 Days</x:v>
+        <x:v>Expiring ≤7 Days</x:v>
       </x:c>
       <x:c r="J9" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K9" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L9" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:f>IF(C9="","",IF(N9&lt;&gt;"",N9,IF(O9&lt;&gt;"",O9,IF(P9&lt;&gt;"",P9,IF(Q9&lt;&gt;"",Q9,IF(R9&lt;&gt;"",R9,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/international-purchases-with-0-fees</x:v>
       </x:c>
       <x:c r="N9" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="O9" s="4" t="s">
-        <x:v>76</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="P9" s="4" t="s">
-        <x:v>77</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="Q9" s="63" t="s">
-        <x:v>78</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R9" s="63" t="s">
-        <x:v>79</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="S9" s="4" t="str">
         <x:v>0% international POS fee campaign is valid from 17 May to 31 August 2026. International e-commerce purchases are excluded; free withdrawals apply to international ATMs. Digital-wallet purchases are eligible under the official terms.</x:v>
@@ -5932,13 +5921,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E10" s="5"/>
       <x:c r="F10" s="5">
@@ -5949,36 +5938,36 @@
       </x:c>
       <x:c r="H10" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C10="",G10=""),"",G10-TODAY())</x:f>
-        <x:v>28</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I10" s="6" t="str">
         <x:f t="shared" si="2">IF(C10="","",IF(G10="","End Date Not Stated",IF(G10&lt;TODAY(),"Expired",IF(G10&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G10&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expiring 8–30 Days</x:v>
       </x:c>
       <x:c r="J10" s="4" t="s">
-        <x:v>82</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="K10" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="L10" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="M10" s="9" t="str">
         <x:f>IF(C10="","",IF(N10&lt;&gt;"",N10,IF(O10&lt;&gt;"",O10,IF(P10&lt;&gt;"",P10,IF(Q10&lt;&gt;"",Q10,IF(R10&lt;&gt;"",R10,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/international-purchases-with-0-fees</x:v>
       </x:c>
       <x:c r="N10" s="63" t="s">
-        <x:v>75</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="O10" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="P10" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="Q10" s="63" t="s">
-        <x:v>86</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="R10" s="4"/>
       <x:c r="S10" s="4" t="str">
@@ -5998,13 +5987,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5"/>
@@ -6013,27 +6002,27 @@
       </x:c>
       <x:c r="H11" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C11="",G11=""),"",G11-TODAY())</x:f>
-        <x:v>14</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="I11" s="6" t="str">
         <x:f t="shared" si="2">IF(C11="","",IF(G11="","End Date Not Stated",IF(G11&lt;TODAY(),"Expired",IF(G11&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G11&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
-        <x:v>Expiring 8–30 Days</x:v>
+        <x:v>Expired</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K11" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="L11" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:f t="shared" ref="M11:M53" si="4">IF(C11="","",IF(N11&lt;&gt;"",N11,IF(O11&lt;&gt;"",O11,IF(P11&lt;&gt;"",P11,IF(Q11&lt;&gt;"",Q11,IF(R11&lt;&gt;"",R11,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/visa_cards_rewards</x:v>
       </x:c>
       <x:c r="N11" s="63" t="s">
-        <x:v>91</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O11" s="4"/>
       <x:c r="P11" s="4"/>
@@ -6056,13 +6045,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E12" s="5">
         <x:v>46217</x:v>
@@ -6077,13 +6066,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J12" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K12" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L12" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
         <x:f t="shared" si="4">IF(C12="","",IF(N12&lt;&gt;"",N12,IF(O12&lt;&gt;"",O12,IF(P12&lt;&gt;"",P12,IF(Q12&lt;&gt;"",Q12,IF(R12&lt;&gt;"",R12,""))))))</x:f>
@@ -6091,17 +6080,17 @@
       </x:c>
       <x:c r="N12" s="4"/>
       <x:c r="O12" s="63" t="s">
-        <x:v>97</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="P12" s="63" t="s">
-        <x:v>98</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q12" s="63" t="s">
-        <x:v>99</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="R12" s="4"/>
       <x:c r="S12" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="T12" s="5" t="n">
         <x:v>46240</x:v>
@@ -6117,13 +6106,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>102</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>103</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E13" s="5"/>
       <x:c r="F13" s="5"/>
@@ -6132,27 +6121,27 @@
       </x:c>
       <x:c r="H13" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C13="",G13=""),"",G13-TODAY())</x:f>
-        <x:v>512</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="I13" s="6" t="str">
         <x:f t="shared" si="2">IF(C13="","",IF(G13="","End Date Not Stated",IF(G13&lt;TODAY(),"Expired",IF(G13&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G13&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J13" s="4" t="s">
-        <x:v>104</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K13" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L13" s="4" t="s">
-        <x:v>106</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M13" s="9" t="str">
         <x:f t="shared" si="4">IF(C13="","",IF(N13&lt;&gt;"",N13,IF(O13&lt;&gt;"",O13,IF(P13&lt;&gt;"",P13,IF(Q13&lt;&gt;"",Q13,IF(R13&lt;&gt;"",R13,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/almatar-offer</x:v>
       </x:c>
       <x:c r="N13" s="4" t="s">
-        <x:v>107</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="O13" s="4"/>
       <x:c r="P13" s="4"/>
@@ -6175,13 +6164,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B14" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C14" s="4" t="s">
-        <x:v>108</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>109</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E14" s="5"/>
       <x:c r="F14" s="5"/>
@@ -6190,27 +6179,27 @@
       </x:c>
       <x:c r="H14" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C14="",G14=""),"",G14-TODAY())</x:f>
-        <x:v>-6</x:v>
+        <x:v>-26</x:v>
       </x:c>
       <x:c r="I14" s="6" t="str">
         <x:f t="shared" si="2">IF(C14="","",IF(G14="","End Date Not Stated",IF(G14&lt;TODAY(),"Expired",IF(G14&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G14&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J14" s="4" t="s">
-        <x:v>110</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K14" s="4" t="s">
-        <x:v>111</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="L14" s="4" t="s">
-        <x:v>112</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="M14" s="9" t="str">
         <x:f t="shared" si="4">IF(C14="","",IF(N14&lt;&gt;"",N14,IF(O14&lt;&gt;"",O14,IF(P14&lt;&gt;"",P14,IF(Q14&lt;&gt;"",Q14,IF(R14&lt;&gt;"",R14,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/whites-offer</x:v>
       </x:c>
       <x:c r="N14" s="4" t="s">
-        <x:v>113</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="O14" s="4"/>
       <x:c r="P14" s="4"/>
@@ -6233,13 +6222,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B15" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C15" s="4" t="s">
-        <x:v>114</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>115</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E15" s="5"/>
       <x:c r="F15" s="5"/>
@@ -6248,27 +6237,27 @@
       </x:c>
       <x:c r="H15" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C15="",G15=""),"",G15-TODAY())</x:f>
-        <x:v>-4</x:v>
+        <x:v>-24</x:v>
       </x:c>
       <x:c r="I15" s="6" t="str">
         <x:f t="shared" si="2">IF(C15="","",IF(G15="","End Date Not Stated",IF(G15&lt;TODAY(),"Expired",IF(G15&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G15&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J15" s="4" t="s">
-        <x:v>116</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K15" s="4" t="s">
-        <x:v>117</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="L15" s="4" t="s">
-        <x:v>112</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="M15" s="9" t="str">
         <x:f t="shared" si="4">IF(C15="","",IF(N15&lt;&gt;"",N15,IF(O15&lt;&gt;"",O15,IF(P15&lt;&gt;"",P15,IF(Q15&lt;&gt;"",Q15,IF(R15&lt;&gt;"",R15,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/huawei</x:v>
       </x:c>
       <x:c r="N15" s="4" t="s">
-        <x:v>118</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="O15" s="4"/>
       <x:c r="P15" s="4"/>
@@ -6291,13 +6280,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C16" s="4" t="s">
-        <x:v>119</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D16" s="4" t="s">
-        <x:v>120</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E16" s="5"/>
       <x:c r="F16" s="5">
@@ -6308,27 +6297,27 @@
       </x:c>
       <x:c r="H16" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C16="",G16=""),"",G16-TODAY())</x:f>
-        <x:v>19</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="I16" s="6" t="str">
         <x:f t="shared" si="2">IF(C16="","",IF(G16="","End Date Not Stated",IF(G16&lt;TODAY(),"Expired",IF(G16&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G16&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
-        <x:v>Expiring 8–30 Days</x:v>
+        <x:v>Expired</x:v>
       </x:c>
       <x:c r="J16" s="4" t="s">
-        <x:v>121</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K16" s="4" t="s">
-        <x:v>122</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="L16" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="M16" s="9" t="str">
         <x:f t="shared" si="4">IF(C16="","",IF(N16&lt;&gt;"",N16,IF(O16&lt;&gt;"",O16,IF(P16&lt;&gt;"",P16,IF(Q16&lt;&gt;"",Q16,IF(R16&lt;&gt;"",R16,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/loca</x:v>
       </x:c>
       <x:c r="N16" s="4" t="s">
-        <x:v>124</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="O16" s="4"/>
       <x:c r="P16" s="4"/>
@@ -6351,13 +6340,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B17" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C17" s="4" t="s">
-        <x:v>125</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D17" s="4" t="s">
-        <x:v>126</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E17" s="5"/>
       <x:c r="F17" s="5"/>
@@ -6366,27 +6355,27 @@
       </x:c>
       <x:c r="H17" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C17="",G17=""),"",G17-TODAY())</x:f>
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I17" s="6" t="str">
         <x:f t="shared" si="2">IF(C17="","",IF(G17="","End Date Not Stated",IF(G17&lt;TODAY(),"Expired",IF(G17&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G17&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J17" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K17" s="4" t="s">
-        <x:v>122</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="L17" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="M17" s="9" t="str">
         <x:f t="shared" si="4">IF(C17="","",IF(N17&lt;&gt;"",N17,IF(O17&lt;&gt;"",O17,IF(P17&lt;&gt;"",P17,IF(Q17&lt;&gt;"",Q17,IF(R17&lt;&gt;"",R17,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/canton-offer</x:v>
       </x:c>
       <x:c r="N17" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="O17" s="4"/>
       <x:c r="P17" s="4"/>
@@ -6409,13 +6398,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B18" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C18" s="4" t="s">
-        <x:v>129</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D18" s="4" t="s">
-        <x:v>130</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E18" s="5"/>
       <x:c r="F18" s="5"/>
@@ -6424,27 +6413,27 @@
       </x:c>
       <x:c r="H18" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C18="",G18=""),"",G18-TODAY())</x:f>
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I18" s="6" t="str">
         <x:f t="shared" si="2">IF(C18="","",IF(G18="","End Date Not Stated",IF(G18&lt;TODAY(),"Expired",IF(G18&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G18&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J18" s="4" t="s">
-        <x:v>131</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K18" s="4" t="s">
-        <x:v>132</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="L18" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="M18" s="9" t="str">
         <x:f t="shared" si="4">IF(C18="","",IF(N18&lt;&gt;"",N18,IF(O18&lt;&gt;"",O18,IF(P18&lt;&gt;"",P18,IF(Q18&lt;&gt;"",Q18,IF(R18&lt;&gt;"",R18,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/boost-your-health</x:v>
       </x:c>
       <x:c r="N18" s="4" t="s">
-        <x:v>133</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="O18" s="4"/>
       <x:c r="P18" s="4"/>
@@ -6467,13 +6456,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B19" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C19" s="4" t="s">
-        <x:v>134</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D19" s="4" t="s">
-        <x:v>135</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E19" s="5"/>
       <x:c r="F19" s="5"/>
@@ -6482,27 +6471,27 @@
       </x:c>
       <x:c r="H19" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C19="",G19=""),"",G19-TODAY())</x:f>
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I19" s="6" t="str">
         <x:f t="shared" si="2">IF(C19="","",IF(G19="","End Date Not Stated",IF(G19&lt;TODAY(),"Expired",IF(G19&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G19&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J19" s="4" t="s">
-        <x:v>136</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K19" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="L19" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="M19" s="9" t="str">
         <x:f t="shared" si="4">IF(C19="","",IF(N19&lt;&gt;"",N19,IF(O19&lt;&gt;"",O19,IF(P19&lt;&gt;"",P19,IF(Q19&lt;&gt;"",Q19,IF(R19&lt;&gt;"",R19,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/shop-workout-and-save-with-10-off-on-gosport</x:v>
       </x:c>
       <x:c r="N19" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="O19" s="4"/>
       <x:c r="P19" s="4"/>
@@ -6525,13 +6514,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B20" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C20" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D20" s="4" t="s">
-        <x:v>140</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E20" s="5"/>
       <x:c r="F20" s="5"/>
@@ -6540,27 +6529,27 @@
       </x:c>
       <x:c r="H20" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C20="",G20=""),"",G20-TODAY())</x:f>
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I20" s="6" t="str">
         <x:f t="shared" si="2">IF(C20="","",IF(G20="","End Date Not Stated",IF(G20&lt;TODAY(),"Expired",IF(G20&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G20&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J20" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K20" s="4" t="s">
-        <x:v>142</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="L20" s="4" t="s">
-        <x:v>143</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M20" s="9" t="str">
         <x:f t="shared" si="4">IF(C20="","",IF(N20&lt;&gt;"",N20,IF(O20&lt;&gt;"",O20,IF(P20&lt;&gt;"",P20,IF(Q20&lt;&gt;"",Q20,IF(R20&lt;&gt;"",R20,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/iherb-offer</x:v>
       </x:c>
       <x:c r="N20" s="4" t="s">
-        <x:v>144</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="O20" s="4"/>
       <x:c r="P20" s="4"/>
@@ -6583,13 +6572,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B21" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C21" s="4" t="s">
-        <x:v>145</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D21" s="4" t="s">
-        <x:v>146</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E21" s="5"/>
       <x:c r="F21" s="5"/>
@@ -6598,27 +6587,27 @@
       </x:c>
       <x:c r="H21" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C21="",G21=""),"",G21-TODAY())</x:f>
-        <x:v>512</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="I21" s="6" t="str">
         <x:f t="shared" si="2">IF(C21="","",IF(G21="","End Date Not Stated",IF(G21&lt;TODAY(),"Expired",IF(G21&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G21&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J21" s="4" t="s">
-        <x:v>147</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="K21" s="4" t="s">
-        <x:v>148</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="L21" s="4" t="s">
-        <x:v>106</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M21" s="9" t="str">
         <x:f t="shared" si="4">IF(C21="","",IF(N21&lt;&gt;"",N21,IF(O21&lt;&gt;"",O21,IF(P21&lt;&gt;"",P21,IF(Q21&lt;&gt;"",Q21,IF(R21&lt;&gt;"",R21,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/alothaim-entertainment</x:v>
       </x:c>
       <x:c r="N21" s="4" t="s">
-        <x:v>149</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="O21" s="4"/>
       <x:c r="P21" s="4"/>
@@ -6641,13 +6630,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B22" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C22" s="4" t="s">
-        <x:v>150</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D22" s="4" t="s">
-        <x:v>151</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E22" s="5"/>
       <x:c r="F22" s="5"/>
@@ -6656,27 +6645,27 @@
       </x:c>
       <x:c r="H22" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C22="",G22=""),"",G22-TODAY())</x:f>
-        <x:v>512</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="I22" s="6" t="str">
         <x:f t="shared" si="2">IF(C22="","",IF(G22="","End Date Not Stated",IF(G22&lt;TODAY(),"Expired",IF(G22&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G22&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J22" s="4" t="s">
-        <x:v>152</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="K22" s="4" t="s">
-        <x:v>153</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="L22" s="4" t="s">
-        <x:v>154</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="M22" s="9" t="str">
         <x:f t="shared" si="4">IF(C22="","",IF(N22&lt;&gt;"",N22,IF(O22&lt;&gt;"",O22,IF(P22&lt;&gt;"",P22,IF(Q22&lt;&gt;"",Q22,IF(R22&lt;&gt;"",R22,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/yelo</x:v>
       </x:c>
       <x:c r="N22" s="4" t="s">
-        <x:v>155</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="O22" s="4"/>
       <x:c r="P22" s="4"/>
@@ -6699,13 +6688,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B23" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C23" s="4" t="s">
-        <x:v>156</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D23" s="4" t="s">
-        <x:v>157</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E23" s="5"/>
       <x:c r="F23" s="5">
@@ -6716,42 +6705,42 @@
       </x:c>
       <x:c r="H23" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C23="",G23=""),"",G23-TODAY())</x:f>
-        <x:v>-18</x:v>
+        <x:v>-38</x:v>
       </x:c>
       <x:c r="I23" s="6" t="str">
         <x:f t="shared" si="2">IF(C23="","",IF(G23="","End Date Not Stated",IF(G23&lt;TODAY(),"Expired",IF(G23&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G23&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J23" s="4" t="s">
-        <x:v>158</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K23" s="4" t="s">
-        <x:v>159</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="L23" s="4" t="s">
-        <x:v>160</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="M23" s="9" t="str">
         <x:f t="shared" si="4">IF(C23="","",IF(N23&lt;&gt;"",N23,IF(O23&lt;&gt;"",O23,IF(P23&lt;&gt;"",P23,IF(Q23&lt;&gt;"",Q23,IF(R23&lt;&gt;"",R23,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/stcbank-championship</x:v>
       </x:c>
       <x:c r="N23" s="4" t="s">
-        <x:v>161</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="O23" s="4" t="s">
-        <x:v>162</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="P23" s="4" t="s">
-        <x:v>163</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="Q23" s="63" t="s">
-        <x:v>164</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="R23" s="63" t="s">
-        <x:v>165</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="S23" s="4" t="s">
-        <x:v>166</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="T23" s="5" t="n">
         <x:v>46240</x:v>
@@ -6782,7 +6771,7 @@
       </x:c>
       <x:c r="H24" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C24="",G24=""),"",G24-TODAY())</x:f>
-        <x:v>57</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I24" s="6" t="str">
         <x:f t="shared" si="2">IF(C24="","",IF(G24="","End Date Not Stated",IF(G24&lt;TODAY(),"Expired",IF(G24&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G24&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
@@ -7858,7 +7847,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b570c03836c4987"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf47724ef1e6e477c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7888,7 +7877,7 @@
   <x:sheetData>
     <x:row r="1" ht="22.649999618530273" customHeight="1">
       <x:c r="A1" s="52" t="s">
-        <x:v>167</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B1" s="52"/>
       <x:c r="C1" s="52"/>
@@ -7911,8 +7900,8 @@
       <x:c r="T1" s="52"/>
     </x:row>
     <x:row r="2" ht="21.399999618530273" customHeight="1">
-      <x:c r="A2" s="56" t="s">
-        <x:v>47</x:v>
+      <x:c r="A2" s="56" t="str">
+        <x:v>Active approved campaigns only. Expired campaigns are excluded. Merchant offers are shown as a count only.</x:v>
       </x:c>
       <x:c r="B2" s="56"/>
       <x:c r="C2" s="56"/>
@@ -7926,7 +7915,7 @@
       <x:c r="K2" s="56"/>
       <x:c r="L2" s="56"/>
       <x:c r="M2" s="57" t="s">
-        <x:v>48</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N2" s="57"/>
       <x:c r="O2" s="57"/>
@@ -7938,32 +7927,38 @@
       <x:c r="U2" s="57"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="41" t="s">
-        <x:v>49</x:v>
+      <x:c r="A4" s="41" t="str">
+        <x:v>Active Campaigns</x:v>
       </x:c>
       <x:c r="B4" s="41"/>
       <x:c r="C4" s="41"/>
-      <x:c r="D4" s="41"/>
-      <x:c r="E4" s="41" t="s">
-        <x:v>4</x:v>
+      <x:c r="D4" s="41" t="str">
+        <x:v>End Date Not Stated</x:v>
+      </x:c>
+      <x:c r="E4" s="41" t="str">
+        <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="F4" s="41"/>
-      <x:c r="G4" s="41"/>
+      <x:c r="G4" s="41" t="str">
+        <x:v>Remittance Campaigns</x:v>
+      </x:c>
       <x:c r="H4" s="41"/>
-      <x:c r="I4" s="43" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="J4" s="43"/>
+      <x:c r="I4" s="43" t="str">
+        <x:v>Remittance Campaigns</x:v>
+      </x:c>
+      <x:c r="J4" s="43" t="str">
+        <x:v>Expiring ≤30d</x:v>
+      </x:c>
       <x:c r="K4" s="43"/>
       <x:c r="L4" s="43"/>
-      <x:c r="M4" s="44" t="s">
-        <x:v>6</x:v>
+      <x:c r="M4" s="44" t="str">
+        <x:v>Merchant Offers (Count Only): 0</x:v>
       </x:c>
       <x:c r="N4" s="44"/>
       <x:c r="O4" s="44"/>
       <x:c r="P4" s="44"/>
-      <x:c r="Q4" s="41" t="s">
-        <x:v>7</x:v>
+      <x:c r="Q4" s="41" t="str">
+        <x:v>Expiring ≤30d</x:v>
       </x:c>
       <x:c r="R4" s="41"/>
       <x:c r="S4" s="41"/>
@@ -7971,35 +7966,43 @@
     </x:row>
     <x:row r="5" ht="23">
       <x:c r="A5" s="53" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant")</x:f>
-        <x:v>5</x:v>
+        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$M$9:$M$500,"&lt;&gt;")</x:f>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B5" s="53"/>
       <x:c r="C5" s="53"/>
-      <x:c r="D5" s="53"/>
+      <x:c r="D5" s="53" t="n">
+        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$I$9:$I$500,"End Date Not Stated")</x:f>
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="E5" s="53" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"&lt;&gt;Expired")</x:f>
-        <x:v>5</x:v>
+        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$I$9:$I$500,"End Date Not Stated")</x:f>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F5" s="53"/>
-      <x:c r="G5" s="53"/>
+      <x:c r="G5" s="53" t="n">
+        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$B$9:$B$500,"Remittance")</x:f>
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="H5" s="53"/>
       <x:c r="I5" s="54" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"&lt;&gt;Expired",barq!$B$9:$B$499,"Remittance")</x:f>
+        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$B$9:$B$500,"Remittance")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J5" s="54"/>
+      <x:c r="J5" s="54" t="n">
+        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$I$9:$I$500,"Expiring ≤7 Days")+COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="K5" s="54"/>
       <x:c r="L5" s="54"/>
       <x:c r="M5" s="55" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"Merchant",barq!$I$9:$I$499,"&lt;&gt;Expired")</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N5" s="55"/>
       <x:c r="O5" s="55"/>
       <x:c r="P5" s="55"/>
       <x:c r="Q5" s="53" t="n">
-        <x:f>COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"Expiring ≤7 Days")+COUNTIFS(barq!$C$9:$C$499,"&lt;&gt;",barq!$M$9:$M$499,"&lt;&gt;",barq!$B$9:$B$499,"&lt;&gt;Merchant",barq!$I$9:$I$499,"Expiring 8–30 Days")</x:f>
+        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$I$9:$I$500,"Expiring ≤7 Days")+COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="R5" s="53"/>
@@ -8008,67 +8011,67 @@
     </x:row>
     <x:row r="8" ht="30.649999618530273" customHeight="1">
       <x:c r="A8" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H8" s="3" t="s">
-        <x:v>56</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I8" s="3" t="s">
-        <x:v>57</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="J8" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K8" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L8" s="3" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="M8" s="3" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="N8" s="3" t="s">
-        <x:v>62</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O8" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="P8" s="3" t="s">
-        <x:v>64</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="Q8" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
-        <x:v>66</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="S8" s="3" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="T8" s="3" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="U8" s="34" t="s">
-        <x:v>69</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="T8" s="3" t="str">
+        <x:v>Social Post Count</x:v>
+      </x:c>
+      <x:c r="U8" s="34" t="str">
+        <x:v>Published Platforms</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="46.650001525878906" customHeight="1">
@@ -8077,13 +8080,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>168</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>169</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E9" s="5"/>
       <x:c r="F9" s="5"/>
@@ -8096,13 +8099,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J9" s="4" t="s">
-        <x:v>170</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="K9" s="4" t="s">
-        <x:v>171</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="L9" s="4" t="s">
-        <x:v>172</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:f>IF(C9="","",IF(N9&lt;&gt;"",N9,IF(O9&lt;&gt;"",O9,IF(P9&lt;&gt;"",P9,IF(Q9&lt;&gt;"",Q9,IF(R9&lt;&gt;"",R9,""))))))</x:f>
@@ -8110,15 +8113,15 @@
       </x:c>
       <x:c r="N9" s="4"/>
       <x:c r="O9" s="63" t="s">
-        <x:v>173</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="P9" s="4"/>
       <x:c r="Q9" s="63" t="s">
-        <x:v>174</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="R9" s="4"/>
       <x:c r="S9" s="4" t="s">
-        <x:v>175</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="T9" s="5" t="n">
         <x:v>46240</x:v>
@@ -8134,13 +8137,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>176</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E10" s="5"/>
       <x:c r="F10" s="5"/>
@@ -8153,13 +8156,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J10" s="4" t="s">
-        <x:v>178</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="K10" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="L10" s="4" t="s">
-        <x:v>180</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="M10" s="9" t="str">
         <x:f t="shared" ref="M10:M42" si="4">IF(C10="","",IF(N10&lt;&gt;"",N10,IF(O10&lt;&gt;"",O10,IF(P10&lt;&gt;"",P10,IF(Q10&lt;&gt;"",Q10,IF(R10&lt;&gt;"",R10,""))))))</x:f>
@@ -8169,11 +8172,11 @@
       <x:c r="O10" s="4"/>
       <x:c r="P10" s="4"/>
       <x:c r="Q10" s="63" t="s">
-        <x:v>181</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="R10" s="4"/>
       <x:c r="S10" s="4" t="s">
-        <x:v>175</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="T10" s="5" t="n">
         <x:v>46240</x:v>
@@ -8189,13 +8192,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
-        <x:v>182</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>183</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5"/>
@@ -8208,13 +8211,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
-        <x:v>104</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K11" s="4" t="s">
-        <x:v>184</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="L11" s="4" t="s">
-        <x:v>172</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:f t="shared" si="4">IF(C11="","",IF(N11&lt;&gt;"",N11,IF(O11&lt;&gt;"",O11,IF(P11&lt;&gt;"",P11,IF(Q11&lt;&gt;"",Q11,IF(R11&lt;&gt;"",R11,""))))))</x:f>
@@ -8224,11 +8227,11 @@
       <x:c r="O11" s="4"/>
       <x:c r="P11" s="4"/>
       <x:c r="Q11" s="63" t="s">
-        <x:v>185</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="R11" s="4"/>
       <x:c r="S11" s="4" t="s">
-        <x:v>175</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="T11" s="5" t="n">
         <x:v>46240</x:v>
@@ -8244,13 +8247,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>186</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>187</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E12" s="5"/>
       <x:c r="F12" s="5"/>
@@ -8263,13 +8266,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J12" s="4" t="s">
-        <x:v>188</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K12" s="4" t="s">
-        <x:v>189</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="L12" s="4" t="s">
-        <x:v>190</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
         <x:f t="shared" si="4">IF(C12="","",IF(N12&lt;&gt;"",N12,IF(O12&lt;&gt;"",O12,IF(P12&lt;&gt;"",P12,IF(Q12&lt;&gt;"",Q12,IF(R12&lt;&gt;"",R12,""))))))</x:f>
@@ -8277,7 +8280,7 @@
       </x:c>
       <x:c r="N12" s="4"/>
       <x:c r="O12" s="63" t="s">
-        <x:v>191</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="P12" s="4"/>
       <x:c r="Q12" s="63" t="str">
@@ -8301,13 +8304,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>192</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>193</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E13" s="5"/>
       <x:c r="F13" s="5"/>
@@ -8320,7 +8323,7 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J13" s="4" t="s">
-        <x:v>194</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K13" s="4"/>
       <x:c r="L13" s="4"/>
@@ -8330,16 +8333,16 @@
       </x:c>
       <x:c r="N13" s="4"/>
       <x:c r="O13" s="63" t="s">
-        <x:v>195</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="P13" s="63" t="s">
-        <x:v>196</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="Q13" s="63" t="str">
         <x:v>https://www.facebook.com/usebarq/videos/%D8%AD%D9%84%D8%A7%D8%AA-%D8%A7%D9%84%D8%B3%D9%81%D8%B1-%D8%A8%D8%A7%D9%84%D8%AA%D8%AC%D8%A7%D8%B1%D8%A8-%D9%88%D8%A8%D8%A8%D8%B7%D8%A7%D9%82%D8%A9-%D8%A8%D8%AF%D9%88%D9%86-%D8%B1%D8%B3%D9%88%D9%85-%D8%AF%D9%88%D9%84%D9%8A%D8%A9%EF%B8%8F/1051539764436915/</x:v>
       </x:c>
       <x:c r="R13" s="63" t="s">
-        <x:v>197</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="S13" s="4" t="str">
         <x:v>Current official posts continue to position barq Visa as having no international transaction fees. No campaign end date is stated.</x:v>
@@ -8358,10 +8361,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B14" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C14" s="4" t="s">
-        <x:v>198</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D14" s="4"/>
       <x:c r="E14" s="5"/>
@@ -8375,13 +8378,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J14" s="4" t="s">
-        <x:v>199</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="K14" s="4" t="s">
-        <x:v>200</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="L14" s="4" t="s">
-        <x:v>201</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="M14" s="9" t="str">
         <x:f t="shared" si="4">IF(C14="","",IF(N14&lt;&gt;"",N14,IF(O14&lt;&gt;"",O14,IF(P14&lt;&gt;"",P14,IF(Q14&lt;&gt;"",Q14,IF(R14&lt;&gt;"",R14,""))))))</x:f>
@@ -8389,7 +8392,7 @@
       </x:c>
       <x:c r="N14" s="4"/>
       <x:c r="O14" s="63" t="s">
-        <x:v>202</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="P14" s="4"/>
       <x:c r="Q14" s="4"/>
@@ -9392,7 +9395,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cef492c71ff4799"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a97a54acd1e4495"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9422,7 +9425,7 @@
   <x:sheetData>
     <x:row r="1" ht="22.649999618530273" customHeight="1">
       <x:c r="A1" s="52" t="s">
-        <x:v>203</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B1" s="52"/>
       <x:c r="C1" s="52"/>
@@ -9445,8 +9448,8 @@
       <x:c r="T1" s="52"/>
     </x:row>
     <x:row r="2" ht="21.399999618530273" customHeight="1">
-      <x:c r="A2" s="56" t="s">
-        <x:v>47</x:v>
+      <x:c r="A2" s="56" t="str">
+        <x:v>Active approved campaigns only. Expired campaigns are excluded. Merchant offers are shown as a count only.</x:v>
       </x:c>
       <x:c r="B2" s="56"/>
       <x:c r="C2" s="56"/>
@@ -9460,7 +9463,7 @@
       <x:c r="K2" s="56"/>
       <x:c r="L2" s="56"/>
       <x:c r="M2" s="57" t="s">
-        <x:v>48</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N2" s="57"/>
       <x:c r="O2" s="57"/>
@@ -9472,32 +9475,38 @@
       <x:c r="U2" s="57"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="41" t="s">
-        <x:v>49</x:v>
+      <x:c r="A4" s="41" t="str">
+        <x:v>Active Campaigns</x:v>
       </x:c>
       <x:c r="B4" s="41"/>
       <x:c r="C4" s="41"/>
-      <x:c r="D4" s="41"/>
-      <x:c r="E4" s="41" t="s">
-        <x:v>4</x:v>
+      <x:c r="D4" s="41" t="str">
+        <x:v>End Date Not Stated</x:v>
+      </x:c>
+      <x:c r="E4" s="41" t="str">
+        <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="F4" s="41"/>
-      <x:c r="G4" s="41"/>
+      <x:c r="G4" s="41" t="str">
+        <x:v>Remittance Campaigns</x:v>
+      </x:c>
       <x:c r="H4" s="41"/>
-      <x:c r="I4" s="43" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="J4" s="43"/>
+      <x:c r="I4" s="43" t="str">
+        <x:v>Remittance Campaigns</x:v>
+      </x:c>
+      <x:c r="J4" s="43" t="str">
+        <x:v>Expiring ≤30d</x:v>
+      </x:c>
       <x:c r="K4" s="43"/>
       <x:c r="L4" s="43"/>
-      <x:c r="M4" s="44" t="s">
-        <x:v>6</x:v>
+      <x:c r="M4" s="44" t="str">
+        <x:v>Merchant Offers (Count Only): 0</x:v>
       </x:c>
       <x:c r="N4" s="44"/>
       <x:c r="O4" s="44"/>
       <x:c r="P4" s="44"/>
-      <x:c r="Q4" s="41" t="s">
-        <x:v>7</x:v>
+      <x:c r="Q4" s="41" t="str">
+        <x:v>Expiring ≤30d</x:v>
       </x:c>
       <x:c r="R4" s="41"/>
       <x:c r="S4" s="41"/>
@@ -9505,36 +9514,44 @@
     </x:row>
     <x:row r="5" ht="23">
       <x:c r="A5" s="53" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant")</x:f>
-        <x:v>5</x:v>
+        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;")</x:f>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B5" s="53"/>
       <x:c r="C5" s="53"/>
-      <x:c r="D5" s="53"/>
+      <x:c r="D5" s="53" t="n">
+        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$I$9:$I$500,"End Date Not Stated")</x:f>
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E5" s="53" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
+        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$I$9:$I$500,"End Date Not Stated")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F5" s="53"/>
+      <x:c r="G5" s="53" t="n">
+        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"Remittance")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F5" s="53"/>
-      <x:c r="G5" s="53"/>
       <x:c r="H5" s="53"/>
       <x:c r="I5" s="54" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"&lt;&gt;Expired",'Mobily Pay'!$B$9:$B$500,"Remittance")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J5" s="54"/>
+        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"Remittance")</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J5" s="54" t="n">
+        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$I$9:$I$500,"Expiring ≤7 Days")+COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="K5" s="54"/>
       <x:c r="L5" s="54"/>
       <x:c r="M5" s="55" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"Merchant",'Mobily Pay'!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N5" s="55"/>
       <x:c r="O5" s="55"/>
       <x:c r="P5" s="55"/>
       <x:c r="Q5" s="53" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"Expiring ≤7 Days")+COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"&lt;&gt;Merchant",'Mobily Pay'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
-        <x:v>1</x:v>
+        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$I$9:$I$500,"Expiring ≤7 Days")+COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="R5" s="53"/>
       <x:c r="S5" s="53"/>
@@ -9542,67 +9559,67 @@
     </x:row>
     <x:row r="8" ht="30.649999618530273" customHeight="1">
       <x:c r="A8" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H8" s="3" t="s">
-        <x:v>56</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I8" s="3" t="s">
-        <x:v>57</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="J8" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K8" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L8" s="3" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="M8" s="3" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="N8" s="3" t="s">
-        <x:v>62</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O8" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="P8" s="3" t="s">
-        <x:v>64</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="Q8" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
-        <x:v>66</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="S8" s="3" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="T8" s="3" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="U8" s="34" t="s">
-        <x:v>69</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="T8" s="3" t="str">
+        <x:v>Social Post Count</x:v>
+      </x:c>
+      <x:c r="U8" s="34" t="str">
+        <x:v>Published Platforms</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="46.650001525878906" customHeight="1">
@@ -9611,7 +9628,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>International Transfer Prize Draw – SAR 110,000</x:v>
@@ -9628,7 +9645,7 @@
       </x:c>
       <x:c r="H9" s="7" t="n">
         <x:f t="shared" ref="H9:H42" si="1">IF(OR(C9="",G9=""),"",G9-TODAY())</x:f>
-        <x:v>-31</x:v>
+        <x:v>-51</x:v>
       </x:c>
       <x:c r="I9" s="6" t="str">
         <x:f t="shared" ref="I9:I42" si="2">IF(C9="","",IF(G9="","End Date Not Stated",IF(G9&lt;TODAY(),"Expired",IF(G9&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G9&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
@@ -9651,13 +9668,13 @@
         <x:v>https://mobilypay.sa/ar/offers/offer-51.html</x:v>
       </x:c>
       <x:c r="O9" s="63" t="s">
-        <x:v>204</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="P9" s="63" t="s">
-        <x:v>205</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="Q9" s="63" t="s">
-        <x:v>206</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="R9" s="4"/>
       <x:c r="S9" s="4" t="str">
@@ -9677,7 +9694,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C10" s="4" t="str">
         <x:v>Zero-Fee International Transfers – Aug–Oct 2026</x:v>
@@ -9694,7 +9711,7 @@
       </x:c>
       <x:c r="H10" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C10="",G10=""),"",G10-TODAY())</x:f>
-        <x:v>86</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I10" s="6" t="str">
         <x:f t="shared" si="2">IF(C10="","",IF(G10="","End Date Not Stated",IF(G10&lt;TODAY(),"Expired",IF(G10&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G10&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
@@ -9717,11 +9734,11 @@
         <x:v>https://mobilypay.sa/ar/offers/offer-56.html</x:v>
       </x:c>
       <x:c r="O10" s="63" t="s">
-        <x:v>207</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="P10" s="4"/>
       <x:c r="Q10" s="63" t="s">
-        <x:v>208</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="R10" s="4"/>
       <x:c r="S10" s="4" t="str">
@@ -9741,13 +9758,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
-        <x:v>209</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>210</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5"/>
@@ -9760,13 +9777,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
-        <x:v>188</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K11" s="4" t="s">
-        <x:v>211</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="L11" s="4" t="s">
-        <x:v>212</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:f t="shared" si="3">IF(C11="","",IF(N11&lt;&gt;"",N11,IF(O11&lt;&gt;"",O11,IF(P11&lt;&gt;"",P11,IF(Q11&lt;&gt;"",Q11,IF(R11&lt;&gt;"",R11,""))))))</x:f>
@@ -9776,11 +9793,11 @@
       <x:c r="O11" s="4"/>
       <x:c r="P11" s="4"/>
       <x:c r="Q11" s="63" t="s">
-        <x:v>213</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="R11" s="4"/>
       <x:c r="S11" s="4" t="s">
-        <x:v>214</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="T11" s="5" t="n">
         <x:v>46240</x:v>
@@ -9796,13 +9813,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>215</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>216</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E12" s="5"/>
       <x:c r="F12" s="5">
@@ -9813,34 +9830,34 @@
       </x:c>
       <x:c r="H12" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C12="",G12=""),"",G12-TODAY())</x:f>
-        <x:v>147</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="I12" s="6" t="str">
         <x:f t="shared" si="2">IF(C12="","",IF(G12="","End Date Not Stated",IF(G12&lt;TODAY(),"Expired",IF(G12&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G12&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J12" s="4" t="s">
-        <x:v>217</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="K12" s="4" t="s">
-        <x:v>218</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="L12" s="4" t="s">
-        <x:v>219</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
         <x:f t="shared" si="3">IF(C12="","",IF(N12&lt;&gt;"",N12,IF(O12&lt;&gt;"",O12,IF(P12&lt;&gt;"",P12,IF(Q12&lt;&gt;"",Q12,IF(R12&lt;&gt;"",R12,""))))))</x:f>
         <x:v>https://mobilypay.sa/offer-details.html?id=offer-6</x:v>
       </x:c>
       <x:c r="N12" s="4" t="s">
-        <x:v>220</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="O12" s="4"/>
       <x:c r="P12" s="4"/>
       <x:c r="Q12" s="4"/>
       <x:c r="R12" s="4"/>
       <x:c r="S12" s="4" t="s">
-        <x:v>221</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="T12" s="5" t="n">
         <x:v>46240</x:v>
@@ -9856,13 +9873,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>222</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>223</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="E13" s="5"/>
       <x:c r="F13" s="5">
@@ -9873,17 +9890,17 @@
       </x:c>
       <x:c r="H13" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C13="",G13=""),"",G13-TODAY())</x:f>
-        <x:v>13</x:v>
+        <x:v>-7</x:v>
       </x:c>
       <x:c r="I13" s="6" t="str">
         <x:f t="shared" si="2">IF(C13="","",IF(G13="","End Date Not Stated",IF(G13&lt;TODAY(),"Expired",IF(G13&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G13&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
-        <x:v>Expiring 8–30 Days</x:v>
+        <x:v>Expired</x:v>
       </x:c>
       <x:c r="J13" s="4" t="s">
-        <x:v>224</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K13" s="1" t="s">
-        <x:v>225</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="L13" s="4"/>
       <x:c r="M13" s="9" t="str">
@@ -9891,17 +9908,17 @@
         <x:v>https://mobilypay.sa/offer-details.html?id=offer-53</x:v>
       </x:c>
       <x:c r="N13" s="63" t="s">
-        <x:v>226</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="O13" s="4"/>
       <x:c r="P13" s="63" t="s">
-        <x:v>227</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="Q13" s="63" t="s">
-        <x:v>228</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="R13" s="63" t="s">
-        <x:v>229</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="S13" s="4" t="str">
         <x:v>Campaign is valid from 19 July to 19 August 2026. It includes 0% international transaction fees for eligible newly issued Platinum and Signature Visa cards, free plastic-card issuance, and eligible POS/e-commerce purchases.</x:v>
@@ -9920,13 +9937,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B14" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C14" s="4" t="s">
-        <x:v>230</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>231</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E14" s="5"/>
       <x:c r="F14" s="5">
@@ -9937,36 +9954,36 @@
       </x:c>
       <x:c r="H14" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C14="",G14=""),"",G14-TODAY())</x:f>
-        <x:v>-6</x:v>
+        <x:v>-26</x:v>
       </x:c>
       <x:c r="I14" s="6" t="str">
         <x:f t="shared" si="2">IF(C14="","",IF(G14="","End Date Not Stated",IF(G14&lt;TODAY(),"Expired",IF(G14&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G14&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J14" s="4" t="s">
-        <x:v>232</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K14" s="4" t="s">
-        <x:v>233</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="L14" s="4" t="s">
-        <x:v>234</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="M14" s="9" t="str">
         <x:f t="shared" si="3">IF(C14="","",IF(N14&lt;&gt;"",N14,IF(O14&lt;&gt;"",O14,IF(P14&lt;&gt;"",P14,IF(Q14&lt;&gt;"",Q14,IF(R14&lt;&gt;"",R14,""))))))</x:f>
         <x:v>https://mobilypay.sa/offer-details.html?id=offer-54</x:v>
       </x:c>
       <x:c r="N14" s="63" t="s">
-        <x:v>235</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="O14" s="63" t="s">
-        <x:v>236</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="P14" s="63" t="s">
-        <x:v>237</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="Q14" s="63" t="s">
-        <x:v>238</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="R14" s="4"/>
       <x:c r="S14" s="4" t="str">
@@ -10986,7 +11003,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf56c8f61049c4388"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc510448c70f14db5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11016,7 +11033,7 @@
   <x:sheetData>
     <x:row r="1" ht="22.649999618530273" customHeight="1">
       <x:c r="A1" s="52" t="s">
-        <x:v>239</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B1" s="52"/>
       <x:c r="C1" s="52"/>
@@ -11039,8 +11056,8 @@
       <x:c r="T1" s="52"/>
     </x:row>
     <x:row r="2" ht="21.399999618530273" customHeight="1">
-      <x:c r="A2" s="56" t="s">
-        <x:v>47</x:v>
+      <x:c r="A2" s="56" t="str">
+        <x:v>Active approved campaigns only. Expired campaigns are excluded. Merchant offers are shown as a count only.</x:v>
       </x:c>
       <x:c r="B2" s="56"/>
       <x:c r="C2" s="56"/>
@@ -11054,7 +11071,7 @@
       <x:c r="K2" s="56"/>
       <x:c r="L2" s="56"/>
       <x:c r="M2" s="57" t="s">
-        <x:v>48</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N2" s="57"/>
       <x:c r="O2" s="57"/>
@@ -11066,32 +11083,38 @@
       <x:c r="U2" s="57"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="41" t="s">
-        <x:v>49</x:v>
+      <x:c r="A4" s="41" t="str">
+        <x:v>Active Campaigns</x:v>
       </x:c>
       <x:c r="B4" s="41"/>
       <x:c r="C4" s="41"/>
-      <x:c r="D4" s="41"/>
-      <x:c r="E4" s="41" t="s">
-        <x:v>4</x:v>
+      <x:c r="D4" s="41" t="str">
+        <x:v>End Date Not Stated</x:v>
+      </x:c>
+      <x:c r="E4" s="41" t="str">
+        <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="F4" s="41"/>
-      <x:c r="G4" s="41"/>
+      <x:c r="G4" s="41" t="str">
+        <x:v>Remittance Campaigns</x:v>
+      </x:c>
       <x:c r="H4" s="41"/>
-      <x:c r="I4" s="43" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="J4" s="43"/>
+      <x:c r="I4" s="43" t="str">
+        <x:v>Remittance Campaigns</x:v>
+      </x:c>
+      <x:c r="J4" s="43" t="str">
+        <x:v>Expiring ≤30d</x:v>
+      </x:c>
       <x:c r="K4" s="43"/>
       <x:c r="L4" s="43"/>
-      <x:c r="M4" s="44" t="s">
-        <x:v>6</x:v>
+      <x:c r="M4" s="44" t="str">
+        <x:v>Merchant Offers (Count Only): 0</x:v>
       </x:c>
       <x:c r="N4" s="44"/>
       <x:c r="O4" s="44"/>
       <x:c r="P4" s="44"/>
-      <x:c r="Q4" s="41" t="s">
-        <x:v>7</x:v>
+      <x:c r="Q4" s="41" t="str">
+        <x:v>Expiring ≤30d</x:v>
       </x:c>
       <x:c r="R4" s="41"/>
       <x:c r="S4" s="41"/>
@@ -11099,35 +11122,43 @@
     </x:row>
     <x:row r="5" ht="23">
       <x:c r="A5" s="53" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant")</x:f>
-        <x:v>5</x:v>
+        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$M$9:$M$500,"&lt;&gt;")</x:f>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B5" s="53"/>
       <x:c r="C5" s="53"/>
-      <x:c r="D5" s="53"/>
+      <x:c r="D5" s="53" t="n">
+        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$I$9:$I$500,"End Date Not Stated")</x:f>
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="E5" s="53" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>3</x:v>
+        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$I$9:$I$500,"End Date Not Stated")</x:f>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F5" s="53"/>
-      <x:c r="G5" s="53"/>
+      <x:c r="G5" s="53" t="n">
+        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$B$9:$B$500,"Remittance")</x:f>
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="H5" s="53"/>
       <x:c r="I5" s="54" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"&lt;&gt;Expired",tiqmo!$B$9:$B$500,"Remittance")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J5" s="54"/>
+        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$B$9:$B$500,"Remittance")</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J5" s="54" t="n">
+        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$I$9:$I$500,"Expiring ≤7 Days")+COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="K5" s="54"/>
       <x:c r="L5" s="54"/>
       <x:c r="M5" s="55" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"Merchant",tiqmo!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N5" s="55"/>
       <x:c r="O5" s="55"/>
       <x:c r="P5" s="55"/>
       <x:c r="Q5" s="53" t="n">
-        <x:f>COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"Expiring ≤7 Days")+COUNTIFS(tiqmo!$C$9:$C$500,"&lt;&gt;",tiqmo!$M$9:$M$500,"&lt;&gt;",tiqmo!$B$9:$B$500,"&lt;&gt;Merchant",tiqmo!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
+        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$I$9:$I$500,"Expiring ≤7 Days")+COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="R5" s="53"/>
@@ -11136,67 +11167,67 @@
     </x:row>
     <x:row r="8" ht="30.649999618530273" customHeight="1">
       <x:c r="A8" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H8" s="3" t="s">
-        <x:v>56</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I8" s="3" t="s">
-        <x:v>57</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="J8" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K8" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L8" s="3" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="M8" s="3" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="N8" s="3" t="s">
-        <x:v>62</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O8" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="P8" s="3" t="s">
-        <x:v>64</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="Q8" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
-        <x:v>66</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="S8" s="3" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="T8" s="3" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="U8" s="34" t="s">
-        <x:v>69</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="T8" s="3" t="str">
+        <x:v>Social Post Count</x:v>
+      </x:c>
+      <x:c r="U8" s="34" t="str">
+        <x:v>Published Platforms</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="46.650001525878906" customHeight="1">
@@ -11205,13 +11236,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>240</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>241</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="E9" s="5">
         <x:v>46227</x:v>
@@ -11226,13 +11257,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J9" s="4" t="s">
-        <x:v>242</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="K9" s="4" t="s">
-        <x:v>243</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="L9" s="4" t="s">
-        <x:v>244</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:f t="shared" ref="M9:M42" si="3">IF(C9="","",IF(N9&lt;&gt;"",N9,IF(O9&lt;&gt;"",O9,IF(P9&lt;&gt;"",P9,IF(Q9&lt;&gt;"",Q9,IF(R9&lt;&gt;"",R9,""))))))</x:f>
@@ -11240,17 +11271,17 @@
       </x:c>
       <x:c r="N9" s="4"/>
       <x:c r="O9" s="4" t="s">
-        <x:v>245</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="P9" s="63" t="s">
-        <x:v>246</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="Q9" s="63" t="s">
-        <x:v>247</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="R9" s="4"/>
       <x:c r="S9" s="4" t="s">
-        <x:v>175</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="T9" s="5" t="n">
         <x:v>46240</x:v>
@@ -11266,13 +11297,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>248</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>249</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="E10" s="5">
         <x:v>46226</x:v>
@@ -11285,20 +11316,20 @@
       </x:c>
       <x:c r="H10" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C10="",G10=""),"",G10-TODAY())</x:f>
-        <x:v>-6</x:v>
+        <x:v>-26</x:v>
       </x:c>
       <x:c r="I10" s="6" t="str">
         <x:f t="shared" si="2">IF(C10="","",IF(G10="","End Date Not Stated",IF(G10&lt;TODAY(),"Expired",IF(G10&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G10&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J10" s="4" t="s">
-        <x:v>250</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="K10" s="4" t="s">
-        <x:v>251</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="L10" s="4" t="s">
-        <x:v>252</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="M10" s="9" t="str">
         <x:f t="shared" si="3">IF(C10="","",IF(N10&lt;&gt;"",N10,IF(O10&lt;&gt;"",O10,IF(P10&lt;&gt;"",P10,IF(Q10&lt;&gt;"",Q10,IF(R10&lt;&gt;"",R10,""))))))</x:f>
@@ -11306,7 +11337,7 @@
       </x:c>
       <x:c r="N10" s="4"/>
       <x:c r="O10" s="4" t="s">
-        <x:v>253</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="P10" s="4"/>
       <x:c r="Q10" s="4"/>
@@ -11328,13 +11359,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
-        <x:v>254</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>255</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5"/>
@@ -11343,20 +11374,20 @@
       </x:c>
       <x:c r="H11" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C11="",G11=""),"",G11-TODAY())</x:f>
-        <x:v>-67</x:v>
+        <x:v>-87</x:v>
       </x:c>
       <x:c r="I11" s="6" t="str">
         <x:f t="shared" si="2">IF(C11="","",IF(G11="","End Date Not Stated",IF(G11&lt;TODAY(),"Expired",IF(G11&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G11&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
-        <x:v>188</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K11" s="4" t="s">
-        <x:v>256</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="L11" s="4" t="s">
-        <x:v>257</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:f t="shared" si="3">IF(C11="","",IF(N11&lt;&gt;"",N11,IF(O11&lt;&gt;"",O11,IF(P11&lt;&gt;"",P11,IF(Q11&lt;&gt;"",Q11,IF(R11&lt;&gt;"",R11,""))))))</x:f>
@@ -11364,13 +11395,13 @@
       </x:c>
       <x:c r="N11" s="4"/>
       <x:c r="O11" s="4" t="s">
-        <x:v>258</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="P11" s="63" t="s">
-        <x:v>259</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="Q11" s="4" t="s">
-        <x:v>260</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="R11" s="4"/>
       <x:c r="S11" s="4" t="str">
@@ -11390,13 +11421,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>261</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>262</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="E12" s="5"/>
       <x:c r="F12" s="5"/>
@@ -11409,13 +11440,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J12" s="4" t="s">
-        <x:v>188</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K12" s="4" t="s">
-        <x:v>263</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="L12" s="4" t="s">
-        <x:v>264</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
         <x:f t="shared" si="3">IF(C12="","",IF(N12&lt;&gt;"",N12,IF(O12&lt;&gt;"",O12,IF(P12&lt;&gt;"",P12,IF(Q12&lt;&gt;"",Q12,IF(R12&lt;&gt;"",R12,""))))))</x:f>
@@ -11423,17 +11454,17 @@
       </x:c>
       <x:c r="N12" s="4"/>
       <x:c r="O12" s="4" t="s">
-        <x:v>265</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="P12" s="63" t="s">
-        <x:v>266</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="Q12" s="63" t="s">
-        <x:v>267</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="R12" s="4"/>
       <x:c r="S12" s="4" t="s">
-        <x:v>268</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="T12" s="5" t="n">
         <x:v>46240</x:v>
@@ -11449,7 +11480,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
         <x:v>Zero International Card Transaction Fees</x:v>
@@ -11466,7 +11497,7 @@
       </x:c>
       <x:c r="H13" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C13="",G13=""),"",G13-TODAY())</x:f>
-        <x:v>147</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="I13" s="6" t="str">
         <x:f t="shared" si="2">IF(C13="","",IF(G13="","End Date Not Stated",IF(G13&lt;TODAY(),"Expired",IF(G13&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G13&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
@@ -11489,16 +11520,16 @@
         <x:v>https://www.tiqmo.com/ar/offers</x:v>
       </x:c>
       <x:c r="O13" s="63" t="s">
-        <x:v>269</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="P13" s="63" t="s">
-        <x:v>270</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="Q13" s="63" t="s">
-        <x:v>271</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="R13" s="63" t="s">
-        <x:v>272</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="S13" s="4" t="str">
         <x:v>Offer is valid from 1 May to 31 December 2026. It applies outside Saudi Arabia and excludes international online stores, websites and mobile applications. tiqmo standard terms apply.</x:v>
@@ -11532,7 +11563,7 @@
       </x:c>
       <x:c r="H14" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C14="",G14=""),"",G14-TODAY())</x:f>
-        <x:v>-6</x:v>
+        <x:v>-26</x:v>
       </x:c>
       <x:c r="I14" s="6" t="str">
         <x:f t="shared" si="2">IF(C14="","",IF(G14="","End Date Not Stated",IF(G14&lt;TODAY(),"Expired",IF(G14&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G14&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
@@ -12579,7 +12610,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11aeda7c43f84b58"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec33113ccc264e56"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12609,7 +12640,7 @@
   <x:sheetData>
     <x:row r="1" ht="22.649999618530273" customHeight="1">
       <x:c r="A1" s="52" t="s">
-        <x:v>273</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B1" s="52"/>
       <x:c r="C1" s="52"/>
@@ -12632,8 +12663,8 @@
       <x:c r="T1" s="52"/>
     </x:row>
     <x:row r="2" ht="21.399999618530273" customHeight="1">
-      <x:c r="A2" s="56" t="s">
-        <x:v>47</x:v>
+      <x:c r="A2" s="56" t="str">
+        <x:v>Active approved campaigns only. Expired campaigns are excluded. Merchant offers are shown as a count only.</x:v>
       </x:c>
       <x:c r="B2" s="56"/>
       <x:c r="C2" s="56"/>
@@ -12647,7 +12678,7 @@
       <x:c r="K2" s="56"/>
       <x:c r="L2" s="56"/>
       <x:c r="M2" s="57" t="s">
-        <x:v>48</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N2" s="57"/>
       <x:c r="O2" s="57"/>
@@ -12659,32 +12690,38 @@
       <x:c r="U2" s="57"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="41" t="s">
-        <x:v>49</x:v>
+      <x:c r="A4" s="41" t="str">
+        <x:v>Active Campaigns</x:v>
       </x:c>
       <x:c r="B4" s="41"/>
       <x:c r="C4" s="41"/>
-      <x:c r="D4" s="41"/>
-      <x:c r="E4" s="41" t="s">
-        <x:v>4</x:v>
+      <x:c r="D4" s="41" t="str">
+        <x:v>End Date Not Stated</x:v>
+      </x:c>
+      <x:c r="E4" s="41" t="str">
+        <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="F4" s="41"/>
-      <x:c r="G4" s="41"/>
+      <x:c r="G4" s="41" t="str">
+        <x:v>Remittance Campaigns</x:v>
+      </x:c>
       <x:c r="H4" s="41"/>
-      <x:c r="I4" s="43" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="J4" s="43"/>
+      <x:c r="I4" s="43" t="str">
+        <x:v>Remittance Campaigns</x:v>
+      </x:c>
+      <x:c r="J4" s="43" t="str">
+        <x:v>Expiring ≤30d</x:v>
+      </x:c>
       <x:c r="K4" s="43"/>
       <x:c r="L4" s="43"/>
-      <x:c r="M4" s="44" t="s">
-        <x:v>6</x:v>
+      <x:c r="M4" s="44" t="str">
+        <x:v>Merchant Offers (Count Only): 0</x:v>
       </x:c>
       <x:c r="N4" s="44"/>
       <x:c r="O4" s="44"/>
       <x:c r="P4" s="44"/>
-      <x:c r="Q4" s="41" t="s">
-        <x:v>7</x:v>
+      <x:c r="Q4" s="41" t="str">
+        <x:v>Expiring ≤30d</x:v>
       </x:c>
       <x:c r="R4" s="41"/>
       <x:c r="S4" s="41"/>
@@ -12692,35 +12729,43 @@
     </x:row>
     <x:row r="5" ht="23">
       <x:c r="A5" s="53" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant")</x:f>
-        <x:v>3</x:v>
+        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$M$9:$M$500,"&lt;&gt;")</x:f>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="53"/>
       <x:c r="C5" s="53"/>
-      <x:c r="D5" s="53"/>
+      <x:c r="D5" s="53" t="n">
+        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$I$9:$I$500,"End Date Not Stated")</x:f>
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="E5" s="53" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
+        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$I$9:$I$500,"End Date Not Stated")</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="F5" s="53"/>
-      <x:c r="G5" s="53"/>
+      <x:c r="G5" s="53" t="n">
+        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$B$9:$B$500,"Remittance")</x:f>
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H5" s="53"/>
       <x:c r="I5" s="54" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"&lt;&gt;Expired",urpay!$B$9:$B$500,"Remittance")</x:f>
+        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$B$9:$B$500,"Remittance")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J5" s="54"/>
+      <x:c r="J5" s="54" t="n">
+        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$I$9:$I$500,"Expiring ≤7 Days")+COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="K5" s="54"/>
       <x:c r="L5" s="54"/>
       <x:c r="M5" s="55" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"Merchant",urpay!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N5" s="55"/>
       <x:c r="O5" s="55"/>
       <x:c r="P5" s="55"/>
       <x:c r="Q5" s="53" t="n">
-        <x:f>COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"Expiring ≤7 Days")+COUNTIFS(urpay!$C$9:$C$500,"&lt;&gt;",urpay!$M$9:$M$500,"&lt;&gt;",urpay!$B$9:$B$500,"&lt;&gt;Merchant",urpay!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
+        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$I$9:$I$500,"Expiring ≤7 Days")+COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="R5" s="53"/>
@@ -12729,67 +12774,67 @@
     </x:row>
     <x:row r="8" ht="30.649999618530273" customHeight="1">
       <x:c r="A8" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H8" s="3" t="s">
-        <x:v>56</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I8" s="3" t="s">
-        <x:v>57</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="J8" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K8" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L8" s="3" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="M8" s="3" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="N8" s="3" t="s">
-        <x:v>62</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O8" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="P8" s="3" t="s">
-        <x:v>64</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="Q8" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
-        <x:v>66</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="S8" s="3" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="T8" s="3" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="U8" s="34" t="s">
-        <x:v>69</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="T8" s="3" t="str">
+        <x:v>Social Post Count</x:v>
+      </x:c>
+      <x:c r="U8" s="34" t="str">
+        <x:v>Published Platforms</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="46.650001525878906" customHeight="1">
@@ -12798,13 +12843,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>274</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>275</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="E9" s="5"/>
       <x:c r="F9" s="5"/>
@@ -12817,31 +12862,31 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J9" s="4" t="s">
-        <x:v>276</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="K9" s="4" t="s">
-        <x:v>277</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="L9" s="4" t="s">
-        <x:v>278</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:f t="shared" ref="M9:M46" si="3">IF(C9="","",IF(N9&lt;&gt;"",N9,IF(O9&lt;&gt;"",O9,IF(P9&lt;&gt;"",P9,IF(Q9&lt;&gt;"",Q9,IF(R9&lt;&gt;"",R9,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/cashback-system</x:v>
       </x:c>
       <x:c r="N9" s="63" t="s">
-        <x:v>279</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="O9" s="4"/>
       <x:c r="P9" s="63" t="s">
-        <x:v>280</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="Q9" s="4" t="s">
-        <x:v>281</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="R9" s="4"/>
       <x:c r="S9" s="4" t="s">
-        <x:v>282</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="T9" s="5" t="n">
         <x:v>46240</x:v>
@@ -12857,13 +12902,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>283</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>284</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="E10" s="5"/>
       <x:c r="F10" s="5"/>
@@ -12872,34 +12917,34 @@
       </x:c>
       <x:c r="H10" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C10="",G10=""),"",G10-TODAY())</x:f>
-        <x:v>147</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="I10" s="6" t="str">
         <x:f t="shared" si="2">IF(C10="","",IF(G10="","End Date Not Stated",IF(G10&lt;TODAY(),"Expired",IF(G10&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G10&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J10" s="4" t="s">
-        <x:v>285</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="K10" s="4" t="s">
-        <x:v>286</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="L10" s="4" t="s">
-        <x:v>287</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="M10" s="9" t="str">
         <x:f t="shared" si="3">IF(C10="","",IF(N10&lt;&gt;"",N10,IF(O10&lt;&gt;"",O10,IF(P10&lt;&gt;"",P10,IF(Q10&lt;&gt;"",Q10,IF(R10&lt;&gt;"",R10,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/urpay-offers/alhabibbedding</x:v>
       </x:c>
       <x:c r="N10" s="4" t="s">
-        <x:v>288</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="O10" s="4"/>
       <x:c r="P10" s="4"/>
       <x:c r="Q10" s="4"/>
       <x:c r="R10" s="4"/>
       <x:c r="S10" s="4" t="s">
-        <x:v>289</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="T10" s="5" t="n">
         <x:v>46240</x:v>
@@ -12915,13 +12960,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
-        <x:v>290</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>291</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5"/>
@@ -12930,34 +12975,34 @@
       </x:c>
       <x:c r="H11" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C11="",G11=""),"",G11-TODAY())</x:f>
-        <x:v>147</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="I11" s="6" t="str">
         <x:f t="shared" si="2">IF(C11="","",IF(G11="","End Date Not Stated",IF(G11&lt;TODAY(),"Expired",IF(G11&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G11&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
-        <x:v>292</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="K11" s="4" t="s">
-        <x:v>293</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="L11" s="4" t="s">
-        <x:v>294</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:f t="shared" si="3">IF(C11="","",IF(N11&lt;&gt;"",N11,IF(O11&lt;&gt;"",O11,IF(P11&lt;&gt;"",P11,IF(Q11&lt;&gt;"",Q11,IF(R11&lt;&gt;"",R11,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/urpay-offers/squatwolf</x:v>
       </x:c>
       <x:c r="N11" s="4" t="s">
-        <x:v>295</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="O11" s="4"/>
       <x:c r="P11" s="4"/>
       <x:c r="Q11" s="4"/>
       <x:c r="R11" s="4"/>
       <x:c r="S11" s="4" t="s">
-        <x:v>296</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="T11" s="5" t="n">
         <x:v>46240</x:v>
@@ -12973,13 +13018,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>297</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>298</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E12" s="5"/>
       <x:c r="F12" s="5"/>
@@ -12988,34 +13033,34 @@
       </x:c>
       <x:c r="H12" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C12="",G12=""),"",G12-TODAY())</x:f>
-        <x:v>147</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="I12" s="6" t="str">
         <x:f t="shared" si="2">IF(C12="","",IF(G12="","End Date Not Stated",IF(G12&lt;TODAY(),"Expired",IF(G12&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G12&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J12" s="4" t="s">
-        <x:v>299</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="K12" s="4" t="s">
-        <x:v>300</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="L12" s="4" t="s">
-        <x:v>287</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
         <x:f t="shared" si="3">IF(C12="","",IF(N12&lt;&gt;"",N12,IF(O12&lt;&gt;"",O12,IF(P12&lt;&gt;"",P12,IF(Q12&lt;&gt;"",Q12,IF(R12&lt;&gt;"",R12,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/urpay-offers/mag</x:v>
       </x:c>
       <x:c r="N12" s="4" t="s">
-        <x:v>301</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="O12" s="4"/>
       <x:c r="P12" s="4"/>
       <x:c r="Q12" s="4"/>
       <x:c r="R12" s="4"/>
       <x:c r="S12" s="4" t="s">
-        <x:v>302</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="T12" s="5" t="n">
         <x:v>46240</x:v>
@@ -13031,13 +13076,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>303</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>304</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E13" s="5"/>
       <x:c r="F13" s="5"/>
@@ -13046,34 +13091,34 @@
       </x:c>
       <x:c r="H13" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C13="",G13=""),"",G13-TODAY())</x:f>
-        <x:v>147</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="I13" s="6" t="str">
         <x:f t="shared" si="2">IF(C13="","",IF(G13="","End Date Not Stated",IF(G13&lt;TODAY(),"Expired",IF(G13&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G13&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J13" s="4" t="s">
-        <x:v>305</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="K13" s="4" t="s">
-        <x:v>306</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="L13" s="4" t="s">
-        <x:v>294</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="M13" s="9" t="str">
         <x:f t="shared" si="3">IF(C13="","",IF(N13&lt;&gt;"",N13,IF(O13&lt;&gt;"",O13,IF(P13&lt;&gt;"",P13,IF(Q13&lt;&gt;"",Q13,IF(R13&lt;&gt;"",R13,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/urpay-offers/b-bw</x:v>
       </x:c>
       <x:c r="N13" s="4" t="s">
-        <x:v>307</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="O13" s="4"/>
       <x:c r="P13" s="4"/>
       <x:c r="Q13" s="4"/>
       <x:c r="R13" s="4"/>
       <x:c r="S13" s="4" t="s">
-        <x:v>308</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="T13" s="5" t="n">
         <x:v>46240</x:v>
@@ -13089,13 +13134,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B14" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C14" s="4" t="s">
-        <x:v>309</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>310</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="E14" s="5"/>
       <x:c r="F14" s="5"/>
@@ -13104,34 +13149,34 @@
       </x:c>
       <x:c r="H14" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C14="",G14=""),"",G14-TODAY())</x:f>
-        <x:v>147</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="I14" s="6" t="str">
         <x:f t="shared" si="2">IF(C14="","",IF(G14="","End Date Not Stated",IF(G14&lt;TODAY(),"Expired",IF(G14&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G14&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J14" s="4" t="s">
-        <x:v>311</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="K14" s="4" t="s">
-        <x:v>312</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L14" s="4" t="s">
-        <x:v>287</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="M14" s="9" t="str">
         <x:f t="shared" si="3">IF(C14="","",IF(N14&lt;&gt;"",N14,IF(O14&lt;&gt;"",O14,IF(P14&lt;&gt;"",P14,IF(Q14&lt;&gt;"",Q14,IF(R14&lt;&gt;"",R14,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/urpay-offers/nadi-ph</x:v>
       </x:c>
       <x:c r="N14" s="4" t="s">
-        <x:v>313</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="O14" s="4"/>
       <x:c r="P14" s="4"/>
       <x:c r="Q14" s="4"/>
       <x:c r="R14" s="4"/>
       <x:c r="S14" s="4" t="s">
-        <x:v>314</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="T14" s="5" t="n">
         <x:v>46240</x:v>
@@ -13147,13 +13192,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B15" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C15" s="4" t="s">
-        <x:v>315</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>316</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="E15" s="5"/>
       <x:c r="F15" s="5"/>
@@ -13162,34 +13207,34 @@
       </x:c>
       <x:c r="H15" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C15="",G15=""),"",G15-TODAY())</x:f>
-        <x:v>-37</x:v>
+        <x:v>-57</x:v>
       </x:c>
       <x:c r="I15" s="6" t="str">
         <x:f t="shared" si="2">IF(C15="","",IF(G15="","End Date Not Stated",IF(G15&lt;TODAY(),"Expired",IF(G15&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G15&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J15" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K15" s="4" t="s">
-        <x:v>317</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="L15" s="4" t="s">
-        <x:v>318</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="M15" s="9" t="str">
         <x:f t="shared" si="3">IF(C15="","",IF(N15&lt;&gt;"",N15,IF(O15&lt;&gt;"",O15,IF(P15&lt;&gt;"",P15,IF(Q15&lt;&gt;"",Q15,IF(R15&lt;&gt;"",R15,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/urpay-offers/iherb</x:v>
       </x:c>
       <x:c r="N15" s="4" t="s">
-        <x:v>319</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="O15" s="4"/>
       <x:c r="P15" s="4"/>
       <x:c r="Q15" s="4"/>
       <x:c r="R15" s="4"/>
       <x:c r="S15" s="4" t="s">
-        <x:v>320</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="T15" s="5" t="n">
         <x:v>46240</x:v>
@@ -13205,13 +13250,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C16" s="4" t="s">
-        <x:v>321</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D16" s="4" t="s">
-        <x:v>322</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="E16" s="5"/>
       <x:c r="F16" s="5"/>
@@ -13224,13 +13269,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J16" s="4" t="s">
-        <x:v>323</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="K16" s="4" t="s">
-        <x:v>324</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="L16" s="4" t="s">
-        <x:v>325</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="M16" s="9" t="str">
         <x:f t="shared" si="3">IF(C16="","",IF(N16&lt;&gt;"",N16,IF(O16&lt;&gt;"",O16,IF(P16&lt;&gt;"",P16,IF(Q16&lt;&gt;"",Q16,IF(R16&lt;&gt;"",R16,""))))))</x:f>
@@ -13239,12 +13284,12 @@
       <x:c r="N16" s="4"/>
       <x:c r="O16" s="4"/>
       <x:c r="P16" s="4" t="s">
-        <x:v>326</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="Q16" s="4"/>
       <x:c r="R16" s="4"/>
       <x:c r="S16" s="4" t="s">
-        <x:v>327</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="T16" s="5" t="n">
         <x:v>46240</x:v>
@@ -14348,7 +14393,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22b8447572ee4d08"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9f047b21d434be4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14378,7 +14423,7 @@
   <x:sheetData>
     <x:row r="1" ht="22.649999618530273" customHeight="1">
       <x:c r="A1" s="52" t="s">
-        <x:v>328</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B1" s="52"/>
       <x:c r="C1" s="52"/>
@@ -14401,8 +14446,8 @@
       <x:c r="T1" s="52"/>
     </x:row>
     <x:row r="2" ht="21.399999618530273" customHeight="1">
-      <x:c r="A2" s="56" t="s">
-        <x:v>47</x:v>
+      <x:c r="A2" s="56" t="str">
+        <x:v>Active approved campaigns only. Expired campaigns are excluded. Merchant offers are shown as a count only.</x:v>
       </x:c>
       <x:c r="B2" s="56"/>
       <x:c r="C2" s="56"/>
@@ -14416,7 +14461,7 @@
       <x:c r="K2" s="56"/>
       <x:c r="L2" s="56"/>
       <x:c r="M2" s="57" t="s">
-        <x:v>48</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N2" s="57"/>
       <x:c r="O2" s="57"/>
@@ -14428,32 +14473,38 @@
       <x:c r="U2" s="57"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="41" t="s">
-        <x:v>49</x:v>
+      <x:c r="A4" s="41" t="str">
+        <x:v>Active Campaigns</x:v>
       </x:c>
       <x:c r="B4" s="41"/>
       <x:c r="C4" s="41"/>
-      <x:c r="D4" s="41"/>
-      <x:c r="E4" s="41" t="s">
-        <x:v>4</x:v>
+      <x:c r="D4" s="41" t="str">
+        <x:v>End Date Not Stated</x:v>
+      </x:c>
+      <x:c r="E4" s="41" t="str">
+        <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="F4" s="41"/>
-      <x:c r="G4" s="41"/>
+      <x:c r="G4" s="41" t="str">
+        <x:v>Remittance Campaigns</x:v>
+      </x:c>
       <x:c r="H4" s="41"/>
-      <x:c r="I4" s="43" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="J4" s="43"/>
+      <x:c r="I4" s="43" t="str">
+        <x:v>Remittance Campaigns</x:v>
+      </x:c>
+      <x:c r="J4" s="43" t="str">
+        <x:v>Expiring ≤30d</x:v>
+      </x:c>
       <x:c r="K4" s="43"/>
       <x:c r="L4" s="43"/>
-      <x:c r="M4" s="44" t="s">
-        <x:v>6</x:v>
+      <x:c r="M4" s="44" t="str">
+        <x:v>Merchant Offers (Count Only): 0</x:v>
       </x:c>
       <x:c r="N4" s="44"/>
       <x:c r="O4" s="44"/>
       <x:c r="P4" s="44"/>
-      <x:c r="Q4" s="41" t="s">
-        <x:v>7</x:v>
+      <x:c r="Q4" s="41" t="str">
+        <x:v>Expiring ≤30d</x:v>
       </x:c>
       <x:c r="R4" s="41"/>
       <x:c r="S4" s="41"/>
@@ -14461,36 +14512,44 @@
     </x:row>
     <x:row r="5" ht="23">
       <x:c r="A5" s="53" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant")</x:f>
+        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;")</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="B5" s="53"/>
       <x:c r="C5" s="53"/>
-      <x:c r="D5" s="53"/>
+      <x:c r="D5" s="53" t="n">
+        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$I$9:$I$500,"End Date Not Stated")</x:f>
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="E5" s="53" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
-        <x:v>5</x:v>
+        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$I$9:$I$500,"End Date Not Stated")</x:f>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="53"/>
-      <x:c r="G5" s="53"/>
+      <x:c r="G5" s="53" t="n">
+        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"Remittance")</x:f>
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="H5" s="53"/>
       <x:c r="I5" s="54" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"&lt;&gt;Expired",'alinma pay'!$B$9:$B$500,"Remittance")</x:f>
+        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"Remittance")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J5" s="54"/>
+      <x:c r="J5" s="54" t="n">
+        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$I$9:$I$500,"Expiring ≤7 Days")+COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="K5" s="54"/>
       <x:c r="L5" s="54"/>
       <x:c r="M5" s="55" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"Merchant",'alinma pay'!$I$9:$I$500,"&lt;&gt;Expired")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N5" s="55"/>
       <x:c r="O5" s="55"/>
       <x:c r="P5" s="55"/>
       <x:c r="Q5" s="53" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"Expiring ≤7 Days")+COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"&lt;&gt;Merchant",'alinma pay'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
-        <x:v>1</x:v>
+        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$I$9:$I$500,"Expiring ≤7 Days")+COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="R5" s="53"/>
       <x:c r="S5" s="53"/>
@@ -14498,67 +14557,67 @@
     </x:row>
     <x:row r="8" ht="30.649999618530273" customHeight="1">
       <x:c r="A8" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H8" s="3" t="s">
-        <x:v>56</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I8" s="3" t="s">
-        <x:v>57</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="J8" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K8" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L8" s="3" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="M8" s="3" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="N8" s="3" t="s">
-        <x:v>62</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O8" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="P8" s="3" t="s">
-        <x:v>64</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="Q8" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
-        <x:v>66</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="S8" s="3" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="T8" s="3" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="U8" s="34" t="s">
-        <x:v>69</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="T8" s="3" t="str">
+        <x:v>Social Post Count</x:v>
+      </x:c>
+      <x:c r="U8" s="34" t="str">
+        <x:v>Published Platforms</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="46.650001525878906" customHeight="1">
@@ -14567,13 +14626,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>329</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>330</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E9" s="5"/>
       <x:c r="F9" s="5">
@@ -14584,20 +14643,20 @@
       </x:c>
       <x:c r="H9" s="7" t="n">
         <x:f t="shared" ref="H9:H42" si="1">IF(OR(C9="",G9=""),"",G9-TODAY())</x:f>
-        <x:v>1</x:v>
+        <x:v>-19</x:v>
       </x:c>
       <x:c r="I9" s="6" t="str">
         <x:f t="shared" ref="I9:I42" si="2">IF(C9="","",IF(G9="","End Date Not Stated",IF(G9&lt;TODAY(),"Expired",IF(G9&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G9&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
-        <x:v>Expiring ≤7 Days</x:v>
+        <x:v>Expired</x:v>
       </x:c>
       <x:c r="J9" s="4" t="s">
-        <x:v>331</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="K9" s="4" t="s">
-        <x:v>332</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="L9" s="4" t="s">
-        <x:v>333</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:f t="shared" ref="M9:M42" si="3">IF(C9="","",IF(N9&lt;&gt;"",N9,IF(O9&lt;&gt;"",O9,IF(P9&lt;&gt;"",P9,IF(Q9&lt;&gt;"",Q9,IF(R9&lt;&gt;"",R9,""))))))</x:f>
@@ -14605,17 +14664,17 @@
       </x:c>
       <x:c r="N9" s="4"/>
       <x:c r="O9" s="63" t="s">
-        <x:v>334</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="P9" s="4" t="s">
-        <x:v>335</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="Q9" s="63" t="s">
-        <x:v>336</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="R9" s="4"/>
       <x:c r="S9" s="4" t="s">
-        <x:v>337</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="T9" s="5" t="n">
         <x:v>46240</x:v>
@@ -14631,10 +14690,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>338</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="D10" s="4" t="str">
         <x:v>Use alinma pay Cashback Cards internationally with no foreign transaction fees, no fees on the first two international cash withdrawals, and cashback on eligible purchases.</x:v>
@@ -14656,7 +14715,7 @@
         <x:v>Zero international transaction fees, first two international cash withdrawals free, plus cashback on eligible purchases</x:v>
       </x:c>
       <x:c r="L10" s="4" t="s">
-        <x:v>339</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="M10" s="9" t="str">
         <x:f t="shared" si="3">IF(C10="","",IF(N10&lt;&gt;"",N10,IF(O10&lt;&gt;"",O10,IF(P10&lt;&gt;"",P10,IF(Q10&lt;&gt;"",Q10,IF(R10&lt;&gt;"",R10,""))))))</x:f>
@@ -14666,7 +14725,7 @@
       <x:c r="O10" s="4"/>
       <x:c r="P10" s="4"/>
       <x:c r="Q10" s="63" t="s">
-        <x:v>340</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="R10" s="4"/>
       <x:c r="S10" s="4" t="str">
@@ -14686,13 +14745,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
-        <x:v>341</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>342</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5"/>
@@ -14705,13 +14764,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
-        <x:v>343</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="K11" s="4" t="s">
-        <x:v>344</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="L11" s="4" t="s">
-        <x:v>345</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:f t="shared" si="3">IF(C11="","",IF(N11&lt;&gt;"",N11,IF(O11&lt;&gt;"",O11,IF(P11&lt;&gt;"",P11,IF(Q11&lt;&gt;"",Q11,IF(R11&lt;&gt;"",R11,""))))))</x:f>
@@ -14719,17 +14778,17 @@
       </x:c>
       <x:c r="N11" s="4"/>
       <x:c r="O11" s="63" t="s">
-        <x:v>346</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="P11" s="4" t="s">
-        <x:v>347</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="Q11" s="63" t="s">
-        <x:v>348</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="R11" s="4"/>
       <x:c r="S11" s="4" t="s">
-        <x:v>349</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="T11" s="5" t="n">
         <x:v>46240</x:v>
@@ -14745,13 +14804,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>350</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>351</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="E12" s="5">
         <x:v>46068</x:v>
@@ -14766,13 +14825,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J12" s="4" t="s">
-        <x:v>352</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="K12" s="4" t="s">
-        <x:v>353</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="L12" s="4" t="s">
-        <x:v>354</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
         <x:f t="shared" si="3">IF(C12="","",IF(N12&lt;&gt;"",N12,IF(O12&lt;&gt;"",O12,IF(P12&lt;&gt;"",P12,IF(Q12&lt;&gt;"",Q12,IF(R12&lt;&gt;"",R12,""))))))</x:f>
@@ -14782,11 +14841,11 @@
       <x:c r="O12" s="4"/>
       <x:c r="P12" s="4"/>
       <x:c r="Q12" s="63" t="s">
-        <x:v>355</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="R12" s="4"/>
       <x:c r="S12" s="4" t="s">
-        <x:v>214</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="T12" s="5" t="n">
         <x:v>46240</x:v>
@@ -15894,7 +15953,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0978fa95d2494467"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f406d3836b54fc3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15915,7 +15974,7 @@
   <x:sheetData>
     <x:row r="1" ht="21.5">
       <x:c r="A1" s="58" t="s">
-        <x:v>356</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B1" s="58"/>
       <x:c r="C1" s="58"/>
@@ -15926,8 +15985,8 @@
       <x:c r="H1" s="58"/>
     </x:row>
     <x:row r="2" ht="22.649999618530273" customHeight="1">
-      <x:c r="A2" s="59" t="s">
-        <x:v>357</x:v>
+      <x:c r="A2" s="59" t="str">
+        <x:v>Active approved campaigns are listed newest first. Expired campaigns are excluded. Merchant offers appear only as a count in each competitor sheet.</x:v>
       </x:c>
       <x:c r="B2" s="59"/>
       <x:c r="C2" s="59"/>
@@ -15939,119 +15998,119 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="26" t="s">
-        <x:v>358</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B4" s="26" t="s">
-        <x:v>359</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C4" s="26" t="s">
-        <x:v>360</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="D4" s="26" t="s">
-        <x:v>361</x:v>
+        <x:v>319</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="38.650001525878906" customHeight="1">
       <x:c r="A5" s="27" t="s">
-        <x:v>15</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B5" s="27" t="s">
-        <x:v>362</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C5" s="27" t="s">
-        <x:v>363</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="D5" s="27" t="s">
-        <x:v>364</x:v>
+        <x:v>322</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="38.650001525878906" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>362</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>365</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>366</x:v>
+        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="38.650001525878906" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>362</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>367</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>368</x:v>
+        <x:v>326</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="38.650001525878906" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>362</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C8" s="4" t="s">
-        <x:v>369</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>370</x:v>
+        <x:v>328</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="38.650001525878906" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>362</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>371</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>372</x:v>
+        <x:v>330</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="38.650001525878906" customHeight="1">
       <x:c r="A10" s="28" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B10" s="28" t="s">
-        <x:v>373</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C10" s="28" t="s">
-        <x:v>374</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="D10" s="28" t="s">
-        <x:v>375</x:v>
+        <x:v>333</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="38.650001525878906" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>376</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
-        <x:v>377</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>378</x:v>
+        <x:v>336</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="16.5">
       <x:c r="A14" s="46" t="s">
-        <x:v>379</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B14" s="46"/>
       <x:c r="C14" s="46"/>
@@ -16062,8 +16121,8 @@
       <x:c r="H14" s="46"/>
     </x:row>
     <x:row r="15" ht="22.649999618530273" customHeight="1">
-      <x:c r="A15" s="60" t="s">
-        <x:v>380</x:v>
+      <x:c r="A15" s="60" t="str">
+        <x:v>1. Do not list individual merchant offers as campaign rows; retain only the approved active count for each competitor.</x:v>
       </x:c>
       <x:c r="B15" s="60"/>
       <x:c r="C15" s="60"/>
@@ -16074,8 +16133,8 @@
       <x:c r="H15" s="60"/>
     </x:row>
     <x:row r="16" ht="22.649999618530273" customHeight="1">
-      <x:c r="A16" s="61" t="s">
-        <x:v>381</x:v>
+      <x:c r="A16" s="61" t="str">
+        <x:v>2. Exclude expired, inactive, or unapproved merchant offers from the displayed count.</x:v>
       </x:c>
       <x:c r="B16" s="61"/>
       <x:c r="C16" s="61"/>
@@ -16086,8 +16145,8 @@
       <x:c r="H16" s="61"/>
     </x:row>
     <x:row r="17" ht="22.649999618530273" customHeight="1">
-      <x:c r="A17" s="60" t="s">
-        <x:v>382</x:v>
+      <x:c r="A17" s="60" t="str">
+        <x:v>3. Show the merchant-offer count only in the relevant competitor sheet; exclude it from Dashboard campaign KPIs and charts.</x:v>
       </x:c>
       <x:c r="B17" s="60"/>
       <x:c r="C17" s="60"/>
@@ -16098,8 +16157,8 @@
       <x:c r="H17" s="60"/>
     </x:row>
     <x:row r="18" ht="22.649999618530273" customHeight="1">
-      <x:c r="A18" s="61" t="s">
-        <x:v>383</x:v>
+      <x:c r="A18" s="61" t="str">
+        <x:v>4. Count a merchant activation as a campaign only when it has a coordinated objective, defined audience, dedicated timing, communication plan, and measurable campaign KPI.</x:v>
       </x:c>
       <x:c r="B18" s="61"/>
       <x:c r="C18" s="61"/>
@@ -16110,8 +16169,8 @@
       <x:c r="H18" s="61"/>
     </x:row>
     <x:row r="19" ht="22.649999618530273" customHeight="1">
-      <x:c r="A19" s="60" t="s">
-        <x:v>384</x:v>
+      <x:c r="A19" s="60" t="str">
+        <x:v>5. This convention prevents individual partner discounts from inflating campaign volume.</x:v>
       </x:c>
       <x:c r="B19" s="60"/>
       <x:c r="C19" s="60"/>
@@ -16125,7 +16184,7 @@
     <x:row r="21" ht="36.650001525878906" customHeight="1"/>
     <x:row r="22" ht="36.650001525878906" customHeight="1">
       <x:c r="A22" s="45" t="s">
-        <x:v>385</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B22" s="45"/>
       <x:c r="C22" s="45"/>
@@ -16138,139 +16197,139 @@
     <x:row r="23" ht="32" customHeight="1"/>
     <x:row r="24" ht="32" customHeight="1">
       <x:c r="A24" s="21" t="s">
-        <x:v>386</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B24" s="21" t="s">
-        <x:v>387</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D24" s="29" t="s">
-        <x:v>388</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="E24" s="29" t="s">
-        <x:v>389</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="F24" s="29" t="s">
-        <x:v>390</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="G24" s="29" t="s">
-        <x:v>391</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="H24" s="29" t="s">
-        <x:v>392</x:v>
+        <x:v>345</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="46.650001525878906" customHeight="1">
       <x:c r="A25" s="1" t="s">
-        <x:v>393</x:v>
-      </x:c>
-      <x:c r="B25" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="str">
+        <x:v>Campaign rows are populated automatically from approved monitoring data.</x:v>
       </x:c>
       <x:c r="D25" s="4" t="s">
-        <x:v>395</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="E25" s="4" t="s">
-        <x:v>396</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="F25" s="4" t="s">
-        <x:v>397</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="G25" s="4" t="s">
-        <x:v>398</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="H25" s="4" t="s">
-        <x:v>399</x:v>
+        <x:v>351</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="46.650001525878906" customHeight="1">
       <x:c r="A26" s="1" t="s">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="B26" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="str">
+        <x:v>Merchant offers are shown only as an active approved count in each competitor sheet.</x:v>
       </x:c>
       <x:c r="D26" s="4" t="s">
-        <x:v>402</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="E26" s="4" t="s">
-        <x:v>403</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="F26" s="4" t="s">
-        <x:v>404</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="G26" s="4" t="s">
-        <x:v>405</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="H26" s="4" t="s">
-        <x:v>406</x:v>
+        <x:v>357</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="46.650001525878906" customHeight="1">
       <x:c r="A27" s="1" t="s">
-        <x:v>407</x:v>
-      </x:c>
-      <x:c r="B27" s="1" t="s">
-        <x:v>408</x:v>
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="str">
+        <x:v>Use Remittance for all international-transfer campaigns; these rows are highlighted automatically.</x:v>
       </x:c>
       <x:c r="D27" s="4" t="s">
-        <x:v>409</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="E27" s="4" t="s">
-        <x:v>410</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="F27" s="4" t="s">
-        <x:v>411</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="G27" s="4" t="s">
-        <x:v>412</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="H27" s="4" t="s">
-        <x:v>413</x:v>
+        <x:v>363</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="30.649999618530273" customHeight="1">
       <x:c r="A28" s="1" t="s">
-        <x:v>414</x:v>
-      </x:c>
-      <x:c r="B28" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="str">
+        <x:v>Each listed campaign must retain a direct official campaign page or confirmed official social source.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="30.649999618530273" customHeight="1">
       <x:c r="A29" s="1" t="s">
-        <x:v>416</x:v>
-      </x:c>
-      <x:c r="B29" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="str">
+        <x:v>Expired campaigns are excluded; leave End Date blank only when the official source does not state it.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="30.649999618530273" customHeight="1">
       <x:c r="A30" s="1" t="s">
-        <x:v>418</x:v>
-      </x:c>
-      <x:c r="B30" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="str">
+        <x:v>Campaigns are sorted newest first using Start Date, Published Date, and detection date.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="30.649999618530273" customHeight="1">
       <x:c r="A31" s="1" t="s">
-        <x:v>420</x:v>
-      </x:c>
-      <x:c r="B31" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="str">
+        <x:v>Dashboard campaign KPIs, category mix, remittance analysis, and the 14-day social Bar Chart update automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="30.649999618530273" customHeight="1">
       <x:c r="A32" s="1" t="s">
-        <x:v>422</x:v>
-      </x:c>
-      <x:c r="B32" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="str">
+        <x:v>Social Post Count includes confirmed posts linked to the campaign; Published Platforms lists the relevant channels.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22.649999618530273" customHeight="1">
-      <x:c r="A34" s="62" t="s">
-        <x:v>424</x:v>
+      <x:c r="A34" s="62" t="str">
+        <x:v>The Social Media Activity Bar Chart counts unique direct official posts published during the latest 14-day window.</x:v>
       </x:c>
       <x:c r="B34" s="62"/>
       <x:c r="C34" s="62"/>

--- a/competitor_campaigns_template.xlsx
+++ b/competitor_campaigns_template.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Dashboard" sheetId="1" r:id="R8bfa44e4a7c742be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STC Bank" sheetId="2" r:id="R2e06e46aab874d7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="barq" sheetId="3" r:id="Ra56fd28c908b435e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobily Pay" sheetId="4" r:id="R94fc1ecd33504839"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tiqmo" sheetId="5" r:id="Rc405098af46c4d0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="urpay" sheetId="6" r:id="R78cbdb297ae84077"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="alinma pay" sheetId="7" r:id="Rf9268759951b465c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Guide" sheetId="8" r:id="Rb7478ae8afe54542"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Dashboard" sheetId="1" r:id="R93a0e4df54b04dc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STC Bank" sheetId="2" r:id="R0f4b2a310a5d4cbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="barq" sheetId="3" r:id="Rccaebdff65664c1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobily Pay" sheetId="4" r:id="Rd395576924ac4b0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tiqmo" sheetId="5" r:id="R6462069155004c18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="urpay" sheetId="6" r:id="Rd4613b455b3d4e0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="alinma pay" sheetId="7" r:id="Rf6067ccee45942f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Guide" sheetId="8" r:id="R9cd53a35de31429f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,12 +17,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t xml:space="preserve">STC Bank | barq | Mobily Pay | tiqmo | urpay | alinma pay</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Status Calculated As Of</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">STC Bank – Verified Campaign Inventory</x:t>
   </x:si>
   <x:si>
@@ -1131,12 +1125,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="5">
     <x:numFmt numFmtId="164" formatCode="mmmm\ d\,\ yyyy"/>
     <x:numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <x:numFmt numFmtId="200" formatCode="0%"/>
+    <x:numFmt numFmtId="201" formatCode="mmm d, yyyy"/>
+    <x:numFmt numFmtId="202" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="21">
+  <x:fonts count="29">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -1252,8 +1248,52 @@
       <x:color rgb="FF1F4E78"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF183247"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="18"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos Display"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FFD8EAF2"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF64798B"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF183247"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="19"/>
+      <x:color rgb="FF183247"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:sz val="7"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="27">
+  <x:fills count="43">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -1385,16 +1425,194 @@
         <x:fgColor rgb="FFB4C7E7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF12314A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F7F9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2D72A4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE9F3F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F7C83"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9A62E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFBF2D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF12314A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F7F9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2D72A4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE9F3F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F7C83"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9A62E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFBF2D6"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="12">
     <x:border/>
     <x:border/>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF2D72A4"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FF2D72A4"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF2D72A4"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF2D72A4"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF2D72A4"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF2D72A4"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8E2E8"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD8E2E8"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD8E2E8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD8E2E8"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8E2E8"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E2E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD8E2E8"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E2E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF0F7C83"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FF0F7C83"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF0F7C83"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF0F7C83"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF0F7C83"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF0F7C83"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9A62E"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD9A62E"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9A62E"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9A62E"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9A62E"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9A62E"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="130">
+  <x:cellXfs count="290">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -1773,6 +1991,314 @@
     <x:xf numFmtId="200" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="21" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="21" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="24" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="24" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="24" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="30" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="30" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="30" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="31" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="31" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="31" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="31" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="31" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="31" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="31" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="31" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="31" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="31" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="31" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="31" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="31" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="31" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="31" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="31" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="32" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="32" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="32" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="32" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="32" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="32" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="34" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="34" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="34" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="34" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="34" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="34" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="34" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="34" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="34" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="34" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="34" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="34" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="34" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="34" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="34" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="34" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="21" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="21" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="24" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="24" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="24" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="38" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="38" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="38" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="38" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="38" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="38" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="39" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="39" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="39" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="39" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="39" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="39" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="39" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="39" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="39" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="39" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="39" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="39" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="39" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="39" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="39" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="39" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="40" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="40" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="40" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="40" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="40" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="40" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="42" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="42" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="42" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="42" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="42" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="42" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="42" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="42" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="27" fillId="42" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="42" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="42" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="42" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="42" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="42" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="42" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="27" fillId="42" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Hyperlink" xfId="1"/>
@@ -2765,7 +3291,6 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -2774,556 +3299,22 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:t>Current Campaign Mix (Merchant Excluded)</a:t>
+              <a:rPr sz="900"/>
+              <a:t>Active Campaigns by Competitor</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
       <c:overlay val="0"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>Market Count</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Executive Dashboard'!$X$19:$X$24</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>Remittance</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Musaned</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>SADAD</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Card</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Engagement</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Other</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Executive Dashboard'!$Y$19:$Y$24</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:axId val="48650112"/>
-        <c:axId val="48672768"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="48650112"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="48672768"/>
-        <c:crosses val="autoZero"/>
-        <c:lblOffset val="100"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="48672768"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="48650112"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-  </c:chart>
-  <c:spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </c:spPr>
-</c:chartSpace>
-</file>
-
-<file path=xl/drawings/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <c:style val="2"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:r>
-              <a:t>Remittance Campaign Focus</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>Remittance Campaigns</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Executive Dashboard'!$X$31:$X$36</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>STC Bank</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>barq</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Mobily Pay</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>tiqmo</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>urpay</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>alinma pay</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Executive Dashboard'!$Y$31:$Y$36</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:axId val="48650112"/>
-        <c:axId val="48672768"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="48650112"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="48672768"/>
-        <c:crosses val="autoZero"/>
-        <c:lblOffset val="100"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="48672768"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="48650112"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-  </c:chart>
-  <c:spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </c:spPr>
-</c:chartSpace>
-</file>
-
-<file path=xl/drawings/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" mc:Ignorable="c14">
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent>
-    <mc:Choice Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:plotArea>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Executive Dashboard'!$B$9</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Current Campaigns</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Executive Dashboard'!$A$10:$A$15</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>STC Bank</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>barq</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Mobily Pay</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>tiqmo</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>urpay</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>alinma pay</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Executive Dashboard'!$B$10:$B$15</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="ctr"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="79"/>
-        <c:axId val="48650112"/>
-        <c:axId val="48672768"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="48650112"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cmpd="sng">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cmpd="sng">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" vert="horz" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="800" b="0" i="0" u="none" cap="all">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-lt"/>
-                <a:cs typeface="+mn-lt"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="48672768"/>
-        <c:crosses val="autoZero"/>
-        <c:lblOffset val="100"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="48672768"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="48650112"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="t"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-      </c:spPr>
       <c:txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" vert="horz" anchor="ctr" anchorCtr="1"/>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
         <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-lt"/>
-              <a:cs typeface="+mn-lt"/>
-            </a:defRPr>
+            <a:defRPr sz="900"/>
           </a:pPr>
         </a:p>
       </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:schemeClr val="lt1"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cmpd="sng">
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-</c:chartSpace>
-</file>
-
-<file path=xl/drawings/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:r>
-              <a:t>Social Media Activity — Last 14 Days</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
     </c:title>
     <c:plotArea>
       <c:barChart>
@@ -3333,11 +3324,16 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Instagram</c:v>
+            <c:v>Active Campaigns</c:v>
           </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2D72A4"/>
+            </a:solidFill>
+          </c:spPr>
           <c:cat>
             <c:strRef>
-              <c:f>'Executive Dashboard'!$A$54:$A$59</c:f>
+              <c:f>'Executive Dashboard'!$X$2:$X$7</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -3345,81 +3341,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Executive Dashboard'!$B$54:$B$59</c:f>
+              <c:f>'Executive Dashboard'!$Y$2:$Y$7</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="0"/>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>X</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Executive Dashboard'!$A$54:$A$59</c:f>
-              <c:strCache>
-                <c:ptCount val="0"/>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Executive Dashboard'!$C$54:$C$59</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="0"/>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:v>Facebook</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Executive Dashboard'!$A$54:$A$59</c:f>
-              <c:strCache>
-                <c:ptCount val="0"/>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Executive Dashboard'!$D$54:$D$59</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="0"/>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:v>TikTok</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Executive Dashboard'!$A$54:$A$59</c:f>
-              <c:strCache>
-                <c:ptCount val="0"/>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Executive Dashboard'!$E$54:$E$59</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="0"/>
               </c:numCache>
             </c:numRef>
@@ -3468,7 +3392,418 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
+        <c:numFmt formatCode="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:rPr sz="900"/>
+              <a:t>Active Campaign Mix</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900"/>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:plotArea>
+      <c:doughnutChart>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Campaigns</c:v>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Executive Dashboard'!$AD$2:$AD$7</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Executive Dashboard'!$AE$2:$AE$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+      </c:doughnutChart>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:rPr sz="900"/>
+              <a:t>Remittance Campaigns by Competitor</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900"/>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Remittance Campaigns</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="D9A62E"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Executive Dashboard'!$AA$2:$AA$7</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Executive Dashboard'!$AB$2:$AB$7</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48672768"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:rPr sz="900"/>
+              <a:t>Social Media Activity — Last 14 Days</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900"/>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Instagram</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="287E9B"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Executive Dashboard'!$X$12:$X$17</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Executive Dashboard'!$Y$12:$Y$17</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>X</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="E8732A"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Executive Dashboard'!$X$12:$X$17</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Executive Dashboard'!$Z$12:$Z$17</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Facebook</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="3B8B6B"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Executive Dashboard'!$X$12:$X$17</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Executive Dashboard'!$AA$12:$AA$17</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>TikTok</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="5A78B8"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Executive Dashboard'!$X$12:$X$17</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Executive Dashboard'!$AB$12:$AB$17</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48672768"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:crossAx val="48650112"/>
@@ -3496,16 +3831,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>328447</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>547414</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>142328</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3518,7 +3853,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R77f37ecfa86a4725"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rec83b2805158415e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3527,15 +3862,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>317500</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>613103</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>153276</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3548,7 +3883,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R189a839208b44784"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R78fe1c7190874992"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3556,16 +3891,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>193782</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>10948</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>54740</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>164224</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3578,7 +3913,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rae770279fed9449d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7361499901e04baa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3586,15 +3921,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3608,7 +3943,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4d5300143ead441a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3c903b4bd7cd4313"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3940,1424 +4275,1255 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="14"/>
   <x:cols>
-    <x:col min="1" max="1" width="18.75" customWidth="1"/>
-    <x:col min="2" max="2" width="20.75" customWidth="1"/>
-    <x:col min="3" max="3" width="22.5" customWidth="1"/>
-    <x:col min="4" max="4" width="16.1640625" customWidth="1"/>
-    <x:col min="5" max="5" width="26.9140625" customWidth="1"/>
-    <x:col min="6" max="6" width="14.33203125" customWidth="1"/>
-    <x:col min="7" max="7" width="26" customWidth="1"/>
-    <x:col min="8" max="8" width="12" customWidth="1"/>
+    <x:col min="1" max="1" width="11.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11.5" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="3.200000047683716" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.5" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="11.5" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="3.200000047683716" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11.5" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="11.5" hidden="0" customWidth="1"/>
     <x:col min="9" max="11" width="15" customWidth="1"/>
-    <x:col min="12" max="12" width="14" customWidth="1"/>
-    <x:col min="13" max="13" width="16" customWidth="1"/>
-    <x:col min="14" max="14" width="24" customWidth="1"/>
+    <x:col min="12" max="12" width="3.200000047683716" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="11.5" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="11.5" hidden="0" customWidth="1"/>
     <x:col min="24" max="25" width="2" customWidth="1"/>
+    <x:col min="10" max="10" width="11.5" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="11.5" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="3.200000047683716" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="2" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="2" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="2" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="2" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="2" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="2" hidden="0" customWidth="1"/>
+    <x:col min="30" max="30" width="2" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="2" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="38" t="str">
-        <x:v>Competitor Intelligence Campaign Dashboard</x:v>
-      </x:c>
-      <x:c r="B1" s="38"/>
-      <x:c r="C1" s="38"/>
-      <x:c r="D1" s="38"/>
-      <x:c r="E1" s="38"/>
-      <x:c r="F1" s="38"/>
-      <x:c r="G1" s="38"/>
-      <x:c r="H1" s="38"/>
-      <x:c r="I1" s="38"/>
-      <x:c r="J1" s="38"/>
-      <x:c r="K1" s="38"/>
-      <x:c r="L1" s="38"/>
-      <x:c r="M1" s="38"/>
-      <x:c r="N1" s="38"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="39" t="s">
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="215" t="str">
+        <x:v>Competitor Analysis Dashboard</x:v>
+      </x:c>
+      <x:c r="B1" s="215"/>
+      <x:c r="C1" s="215"/>
+      <x:c r="D1" s="215"/>
+      <x:c r="E1" s="215"/>
+      <x:c r="F1" s="215"/>
+      <x:c r="G1" s="215"/>
+      <x:c r="H1" s="215"/>
+      <x:c r="I1" s="215"/>
+      <x:c r="J1" s="215"/>
+      <x:c r="K1" s="215"/>
+      <x:c r="L1" s="215"/>
+      <x:c r="M1" s="215"/>
+      <x:c r="N1" s="215"/>
+      <x:c r="X1" s="289" t="str">
+        <x:v>Competitor</x:v>
+      </x:c>
+      <x:c r="Y1" s="289" t="str">
+        <x:v>Active Campaigns</x:v>
+      </x:c>
+      <x:c r="AA1" s="289" t="str">
+        <x:v>Competitor</x:v>
+      </x:c>
+      <x:c r="AB1" s="289" t="str">
+        <x:v>Remittance Campaigns</x:v>
+      </x:c>
+      <x:c r="AD1" s="289" t="str">
+        <x:v>Category</x:v>
+      </x:c>
+      <x:c r="AE1" s="289" t="str">
+        <x:v>Campaigns</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="20" customHeight="1">
+      <x:c r="A2" s="218" t="str">
+        <x:v>Active campaigns, campaign mix, remittance focus and verified social activity</x:v>
+      </x:c>
+      <x:c r="B2" s="218"/>
+      <x:c r="C2" s="218"/>
+      <x:c r="D2" s="218"/>
+      <x:c r="E2" s="218"/>
+      <x:c r="F2" s="218"/>
+      <x:c r="G2" s="218"/>
+      <x:c r="H2" s="218"/>
+      <x:c r="I2" s="218"/>
+      <x:c r="J2" s="218"/>
+      <x:c r="K2" s="218"/>
+      <x:c r="L2" s="218"/>
+      <x:c r="M2" s="218"/>
+      <x:c r="N2" s="218"/>
+      <x:c r="X2" s="289" t="str">
+        <x:v>STC Bank</x:v>
+      </x:c>
+      <x:c r="Y2" s="289" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="AA2" s="289" t="str">
+        <x:v>STC Bank</x:v>
+      </x:c>
+      <x:c r="AB2" s="289" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD2" s="289" t="str">
+        <x:v>Remittance</x:v>
+      </x:c>
+      <x:c r="AE2" s="289" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="226" t="str">
+        <x:v>Research Cut-off</x:v>
+      </x:c>
+      <x:c r="B3" s="227" t="n">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C3" s="227"/>
+      <x:c r="D3" s="227"/>
+      <x:c r="E3" s="228" t="str">
+        <x:v>Merchant offers excluded from Dashboard KPIs</x:v>
+      </x:c>
+      <x:c r="F3" s="228"/>
+      <x:c r="G3" s="228"/>
+      <x:c r="H3" s="228"/>
+      <x:c r="I3" s="228"/>
+      <x:c r="J3" s="226" t="str">
+        <x:v>Status As Of</x:v>
+      </x:c>
+      <x:c r="K3" s="227" t="n">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="L3" s="227"/>
+      <x:c r="M3" s="227"/>
+      <x:c r="N3" s="227"/>
+      <x:c r="X3" s="289" t="str">
+        <x:v>barq</x:v>
+      </x:c>
+      <x:c r="Y3" s="289" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AA3" s="289" t="str">
+        <x:v>barq</x:v>
+      </x:c>
+      <x:c r="AB3" s="289" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AD3" s="289" t="str">
+        <x:v>Musaned</x:v>
+      </x:c>
+      <x:c r="AE3" s="289" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="19" customHeight="1">
+      <x:c r="A4" s="211"/>
+      <x:c r="B4" s="211"/>
+      <x:c r="C4" s="211"/>
+      <x:c r="D4" s="211"/>
+      <x:c r="E4" s="211"/>
+      <x:c r="F4" s="211"/>
+      <x:c r="G4" s="211"/>
+      <x:c r="H4" s="211"/>
+      <x:c r="I4" s="211"/>
+      <x:c r="J4" s="211"/>
+      <x:c r="K4" s="211"/>
+      <x:c r="L4" s="211"/>
+      <x:c r="M4" s="211"/>
+      <x:c r="N4" s="211"/>
+      <x:c r="X4" s="289" t="str">
+        <x:v>Mobily Pay</x:v>
+      </x:c>
+      <x:c r="Y4" s="289" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AA4" s="289" t="str">
+        <x:v>Mobily Pay</x:v>
+      </x:c>
+      <x:c r="AB4" s="289" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AD4" s="289" t="str">
+        <x:v>SADAD</x:v>
+      </x:c>
+      <x:c r="AE4" s="289" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="19" customHeight="1">
+      <x:c r="A5" s="235" t="str">
+        <x:v>Active Campaigns</x:v>
+      </x:c>
+      <x:c r="B5" s="236"/>
+      <x:c r="C5" s="211"/>
+      <x:c r="D5" s="261" t="str">
+        <x:v>Remittance Campaigns</x:v>
+      </x:c>
+      <x:c r="E5" s="262"/>
+      <x:c r="F5" s="211"/>
+      <x:c r="G5" s="269" t="str">
+        <x:v>Social Posts — 14 Days</x:v>
+      </x:c>
+      <x:c r="H5" s="270"/>
+      <x:c r="I5" s="211"/>
+      <x:c r="J5" s="235" t="str">
+        <x:v>Expiring ≤30 Days</x:v>
+      </x:c>
+      <x:c r="K5" s="236"/>
+      <x:c r="L5" s="211"/>
+      <x:c r="M5" s="261" t="str">
+        <x:v>Competitors</x:v>
+      </x:c>
+      <x:c r="N5" s="262"/>
+      <x:c r="X5" s="289" t="str">
+        <x:v>tiqmo</x:v>
+      </x:c>
+      <x:c r="Y5" s="289" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AA5" s="289" t="str">
+        <x:v>tiqmo</x:v>
+      </x:c>
+      <x:c r="AB5" s="289" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AD5" s="289" t="str">
+        <x:v>Card</x:v>
+      </x:c>
+      <x:c r="AE5" s="289" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="19" customHeight="1">
+      <x:c r="A6" s="251" t="n">
+        <x:f>SUM($Y$2:$Y$7)</x:f>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B6" s="252"/>
+      <x:c r="C6" s="211"/>
+      <x:c r="D6" s="251" t="n">
+        <x:f>SUM($AB$2:$AB$7)</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E6" s="252"/>
+      <x:c r="F6" s="211"/>
+      <x:c r="G6" s="285" t="n">
+        <x:f>SUM($Y$12:$AB$17)</x:f>
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="H6" s="286"/>
+      <x:c r="I6" s="211"/>
+      <x:c r="J6" s="251" t="n">
+        <x:f>$AE$12</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K6" s="252"/>
+      <x:c r="L6" s="211"/>
+      <x:c r="M6" s="251" t="n">
+        <x:f>COUNTA($X$2:$X$7)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N6" s="252"/>
+      <x:c r="X6" s="289" t="str">
+        <x:v>urpay</x:v>
+      </x:c>
+      <x:c r="Y6" s="289" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AA6" s="289" t="str">
+        <x:v>urpay</x:v>
+      </x:c>
+      <x:c r="AB6" s="289" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD6" s="289" t="str">
+        <x:v>Engagement</x:v>
+      </x:c>
+      <x:c r="AE6" s="289" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="19" customHeight="1">
+      <x:c r="A7" s="253"/>
+      <x:c r="B7" s="254"/>
+      <x:c r="C7" s="211"/>
+      <x:c r="D7" s="253"/>
+      <x:c r="E7" s="254"/>
+      <x:c r="F7" s="211"/>
+      <x:c r="G7" s="287"/>
+      <x:c r="H7" s="288"/>
+      <x:c r="I7" s="211"/>
+      <x:c r="J7" s="253"/>
+      <x:c r="K7" s="254"/>
+      <x:c r="L7" s="211"/>
+      <x:c r="M7" s="253"/>
+      <x:c r="N7" s="254"/>
+      <x:c r="X7" s="289" t="str">
+        <x:v>alinma pay</x:v>
+      </x:c>
+      <x:c r="Y7" s="289" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="AA7" s="289" t="str">
+        <x:v>alinma pay</x:v>
+      </x:c>
+      <x:c r="AB7" s="289" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AD7" s="289" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="AE7" s="289" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="19" customHeight="1">
+      <x:c r="A8" s="211"/>
+      <x:c r="B8" s="211"/>
+      <x:c r="C8" s="211"/>
+      <x:c r="D8" s="211"/>
+      <x:c r="E8" s="211"/>
+      <x:c r="F8" s="211"/>
+      <x:c r="G8" s="211"/>
+      <x:c r="H8" s="211"/>
+      <x:c r="I8" s="211"/>
+      <x:c r="J8" s="211"/>
+      <x:c r="K8" s="211"/>
+      <x:c r="L8" s="211"/>
+      <x:c r="M8" s="211"/>
+      <x:c r="N8" s="211"/>
+    </x:row>
+    <x:row r="9" ht="19" customHeight="1">
+      <x:c r="A9" s="211"/>
+      <x:c r="B9" s="211"/>
+      <x:c r="C9" s="211"/>
+      <x:c r="D9" s="211"/>
+      <x:c r="E9" s="211"/>
+      <x:c r="F9" s="211"/>
+      <x:c r="G9" s="211"/>
+      <x:c r="H9" s="211"/>
+      <x:c r="I9" s="211"/>
+      <x:c r="J9" s="211"/>
+      <x:c r="K9" s="211"/>
+      <x:c r="L9" s="211"/>
+      <x:c r="M9" s="211"/>
+      <x:c r="N9" s="211"/>
+    </x:row>
+    <x:row r="10" ht="19" customHeight="1">
+      <x:c r="A10" s="211"/>
+      <x:c r="B10" s="211"/>
+      <x:c r="C10" s="211"/>
+      <x:c r="D10" s="211"/>
+      <x:c r="E10" s="211"/>
+      <x:c r="F10" s="211"/>
+      <x:c r="G10" s="211"/>
+      <x:c r="H10" s="211"/>
+      <x:c r="I10" s="211"/>
+      <x:c r="J10" s="211"/>
+      <x:c r="K10" s="211"/>
+      <x:c r="L10" s="211"/>
+      <x:c r="M10" s="211"/>
+      <x:c r="N10" s="211"/>
+    </x:row>
+    <x:row r="11" ht="19" customHeight="1">
+      <x:c r="A11" s="211"/>
+      <x:c r="B11" s="211"/>
+      <x:c r="C11" s="211"/>
+      <x:c r="D11" s="211"/>
+      <x:c r="E11" s="211"/>
+      <x:c r="F11" s="211"/>
+      <x:c r="G11" s="211"/>
+      <x:c r="H11" s="211"/>
+      <x:c r="I11" s="211"/>
+      <x:c r="J11" s="211"/>
+      <x:c r="K11" s="211"/>
+      <x:c r="L11" s="211"/>
+      <x:c r="M11" s="211"/>
+      <x:c r="N11" s="211"/>
+      <x:c r="X11" s="289" t="str">
+        <x:v>Competitor</x:v>
+      </x:c>
+      <x:c r="Y11" s="289" t="str">
+        <x:v>Instagram</x:v>
+      </x:c>
+      <x:c r="Z11" s="289" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="AA11" s="289" t="str">
+        <x:v>Facebook</x:v>
+      </x:c>
+      <x:c r="AB11" s="289" t="str">
+        <x:v>TikTok</x:v>
+      </x:c>
+      <x:c r="AD11" s="289" t="str">
+        <x:v>Metric</x:v>
+      </x:c>
+      <x:c r="AE11" s="289" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="19" customHeight="1">
+      <x:c r="A12" s="211"/>
+      <x:c r="B12" s="211"/>
+      <x:c r="C12" s="211"/>
+      <x:c r="D12" s="211"/>
+      <x:c r="E12" s="211"/>
+      <x:c r="F12" s="211"/>
+      <x:c r="G12" s="211"/>
+      <x:c r="H12" s="211"/>
+      <x:c r="I12" s="211"/>
+      <x:c r="J12" s="211"/>
+      <x:c r="K12" s="211"/>
+      <x:c r="L12" s="211"/>
+      <x:c r="M12" s="211"/>
+      <x:c r="N12" s="211"/>
+      <x:c r="X12" s="289" t="str">
+        <x:v>STC Bank</x:v>
+      </x:c>
+      <x:c r="Y12" s="289" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Z12" s="289" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="AA12" s="289" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AB12" s="289" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AD12" s="289" t="str">
+        <x:v>Expiring ≤30 Days</x:v>
+      </x:c>
+      <x:c r="AE12" s="289" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="19" customHeight="1">
+      <x:c r="A13" s="211"/>
+      <x:c r="B13" s="211"/>
+      <x:c r="C13" s="211"/>
+      <x:c r="D13" s="211"/>
+      <x:c r="E13" s="211"/>
+      <x:c r="F13" s="211"/>
+      <x:c r="G13" s="211"/>
+      <x:c r="H13" s="211"/>
+      <x:c r="I13" s="211"/>
+      <x:c r="J13" s="211"/>
+      <x:c r="K13" s="211"/>
+      <x:c r="L13" s="211"/>
+      <x:c r="M13" s="211"/>
+      <x:c r="N13" s="211"/>
+      <x:c r="X13" s="289" t="str">
+        <x:v>barq</x:v>
+      </x:c>
+      <x:c r="Y13" s="289" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Z13" s="289" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AA13" s="289" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="AB13" s="289" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="19" customHeight="1">
+      <x:c r="A14" s="211"/>
+      <x:c r="B14" s="211"/>
+      <x:c r="C14" s="211"/>
+      <x:c r="D14" s="211"/>
+      <x:c r="E14" s="211"/>
+      <x:c r="F14" s="211"/>
+      <x:c r="G14" s="211"/>
+      <x:c r="H14" s="211"/>
+      <x:c r="I14" s="211"/>
+      <x:c r="J14" s="211"/>
+      <x:c r="K14" s="211"/>
+      <x:c r="L14" s="211"/>
+      <x:c r="M14" s="211"/>
+      <x:c r="N14" s="211"/>
+      <x:c r="X14" s="289" t="str">
+        <x:v>Mobily Pay</x:v>
+      </x:c>
+      <x:c r="Y14" s="289" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="Z14" s="289" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="AA14" s="289" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="AB14" s="289" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="19" customHeight="1">
+      <x:c r="A15" s="211"/>
+      <x:c r="B15" s="211"/>
+      <x:c r="C15" s="211"/>
+      <x:c r="D15" s="211"/>
+      <x:c r="E15" s="211"/>
+      <x:c r="F15" s="211"/>
+      <x:c r="G15" s="211"/>
+      <x:c r="H15" s="211"/>
+      <x:c r="I15" s="211"/>
+      <x:c r="J15" s="211"/>
+      <x:c r="K15" s="211"/>
+      <x:c r="L15" s="211"/>
+      <x:c r="M15" s="211"/>
+      <x:c r="N15" s="211"/>
+      <x:c r="X15" s="289" t="str">
+        <x:v>tiqmo</x:v>
+      </x:c>
+      <x:c r="Y15" s="289" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Z15" s="289" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="AA15" s="289" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="AB15" s="289" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B2" s="39"/>
-      <x:c r="C2" s="39"/>
-      <x:c r="D2" s="39"/>
-      <x:c r="E2" s="39"/>
-      <x:c r="F2" s="39"/>
-      <x:c r="G2" s="39"/>
-      <x:c r="H2" s="39"/>
-      <x:c r="I2" s="39"/>
-      <x:c r="J2" s="39"/>
-      <x:c r="K2" s="39"/>
-      <x:c r="L2" s="39"/>
-      <x:c r="M2" s="39"/>
-      <x:c r="N2" s="39"/>
-    </x:row>
-    <x:row r="3" ht="28" customHeight="1">
-      <x:c r="A3" s="10" t="str">
-        <x:v>Research Cut-off</x:v>
-      </x:c>
-      <x:c r="B3" s="11" t="n">
-        <x:v>46240</x:v>
-      </x:c>
-      <x:c r="C3" s="10"/>
-      <x:c r="D3" s="10" t="s">
+    </x:row>
+    <x:row r="16" ht="19" customHeight="1">
+      <x:c r="A16" s="211"/>
+      <x:c r="B16" s="211"/>
+      <x:c r="C16" s="211"/>
+      <x:c r="D16" s="211"/>
+      <x:c r="E16" s="211"/>
+      <x:c r="F16" s="211"/>
+      <x:c r="G16" s="211"/>
+      <x:c r="H16" s="211"/>
+      <x:c r="I16" s="211"/>
+      <x:c r="J16" s="211"/>
+      <x:c r="K16" s="211"/>
+      <x:c r="L16" s="211"/>
+      <x:c r="M16" s="211"/>
+      <x:c r="N16" s="211"/>
+      <x:c r="X16" s="289" t="str">
+        <x:v>urpay</x:v>
+      </x:c>
+      <x:c r="Y16" s="289" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Z16" s="289" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="AA16" s="289" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="AB16" s="289" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="19" customHeight="1">
+      <x:c r="A17" s="211"/>
+      <x:c r="B17" s="211"/>
+      <x:c r="C17" s="211"/>
+      <x:c r="D17" s="211"/>
+      <x:c r="E17" s="211"/>
+      <x:c r="F17" s="211"/>
+      <x:c r="G17" s="211"/>
+      <x:c r="H17" s="211"/>
+      <x:c r="I17" s="211"/>
+      <x:c r="J17" s="211"/>
+      <x:c r="K17" s="211"/>
+      <x:c r="L17" s="211"/>
+      <x:c r="M17" s="211"/>
+      <x:c r="N17" s="211"/>
+      <x:c r="X17" s="289" t="str">
+        <x:v>alinma pay</x:v>
+      </x:c>
+      <x:c r="Y17" s="289" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Z17" s="289" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="AA17" s="289" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="AB17" s="289" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E3" s="11" t="n">
-        <x:f>TODAY()</x:f>
-        <x:v>46260</x:v>
-      </x:c>
-      <x:c r="F3" s="10"/>
-      <x:c r="G3" s="40" t="str">
-        <x:v>Dashboard includes active approved campaigns only. Merchant offers are excluded and shown only as a count in each competitor sheet.</x:v>
-      </x:c>
-      <x:c r="H3" s="40"/>
-      <x:c r="I3" s="40"/>
-      <x:c r="J3" s="40"/>
-      <x:c r="K3" s="40"/>
-      <x:c r="L3" s="40"/>
-      <x:c r="M3" s="40"/>
-      <x:c r="N3" s="40"/>
-    </x:row>
-    <x:row r="5" ht="17.399999618530273" customHeight="1">
-      <x:c r="A5" s="12" t="str">
-        <x:v>Current Campaigns</x:v>
-      </x:c>
-      <x:c r="B5" s="12"/>
-      <x:c r="C5" s="14" t="str">
-        <x:v>Remittance Campaigns</x:v>
-      </x:c>
-      <x:c r="D5" s="14"/>
-      <x:c r="E5" s="16" t="str">
-        <x:v>Social Posts — Last 14 Days</x:v>
-      </x:c>
-      <x:c r="F5" s="16"/>
-      <x:c r="G5" s="12" t="str">
-        <x:v>Expiring Campaigns ≤30d</x:v>
-      </x:c>
-      <x:c r="H5" s="12"/>
-      <x:c r="I5" s="41" t="str">
-        <x:v>Competitors Tracked</x:v>
-      </x:c>
-      <x:c r="J5" s="41"/>
-    </x:row>
-    <x:row r="6" ht="25.399999618530273" customHeight="1">
-      <x:c r="A6" s="13" t="n">
-        <x:f>SUM(B10:B15)</x:f>
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B6" s="13"/>
-      <x:c r="C6" s="15" t="n">
-        <x:f>SUM(G10:G15)</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D6" s="15"/>
-      <x:c r="E6" s="17" t="n">
-        <x:f>SUM(F54:F59)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F6" s="17"/>
-      <x:c r="G6" s="13" t="n">
-        <x:f>SUM(E10:F15)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H6" s="13"/>
-      <x:c r="I6" s="42" t="n">
-        <x:f>COUNTA(A10:A15)</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="J6" s="42"/>
-    </x:row>
-    <x:row r="9" ht="30.649999618530273" customHeight="1">
-      <x:c r="A9" s="18" t="str">
-        <x:v>Competitor</x:v>
-      </x:c>
-      <x:c r="B9" s="18" t="str">
-        <x:v>Current Campaigns</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="str">
-        <x:v>Active &gt;30d</x:v>
-      </x:c>
-      <x:c r="D9" s="18" t="str">
-        <x:v>End Date Not Stated</x:v>
-      </x:c>
-      <x:c r="E9" s="18" t="str">
-        <x:v>Expiring ≤7d</x:v>
-      </x:c>
-      <x:c r="F9" s="18" t="str">
-        <x:v>Expiring 8–30d</x:v>
-      </x:c>
-      <x:c r="G9" s="18" t="str">
-        <x:v>Remittance</x:v>
-      </x:c>
-      <x:c r="H9" s="19" t="str">
-        <x:v>Musaned</x:v>
-      </x:c>
-      <x:c r="I9" s="18" t="str">
-        <x:v>SADAD</x:v>
-      </x:c>
-      <x:c r="J9" s="18" t="str">
-        <x:v>Card</x:v>
-      </x:c>
-      <x:c r="K9" s="18" t="str">
-        <x:v>Engagement</x:v>
-      </x:c>
-      <x:c r="L9" s="18" t="str">
-        <x:v>Other</x:v>
-      </x:c>
-      <x:c r="M9" s="18" t="str">
-        <x:v>Social Posts (14d)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="28" customHeight="1">
-      <x:c r="A10" s="2" t="str">
-        <x:v>STC Bank</x:v>
-      </x:c>
-      <x:c r="B10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$M$9:$M$500,"&lt;&gt;")</x:f>
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$I$9:$I$500,"Active")</x:f>
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$I$9:$I$500,"End Date Not Stated")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$I$9:$I$500,"Expiring ≤7 Days")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"Remittance")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H10" s="20" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"Musaned")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"SADAD")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"Card")</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="K10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"Engagement")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L10" s="2" t="n">
-        <x:f>COUNTIFS('STC Bank'!$C$9:$C$500,"&lt;&gt;",'STC Bank'!$B$9:$B$500,"Other")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M10" s="2" t="n">
-        <x:f>F54</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="28" customHeight="1">
-      <x:c r="A11" s="2" t="str">
-        <x:v>barq</x:v>
-      </x:c>
-      <x:c r="B11" s="2" t="n">
-        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$M$9:$M$500,"&lt;&gt;")</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="2" t="n">
-        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$I$9:$I$500,"Active")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D11" s="2" t="n">
-        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$I$9:$I$500,"End Date Not Stated")</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E11" s="2" t="n">
-        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$I$9:$I$500,"Expiring ≤7 Days")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F11" s="2" t="n">
-        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="2" t="n">
-        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$B$9:$B$500,"Remittance")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H11" s="20" t="n">
-        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$B$9:$B$500,"Musaned")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I11" s="2" t="n">
-        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$B$9:$B$500,"SADAD")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J11" s="2" t="n">
-        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$B$9:$B$500,"Card")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K11" s="2" t="n">
-        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$B$9:$B$500,"Engagement")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L11" s="2" t="n">
-        <x:f>COUNTIFS('barq'!$C$9:$C$500,"&lt;&gt;",'barq'!$B$9:$B$500,"Other")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M11" s="2" t="n">
-        <x:f>F55</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="28" customHeight="1">
-      <x:c r="A12" s="2" t="str">
-        <x:v>Mobily Pay</x:v>
-      </x:c>
-      <x:c r="B12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$M$9:$M$500,"&lt;&gt;")</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$I$9:$I$500,"Active")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$I$9:$I$500,"End Date Not Stated")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$I$9:$I$500,"Expiring ≤7 Days")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"Remittance")</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H12" s="20" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"Musaned")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"SADAD")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"Card")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"Engagement")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L12" s="2" t="n">
-        <x:f>COUNTIFS('Mobily Pay'!$C$9:$C$500,"&lt;&gt;",'Mobily Pay'!$B$9:$B$500,"Other")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M12" s="2" t="n">
-        <x:f>F56</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="28" customHeight="1">
-      <x:c r="A13" s="2" t="str">
-        <x:v>tiqmo</x:v>
-      </x:c>
-      <x:c r="B13" s="2" t="n">
-        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$M$9:$M$500,"&lt;&gt;")</x:f>
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C13" s="2" t="n">
-        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$I$9:$I$500,"Active")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="2" t="n">
-        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$I$9:$I$500,"End Date Not Stated")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E13" s="2" t="n">
-        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$I$9:$I$500,"Expiring ≤7 Days")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F13" s="2" t="n">
-        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="2" t="n">
-        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$B$9:$B$500,"Remittance")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H13" s="20" t="n">
-        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$B$9:$B$500,"Musaned")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I13" s="2" t="n">
-        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$B$9:$B$500,"SADAD")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J13" s="2" t="n">
-        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$B$9:$B$500,"Card")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K13" s="2" t="n">
-        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$B$9:$B$500,"Engagement")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L13" s="2" t="n">
-        <x:f>COUNTIFS('tiqmo'!$C$9:$C$500,"&lt;&gt;",'tiqmo'!$B$9:$B$500,"Other")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M13" s="2" t="n">
-        <x:f>F57</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="28" customHeight="1">
-      <x:c r="A14" s="2" t="str">
-        <x:v>urpay</x:v>
-      </x:c>
-      <x:c r="B14" s="2" t="n">
-        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$M$9:$M$500,"&lt;&gt;")</x:f>
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C14" s="2" t="n">
-        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$I$9:$I$500,"Active")</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D14" s="2" t="n">
-        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$I$9:$I$500,"End Date Not Stated")</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E14" s="2" t="n">
-        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$I$9:$I$500,"Expiring ≤7 Days")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F14" s="2" t="n">
-        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="2" t="n">
-        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$B$9:$B$500,"Remittance")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="20" t="n">
-        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$B$9:$B$500,"Musaned")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I14" s="2" t="n">
-        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$B$9:$B$500,"SADAD")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J14" s="2" t="n">
-        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$B$9:$B$500,"Card")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K14" s="2" t="n">
-        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$B$9:$B$500,"Engagement")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L14" s="2" t="n">
-        <x:f>COUNTIFS('urpay'!$C$9:$C$500,"&lt;&gt;",'urpay'!$B$9:$B$500,"Other")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M14" s="2" t="n">
-        <x:f>F58</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="28" customHeight="1">
-      <x:c r="A15" s="2" t="str">
-        <x:v>alinma pay</x:v>
-      </x:c>
-      <x:c r="B15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$M$9:$M$500,"&lt;&gt;")</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$I$9:$I$500,"Active")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$I$9:$I$500,"End Date Not Stated")</x:f>
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$I$9:$I$500,"Expiring ≤7 Days")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$I$9:$I$500,"Expiring 8–30 Days")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"Remittance")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H15" s="20" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"Musaned")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"SADAD")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"Card")</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"Engagement")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L15" s="2" t="n">
-        <x:f>COUNTIFS('alinma pay'!$C$9:$C$500,"&lt;&gt;",'alinma pay'!$B$9:$B$500,"Other")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M15" s="2" t="n">
-        <x:f>F59</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="16.5">
-      <x:c r="A18" s="45" t="str">
-        <x:v>Active Campaign Count by Category — Merchant Offers Excluded</x:v>
-      </x:c>
-      <x:c r="B18" s="45"/>
-      <x:c r="C18" s="45"/>
-      <x:c r="D18" s="45"/>
-      <x:c r="E18" s="45"/>
-      <x:c r="F18" s="45"/>
-      <x:c r="G18" s="45"/>
-      <x:c r="H18" s="45"/>
-      <x:c r="I18" s="45"/>
-      <x:c r="J18" s="45"/>
-      <x:c r="K18" s="45"/>
-      <x:c r="L18" s="45"/>
-      <x:c r="M18" s="45"/>
-      <x:c r="N18" s="45"/>
-      <x:c r="X18" s="30" t="str">
-        <x:v>Campaign Category</x:v>
-      </x:c>
-      <x:c r="Y18" s="30" t="str">
-        <x:v>Market Count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="X19" s="30" t="str">
-        <x:f>B20</x:f>
-        <x:v>Remittance</x:v>
-      </x:c>
-      <x:c r="Y19" s="30" t="n">
-        <x:f>B27</x:f>
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="26.649999618530273" customHeight="1">
-      <x:c r="A20" s="22" t="str">
-        <x:v>Competitor</x:v>
-      </x:c>
-      <x:c r="B20" s="19" t="str">
-        <x:v>Remittance</x:v>
-      </x:c>
-      <x:c r="C20" s="22" t="str">
-        <x:v>Musaned</x:v>
-      </x:c>
-      <x:c r="D20" s="22" t="str">
-        <x:v>SADAD</x:v>
-      </x:c>
-      <x:c r="E20" s="22" t="str">
-        <x:v>Card</x:v>
-      </x:c>
-      <x:c r="F20" s="22" t="str">
-        <x:v>Engagement</x:v>
-      </x:c>
-      <x:c r="G20" s="22" t="str">
-        <x:v>Other</x:v>
-      </x:c>
-      <x:c r="X20" s="30" t="str">
-        <x:f>C20</x:f>
-        <x:v>Musaned</x:v>
-      </x:c>
-      <x:c r="Y20" s="30" t="n">
-        <x:f>C27</x:f>
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="25" t="str">
-        <x:v>STC Bank</x:v>
-      </x:c>
-      <x:c r="B21" s="24" t="n">
-        <x:f>G10</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C21" s="25" t="n">
-        <x:f>H10</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D21" s="25" t="n">
-        <x:f>I10</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E21" s="25" t="n">
-        <x:f>J10</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F21" s="25" t="n">
-        <x:f>K10</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G21" s="25" t="n">
-        <x:f>L10</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X21" s="30" t="str">
-        <x:f>D20</x:f>
-        <x:v>SADAD</x:v>
-      </x:c>
-      <x:c r="Y21" s="30" t="n">
-        <x:f>D27</x:f>
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="25" t="str">
-        <x:v>barq</x:v>
-      </x:c>
-      <x:c r="B22" s="24" t="n">
-        <x:f>G11</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C22" s="25" t="n">
-        <x:f>H11</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D22" s="25" t="n">
-        <x:f>I11</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E22" s="25" t="n">
-        <x:f>J11</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F22" s="25" t="n">
-        <x:f>K11</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G22" s="25" t="n">
-        <x:f>L11</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X22" s="30" t="str">
-        <x:f>E20</x:f>
-        <x:v>Card</x:v>
-      </x:c>
-      <x:c r="Y22" s="30" t="n">
-        <x:f>E27</x:f>
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="25" t="str">
-        <x:v>Mobily Pay</x:v>
-      </x:c>
-      <x:c r="B23" s="24" t="n">
-        <x:f>G12</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C23" s="25" t="n">
-        <x:f>H12</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D23" s="25" t="n">
-        <x:f>I12</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E23" s="25" t="n">
-        <x:f>J12</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F23" s="25" t="n">
-        <x:f>K12</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="25" t="n">
-        <x:f>L12</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X23" s="30" t="str">
-        <x:f>F20</x:f>
-        <x:v>Engagement</x:v>
-      </x:c>
-      <x:c r="Y23" s="30" t="n">
-        <x:f>F27</x:f>
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="25" t="str">
-        <x:v>tiqmo</x:v>
-      </x:c>
-      <x:c r="B24" s="24" t="n">
-        <x:f>G13</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C24" s="25" t="n">
-        <x:f>H13</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D24" s="25" t="n">
-        <x:f>I13</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E24" s="25" t="n">
-        <x:f>J13</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F24" s="25" t="n">
-        <x:f>K13</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="25" t="n">
-        <x:f>L13</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X24" s="30" t="str">
-        <x:f>G20</x:f>
-        <x:v>Other</x:v>
-      </x:c>
-      <x:c r="Y24" s="30" t="n">
-        <x:f>G27</x:f>
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="25" t="str">
-        <x:v>urpay</x:v>
-      </x:c>
-      <x:c r="B25" s="24" t="n">
-        <x:f>G14</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C25" s="25" t="n">
-        <x:f>H14</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D25" s="25" t="n">
-        <x:f>I14</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E25" s="25" t="n">
-        <x:f>J14</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F25" s="25" t="n">
-        <x:f>K14</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="25" t="n">
-        <x:f>L14</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X25" s="30"/>
-      <x:c r="Y25" s="30"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="25" t="str">
-        <x:v>alinma pay</x:v>
-      </x:c>
-      <x:c r="B26" s="24" t="n">
-        <x:f>G15</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C26" s="25" t="n">
-        <x:f>H15</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D26" s="25" t="n">
-        <x:f>I15</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E26" s="25" t="n">
-        <x:f>J15</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F26" s="25" t="n">
-        <x:f>K15</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="25" t="n">
-        <x:f>L15</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X26" s="30"/>
-      <x:c r="Y26" s="30"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="23" t="str">
-        <x:v>Market Total</x:v>
-      </x:c>
-      <x:c r="B27" s="24" t="n">
+    </x:row>
+    <x:row r="18" ht="19" customHeight="1">
+      <x:c r="A18" s="211"/>
+      <x:c r="B18" s="211"/>
+      <x:c r="C18" s="211"/>
+      <x:c r="D18" s="211"/>
+      <x:c r="E18" s="211"/>
+      <x:c r="F18" s="211"/>
+      <x:c r="G18" s="211"/>
+      <x:c r="H18" s="211"/>
+      <x:c r="I18" s="211"/>
+      <x:c r="J18" s="211"/>
+      <x:c r="K18" s="211"/>
+      <x:c r="L18" s="211"/>
+      <x:c r="M18" s="211"/>
+      <x:c r="N18" s="211"/>
+      <x:c r="X18"/>
+      <x:c r="Y18"/>
+    </x:row>
+    <x:row r="19" ht="19" customHeight="1">
+      <x:c r="A19" s="211"/>
+      <x:c r="B19" s="211"/>
+      <x:c r="C19" s="211"/>
+      <x:c r="D19" s="211"/>
+      <x:c r="E19" s="211"/>
+      <x:c r="F19" s="211"/>
+      <x:c r="G19" s="211"/>
+      <x:c r="H19" s="211"/>
+      <x:c r="I19" s="211"/>
+      <x:c r="J19" s="211"/>
+      <x:c r="K19" s="211"/>
+      <x:c r="L19" s="211"/>
+      <x:c r="M19" s="211"/>
+      <x:c r="N19" s="211"/>
+      <x:c r="X19"/>
+      <x:c r="Y19"/>
+    </x:row>
+    <x:row r="20" ht="19" customHeight="1">
+      <x:c r="A20" s="211"/>
+      <x:c r="B20" s="211"/>
+      <x:c r="C20" s="211"/>
+      <x:c r="D20" s="211"/>
+      <x:c r="E20" s="211"/>
+      <x:c r="F20" s="211"/>
+      <x:c r="G20" s="211"/>
+      <x:c r="H20" s="211"/>
+      <x:c r="I20" s="211"/>
+      <x:c r="J20" s="211"/>
+      <x:c r="K20" s="211"/>
+      <x:c r="L20" s="211"/>
+      <x:c r="M20" s="211"/>
+      <x:c r="N20" s="211"/>
+      <x:c r="X20"/>
+      <x:c r="Y20"/>
+    </x:row>
+    <x:row r="21" ht="19" customHeight="1">
+      <x:c r="A21" s="211"/>
+      <x:c r="B21" s="211"/>
+      <x:c r="C21" s="211"/>
+      <x:c r="D21" s="211"/>
+      <x:c r="E21" s="211"/>
+      <x:c r="F21" s="211"/>
+      <x:c r="G21" s="211"/>
+      <x:c r="H21" s="211"/>
+      <x:c r="I21" s="211"/>
+      <x:c r="J21" s="211"/>
+      <x:c r="K21" s="211"/>
+      <x:c r="L21" s="211"/>
+      <x:c r="M21" s="211"/>
+      <x:c r="N21" s="211"/>
+      <x:c r="X21"/>
+      <x:c r="Y21"/>
+    </x:row>
+    <x:row r="22" ht="19" customHeight="1">
+      <x:c r="A22" s="211"/>
+      <x:c r="B22" s="211"/>
+      <x:c r="C22" s="211"/>
+      <x:c r="D22" s="211"/>
+      <x:c r="E22" s="211"/>
+      <x:c r="F22" s="211"/>
+      <x:c r="G22" s="211"/>
+      <x:c r="H22" s="211"/>
+      <x:c r="I22" s="211"/>
+      <x:c r="J22" s="211"/>
+      <x:c r="K22" s="211"/>
+      <x:c r="L22" s="211"/>
+      <x:c r="M22" s="211"/>
+      <x:c r="N22" s="211"/>
+      <x:c r="X22"/>
+      <x:c r="Y22"/>
+    </x:row>
+    <x:row r="23" ht="19" customHeight="1">
+      <x:c r="A23" s="211"/>
+      <x:c r="B23" s="211"/>
+      <x:c r="C23" s="211"/>
+      <x:c r="D23" s="211"/>
+      <x:c r="E23" s="211"/>
+      <x:c r="F23" s="211"/>
+      <x:c r="G23" s="211"/>
+      <x:c r="H23" s="211"/>
+      <x:c r="I23" s="211"/>
+      <x:c r="J23" s="211"/>
+      <x:c r="K23" s="211"/>
+      <x:c r="L23" s="211"/>
+      <x:c r="M23" s="211"/>
+      <x:c r="N23" s="211"/>
+      <x:c r="X23"/>
+      <x:c r="Y23"/>
+    </x:row>
+    <x:row r="24" ht="19" customHeight="1">
+      <x:c r="A24" s="211"/>
+      <x:c r="B24" s="211"/>
+      <x:c r="C24" s="211"/>
+      <x:c r="D24" s="211"/>
+      <x:c r="E24" s="211"/>
+      <x:c r="F24" s="211"/>
+      <x:c r="G24" s="211"/>
+      <x:c r="H24" s="211"/>
+      <x:c r="I24" s="211"/>
+      <x:c r="J24" s="211"/>
+      <x:c r="K24" s="211"/>
+      <x:c r="L24" s="211"/>
+      <x:c r="M24" s="211"/>
+      <x:c r="N24" s="211"/>
+      <x:c r="X24"/>
+      <x:c r="Y24"/>
+    </x:row>
+    <x:row r="25" ht="19" customHeight="1">
+      <x:c r="A25" s="211"/>
+      <x:c r="B25" s="211"/>
+      <x:c r="C25" s="211"/>
+      <x:c r="D25" s="211"/>
+      <x:c r="E25" s="211"/>
+      <x:c r="F25" s="211"/>
+      <x:c r="G25" s="211"/>
+      <x:c r="H25" s="211"/>
+      <x:c r="I25" s="211"/>
+      <x:c r="J25" s="211"/>
+      <x:c r="K25" s="211"/>
+      <x:c r="L25" s="211"/>
+      <x:c r="M25" s="211"/>
+      <x:c r="N25" s="211"/>
+      <x:c r="X25"/>
+      <x:c r="Y25"/>
+    </x:row>
+    <x:row r="26" ht="19" customHeight="1">
+      <x:c r="A26" s="211"/>
+      <x:c r="B26" s="211"/>
+      <x:c r="C26" s="211"/>
+      <x:c r="D26" s="211"/>
+      <x:c r="E26" s="211"/>
+      <x:c r="F26" s="211"/>
+      <x:c r="G26" s="211"/>
+      <x:c r="H26" s="211"/>
+      <x:c r="I26" s="211"/>
+      <x:c r="J26" s="211"/>
+      <x:c r="K26" s="211"/>
+      <x:c r="L26" s="211"/>
+      <x:c r="M26" s="211"/>
+      <x:c r="N26" s="211"/>
+      <x:c r="X26"/>
+      <x:c r="Y26"/>
+    </x:row>
+    <x:row r="27" ht="19" customHeight="1">
+      <x:c r="A27" s="211"/>
+      <x:c r="B27" s="211">
         <x:f t="shared" ref="B27:G27" si="0">SUM(B21:B26)</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C27" s="23" t="n">
-        <x:f t="shared" si="0">SUM(C21:C26)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D27" s="23" t="n">
-        <x:f t="shared" si="0">SUM(D21:D26)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E27" s="23" t="n">
-        <x:f t="shared" si="0">SUM(E21:E26)</x:f>
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F27" s="23" t="n">
-        <x:f t="shared" si="0">SUM(F21:F26)</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G27" s="23" t="n">
-        <x:f t="shared" si="0">SUM(G21:G26)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="X27" s="30"/>
-      <x:c r="Y27" s="30"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="X28" s="30"/>
-      <x:c r="Y28" s="30"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="X29" s="30"/>
-      <x:c r="Y29" s="30"/>
-    </x:row>
-    <x:row r="30" ht="16.5">
-      <x:c r="A30" s="46" t="str">
-        <x:v>Active Remittance Campaigns by Competitor</x:v>
-      </x:c>
-      <x:c r="B30" s="46"/>
-      <x:c r="C30" s="46"/>
-      <x:c r="D30" s="46"/>
-      <x:c r="E30" s="46"/>
-      <x:c r="F30" s="46"/>
-      <x:c r="G30" s="46"/>
-      <x:c r="H30" s="46"/>
-      <x:c r="I30" s="46"/>
-      <x:c r="J30" s="46"/>
-      <x:c r="K30" s="46"/>
-      <x:c r="L30" s="46"/>
-      <x:c r="M30" s="46"/>
-      <x:c r="N30" s="46"/>
-      <x:c r="X30" s="30" t="str">
-        <x:v>Competitor</x:v>
-      </x:c>
-      <x:c r="Y30" s="30" t="str">
-        <x:v>Remittance Campaigns</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="20" customHeight="1">
-      <x:c r="X31" s="30" t="str">
+      </x:c>
+      <x:c r="C27" s="211">
+        <x:f t="shared" si="0"/>
+      </x:c>
+      <x:c r="D27" s="211">
+        <x:f t="shared" si="0"/>
+      </x:c>
+      <x:c r="E27" s="211">
+        <x:f t="shared" si="0"/>
+      </x:c>
+      <x:c r="F27" s="211">
+        <x:f t="shared" si="0"/>
+      </x:c>
+      <x:c r="G27" s="211">
+        <x:f t="shared" si="0"/>
+      </x:c>
+      <x:c r="H27" s="211"/>
+      <x:c r="I27" s="211"/>
+      <x:c r="J27" s="211"/>
+      <x:c r="K27" s="211"/>
+      <x:c r="L27" s="211"/>
+      <x:c r="M27" s="211"/>
+      <x:c r="N27" s="211"/>
+      <x:c r="X27"/>
+      <x:c r="Y27"/>
+    </x:row>
+    <x:row r="28" ht="19" customHeight="1">
+      <x:c r="A28" s="211"/>
+      <x:c r="B28" s="211"/>
+      <x:c r="C28" s="211"/>
+      <x:c r="D28" s="211"/>
+      <x:c r="E28" s="211"/>
+      <x:c r="F28" s="211"/>
+      <x:c r="G28" s="211"/>
+      <x:c r="H28" s="211"/>
+      <x:c r="I28" s="211"/>
+      <x:c r="J28" s="211"/>
+      <x:c r="K28" s="211"/>
+      <x:c r="L28" s="211"/>
+      <x:c r="M28" s="211"/>
+      <x:c r="N28" s="211"/>
+      <x:c r="X28"/>
+      <x:c r="Y28"/>
+    </x:row>
+    <x:row r="29" ht="19" customHeight="1">
+      <x:c r="A29" s="211"/>
+      <x:c r="B29" s="211"/>
+      <x:c r="C29" s="211"/>
+      <x:c r="D29" s="211"/>
+      <x:c r="E29" s="211"/>
+      <x:c r="F29" s="211"/>
+      <x:c r="G29" s="211"/>
+      <x:c r="H29" s="211"/>
+      <x:c r="I29" s="211"/>
+      <x:c r="J29" s="211"/>
+      <x:c r="K29" s="211"/>
+      <x:c r="L29" s="211"/>
+      <x:c r="M29" s="211"/>
+      <x:c r="N29" s="211"/>
+      <x:c r="X29"/>
+      <x:c r="Y29"/>
+    </x:row>
+    <x:row r="30" ht="19" customHeight="1">
+      <x:c r="A30" s="211"/>
+      <x:c r="B30" s="211"/>
+      <x:c r="C30" s="211"/>
+      <x:c r="D30" s="211"/>
+      <x:c r="E30" s="211"/>
+      <x:c r="F30" s="211"/>
+      <x:c r="G30" s="211"/>
+      <x:c r="H30" s="211"/>
+      <x:c r="I30" s="211"/>
+      <x:c r="J30" s="211"/>
+      <x:c r="K30" s="211"/>
+      <x:c r="L30" s="211"/>
+      <x:c r="M30" s="211"/>
+      <x:c r="N30" s="211"/>
+      <x:c r="X30"/>
+      <x:c r="Y30"/>
+    </x:row>
+    <x:row r="31" ht="19" customHeight="1">
+      <x:c r="A31" s="211"/>
+      <x:c r="B31" s="211"/>
+      <x:c r="C31" s="211"/>
+      <x:c r="D31" s="211"/>
+      <x:c r="E31" s="211"/>
+      <x:c r="F31" s="211"/>
+      <x:c r="G31" s="211"/>
+      <x:c r="H31" s="211"/>
+      <x:c r="I31" s="211"/>
+      <x:c r="J31" s="211"/>
+      <x:c r="K31" s="211"/>
+      <x:c r="L31" s="211"/>
+      <x:c r="M31" s="211"/>
+      <x:c r="N31" s="211"/>
+      <x:c r="X31">
         <x:f t="shared" ref="X31:X36" si="1">A10</x:f>
-        <x:v>STC Bank</x:v>
-      </x:c>
-      <x:c r="Y31" s="30" t="n">
-        <x:f>G10</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="22.649999618530273" customHeight="1">
-      <x:c r="A32" s="31" t="str">
-        <x:v>Competitor</x:v>
-      </x:c>
-      <x:c r="B32" s="31" t="str">
-        <x:v>Remittance Campaigns</x:v>
-      </x:c>
-      <x:c r="C32" s="31" t="str">
-        <x:v>Share of Current Campaigns</x:v>
-      </x:c>
-      <x:c r="D32" s="31"/>
-      <x:c r="E32" s="31"/>
-      <x:c r="X32" s="30" t="str">
-        <x:f t="shared" si="1"/>
-        <x:v>barq</x:v>
-      </x:c>
-      <x:c r="Y32" s="30" t="n">
-        <x:f>G11</x:f>
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="17.399999618530273" customHeight="1">
-      <x:c r="A33" s="32" t="str">
-        <x:v>STC Bank</x:v>
-      </x:c>
-      <x:c r="B33" s="32" t="n">
-        <x:f>G10</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C33" s="128" t="n">
-        <x:f>IFERROR(B33/B10,0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D33" s="32"/>
-      <x:c r="E33" s="32"/>
-      <x:c r="X33" s="30" t="str">
-        <x:f t="shared" si="1"/>
-        <x:v>Mobily Pay</x:v>
-      </x:c>
-      <x:c r="Y33" s="30" t="n">
-        <x:f>G12</x:f>
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="17.399999618530273" customHeight="1">
-      <x:c r="A34" s="32" t="str">
-        <x:v>barq</x:v>
-      </x:c>
-      <x:c r="B34" s="32" t="n">
-        <x:f>G11</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C34" s="128" t="n">
-        <x:f>IFERROR(B34/B11,0)</x:f>
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
-      <x:c r="D34" s="32"/>
-      <x:c r="E34" s="32"/>
-      <x:c r="X34" s="30" t="str">
-        <x:f t="shared" si="1"/>
-        <x:v>tiqmo</x:v>
-      </x:c>
-      <x:c r="Y34" s="30" t="n">
-        <x:f>G13</x:f>
-        <x:v>2</x:v>
-      </x:c>
+      </x:c>
+      <x:c r="Y31"/>
+    </x:row>
+    <x:row r="32" ht="19" customHeight="1">
+      <x:c r="A32" s="211"/>
+      <x:c r="B32" s="211"/>
+      <x:c r="C32" s="211"/>
+      <x:c r="D32" s="211"/>
+      <x:c r="E32" s="211"/>
+      <x:c r="F32" s="211"/>
+      <x:c r="G32" s="211"/>
+      <x:c r="H32" s="211"/>
+      <x:c r="I32" s="211"/>
+      <x:c r="J32" s="211"/>
+      <x:c r="K32" s="211"/>
+      <x:c r="L32" s="211"/>
+      <x:c r="M32" s="211"/>
+      <x:c r="N32" s="211"/>
+      <x:c r="X32">
+        <x:f t="shared" si="1"/>
+      </x:c>
+      <x:c r="Y32"/>
+    </x:row>
+    <x:row r="33" ht="19" customHeight="1">
+      <x:c r="A33" s="211"/>
+      <x:c r="B33" s="211"/>
+      <x:c r="C33" s="211"/>
+      <x:c r="D33" s="211"/>
+      <x:c r="E33" s="211"/>
+      <x:c r="F33" s="211"/>
+      <x:c r="G33" s="211"/>
+      <x:c r="H33" s="211"/>
+      <x:c r="I33" s="211"/>
+      <x:c r="J33" s="211"/>
+      <x:c r="K33" s="211"/>
+      <x:c r="L33" s="211"/>
+      <x:c r="M33" s="211"/>
+      <x:c r="N33" s="211"/>
+      <x:c r="X33">
+        <x:f t="shared" si="1"/>
+      </x:c>
+      <x:c r="Y33"/>
+    </x:row>
+    <x:row r="34" ht="19" customHeight="1">
+      <x:c r="A34" s="211"/>
+      <x:c r="B34" s="211"/>
+      <x:c r="C34" s="211"/>
+      <x:c r="D34" s="211"/>
+      <x:c r="E34" s="211"/>
+      <x:c r="F34" s="211"/>
+      <x:c r="G34" s="211"/>
+      <x:c r="H34" s="211"/>
+      <x:c r="I34" s="211"/>
+      <x:c r="J34" s="211"/>
+      <x:c r="K34" s="211"/>
+      <x:c r="L34" s="211"/>
+      <x:c r="M34" s="211"/>
+      <x:c r="N34" s="211"/>
+      <x:c r="X34">
+        <x:f t="shared" si="1"/>
+      </x:c>
+      <x:c r="Y34"/>
     </x:row>
     <x:row r="35" ht="17.399999618530273" customHeight="1">
-      <x:c r="A35" s="32" t="str">
-        <x:v>Mobily Pay</x:v>
-      </x:c>
-      <x:c r="B35" s="32" t="n">
-        <x:f>G12</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C35" s="128" t="n">
-        <x:f>IFERROR(B35/B12,0)</x:f>
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="D35" s="32"/>
-      <x:c r="E35" s="32"/>
-      <x:c r="X35" s="30" t="str">
-        <x:f t="shared" si="1"/>
-        <x:v>urpay</x:v>
-      </x:c>
-      <x:c r="Y35" s="30" t="n">
-        <x:f>G14</x:f>
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="A35"/>
+      <x:c r="B35"/>
+      <x:c r="C35"/>
+      <x:c r="D35"/>
+      <x:c r="E35"/>
+      <x:c r="X35">
+        <x:f t="shared" si="1"/>
+      </x:c>
+      <x:c r="Y35"/>
     </x:row>
     <x:row r="36" ht="17.399999618530273" customHeight="1">
-      <x:c r="A36" s="32" t="str">
-        <x:v>tiqmo</x:v>
-      </x:c>
-      <x:c r="B36" s="32" t="n">
-        <x:f>G13</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C36" s="128" t="n">
-        <x:f>IFERROR(B36/B13,0)</x:f>
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
-      <x:c r="D36" s="32"/>
-      <x:c r="E36" s="32"/>
-      <x:c r="X36" s="30" t="str">
-        <x:f t="shared" si="1"/>
-        <x:v>alinma pay</x:v>
-      </x:c>
-      <x:c r="Y36" s="30" t="n">
-        <x:f>G15</x:f>
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A36"/>
+      <x:c r="B36"/>
+      <x:c r="C36"/>
+      <x:c r="D36"/>
+      <x:c r="E36"/>
+      <x:c r="X36">
+        <x:f t="shared" si="1"/>
+      </x:c>
+      <x:c r="Y36"/>
     </x:row>
     <x:row r="37" ht="17.399999618530273" customHeight="1">
-      <x:c r="A37" s="32" t="str">
-        <x:v>urpay</x:v>
-      </x:c>
-      <x:c r="B37" s="32" t="n">
-        <x:f>G14</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C37" s="128" t="n">
-        <x:f>IFERROR(B37/B14,0)</x:f>
-        <x:v>0.1111111111111111</x:v>
-      </x:c>
-      <x:c r="D37" s="32"/>
-      <x:c r="E37" s="32"/>
+      <x:c r="A37"/>
+      <x:c r="B37"/>
+      <x:c r="C37"/>
+      <x:c r="D37"/>
+      <x:c r="E37"/>
     </x:row>
     <x:row r="38" ht="17.399999618530273" customHeight="1">
-      <x:c r="A38" s="32" t="str">
-        <x:v>alinma pay</x:v>
-      </x:c>
-      <x:c r="B38" s="32" t="n">
-        <x:f>G15</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C38" s="128" t="n">
-        <x:f>IFERROR(B38/B15,0)</x:f>
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="D38" s="32"/>
-      <x:c r="E38" s="32"/>
+      <x:c r="A38"/>
+      <x:c r="B38"/>
+      <x:c r="C38"/>
+      <x:c r="D38"/>
+      <x:c r="E38"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="33" t="str">
-        <x:v>Market Total</x:v>
-      </x:c>
-      <x:c r="B39" s="33" t="n">
-        <x:f>SUM(B33:B38)</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C39" s="129" t="n">
-        <x:f>IFERROR(B39/SUM(B10:B15),0)</x:f>
-        <x:v>0.20833333333333334</x:v>
-      </x:c>
-      <x:c r="D39" s="33"/>
-      <x:c r="E39" s="33"/>
+      <x:c r="A39"/>
+      <x:c r="B39"/>
+      <x:c r="C39"/>
+      <x:c r="D39"/>
+      <x:c r="E39"/>
     </x:row>
     <x:row r="42" ht="16.5">
-      <x:c r="A42" s="45" t="str">
-        <x:v>Dynamic Management Signals</x:v>
-      </x:c>
-      <x:c r="B42" s="45"/>
-      <x:c r="C42" s="45"/>
-      <x:c r="D42" s="45"/>
-      <x:c r="E42" s="45"/>
-      <x:c r="F42" s="45"/>
-      <x:c r="G42" s="45"/>
-      <x:c r="H42" s="45"/>
-      <x:c r="I42" s="45"/>
-      <x:c r="J42" s="45"/>
-      <x:c r="K42" s="45"/>
-      <x:c r="L42" s="45"/>
-      <x:c r="M42" s="45"/>
-      <x:c r="N42" s="45"/>
+      <x:c r="A42"/>
+      <x:c r="B42"/>
+      <x:c r="C42"/>
+      <x:c r="D42"/>
+      <x:c r="E42"/>
+      <x:c r="F42"/>
+      <x:c r="G42"/>
+      <x:c r="H42"/>
+      <x:c r="I42"/>
+      <x:c r="J42"/>
+      <x:c r="K42"/>
+      <x:c r="L42"/>
+      <x:c r="M42"/>
+      <x:c r="N42"/>
     </x:row>
     <x:row r="43" ht="20.649999618530273" customHeight="1">
-      <x:c r="A43" s="48" t="str">
-        <x:v>Largest active campaign portfolio is refreshed automatically from the competitor sheets.</x:v>
-      </x:c>
-      <x:c r="B43" s="48"/>
-      <x:c r="C43" s="48"/>
-      <x:c r="D43" s="48"/>
-      <x:c r="E43" s="48"/>
-      <x:c r="F43" s="48"/>
-      <x:c r="G43" s="48"/>
-      <x:c r="H43" s="48"/>
-      <x:c r="I43" s="48"/>
-      <x:c r="J43" s="48"/>
-      <x:c r="K43" s="48"/>
-      <x:c r="L43" s="48"/>
-      <x:c r="M43" s="48"/>
-      <x:c r="N43" s="48"/>
+      <x:c r="A43"/>
+      <x:c r="B43"/>
+      <x:c r="C43"/>
+      <x:c r="D43"/>
+      <x:c r="E43"/>
+      <x:c r="F43"/>
+      <x:c r="G43"/>
+      <x:c r="H43"/>
+      <x:c r="I43"/>
+      <x:c r="J43"/>
+      <x:c r="K43"/>
+      <x:c r="L43"/>
+      <x:c r="M43"/>
+      <x:c r="N43"/>
     </x:row>
     <x:row r="44" ht="20.649999618530273" customHeight="1">
-      <x:c r="A44" s="49" t="str">
-        <x:v>Remittance campaign totals and the market leader are recalculated on every export.</x:v>
-      </x:c>
-      <x:c r="B44" s="49"/>
-      <x:c r="C44" s="49"/>
-      <x:c r="D44" s="49"/>
-      <x:c r="E44" s="49"/>
-      <x:c r="F44" s="49"/>
-      <x:c r="G44" s="49"/>
-      <x:c r="H44" s="49"/>
-      <x:c r="I44" s="49"/>
-      <x:c r="J44" s="49"/>
-      <x:c r="K44" s="49"/>
-      <x:c r="L44" s="49"/>
-      <x:c r="M44" s="49"/>
-      <x:c r="N44" s="49"/>
+      <x:c r="A44"/>
+      <x:c r="B44"/>
+      <x:c r="C44"/>
+      <x:c r="D44"/>
+      <x:c r="E44"/>
+      <x:c r="F44"/>
+      <x:c r="G44"/>
+      <x:c r="H44"/>
+      <x:c r="I44"/>
+      <x:c r="J44"/>
+      <x:c r="K44"/>
+      <x:c r="L44"/>
+      <x:c r="M44"/>
+      <x:c r="N44"/>
     </x:row>
     <x:row r="45" ht="20.649999618530273" customHeight="1">
-      <x:c r="A45" s="49" t="str">
-        <x:v>Remittance share includes active approved campaigns only.</x:v>
-      </x:c>
-      <x:c r="B45" s="49"/>
-      <x:c r="C45" s="49"/>
-      <x:c r="D45" s="49"/>
-      <x:c r="E45" s="49"/>
-      <x:c r="F45" s="49"/>
-      <x:c r="G45" s="49"/>
-      <x:c r="H45" s="49"/>
-      <x:c r="I45" s="49"/>
-      <x:c r="J45" s="49"/>
-      <x:c r="K45" s="49"/>
-      <x:c r="L45" s="49"/>
-      <x:c r="M45" s="49"/>
-      <x:c r="N45" s="49"/>
+      <x:c r="A45"/>
+      <x:c r="B45"/>
+      <x:c r="C45"/>
+      <x:c r="D45"/>
+      <x:c r="E45"/>
+      <x:c r="F45"/>
+      <x:c r="G45"/>
+      <x:c r="H45"/>
+      <x:c r="I45"/>
+      <x:c r="J45"/>
+      <x:c r="K45"/>
+      <x:c r="L45"/>
+      <x:c r="M45"/>
+      <x:c r="N45"/>
     </x:row>
     <x:row r="46" ht="20.649999618530273" customHeight="1">
-      <x:c r="A46" s="50" t="str">
-        <x:v>Social activity covers unique direct official posts published during the latest 14-day window.</x:v>
-      </x:c>
-      <x:c r="B46" s="50"/>
-      <x:c r="C46" s="50"/>
-      <x:c r="D46" s="50"/>
-      <x:c r="E46" s="50"/>
-      <x:c r="F46" s="50"/>
-      <x:c r="G46" s="50"/>
-      <x:c r="H46" s="50"/>
-      <x:c r="I46" s="50"/>
-      <x:c r="J46" s="50"/>
-      <x:c r="K46" s="50"/>
-      <x:c r="L46" s="50"/>
-      <x:c r="M46" s="50"/>
-      <x:c r="N46" s="50"/>
+      <x:c r="A46"/>
+      <x:c r="B46"/>
+      <x:c r="C46"/>
+      <x:c r="D46"/>
+      <x:c r="E46"/>
+      <x:c r="F46"/>
+      <x:c r="G46"/>
+      <x:c r="H46"/>
+      <x:c r="I46"/>
+      <x:c r="J46"/>
+      <x:c r="K46"/>
+      <x:c r="L46"/>
+      <x:c r="M46"/>
+      <x:c r="N46"/>
     </x:row>
     <x:row r="47" ht="20.649999618530273" customHeight="1">
-      <x:c r="A47" s="48" t="str">
-        <x:v>Merchant offers are excluded from Dashboard KPIs and retained only as a count in each competitor sheet.</x:v>
-      </x:c>
-      <x:c r="B47" s="48"/>
-      <x:c r="C47" s="48"/>
-      <x:c r="D47" s="48"/>
-      <x:c r="E47" s="48"/>
-      <x:c r="F47" s="48"/>
-      <x:c r="G47" s="48"/>
-      <x:c r="H47" s="48"/>
-      <x:c r="I47" s="48"/>
-      <x:c r="J47" s="48"/>
-      <x:c r="K47" s="48"/>
-      <x:c r="L47" s="48"/>
-      <x:c r="M47" s="48"/>
-      <x:c r="N47" s="48"/>
+      <x:c r="A47"/>
+      <x:c r="B47"/>
+      <x:c r="C47"/>
+      <x:c r="D47"/>
+      <x:c r="E47"/>
+      <x:c r="F47"/>
+      <x:c r="G47"/>
+      <x:c r="H47"/>
+      <x:c r="I47"/>
+      <x:c r="J47"/>
+      <x:c r="K47"/>
+      <x:c r="L47"/>
+      <x:c r="M47"/>
+      <x:c r="N47"/>
     </x:row>
     <x:row r="48" ht="20.649999618530273" customHeight="1">
-      <x:c r="A48" s="50"/>
-      <x:c r="B48" s="50"/>
-      <x:c r="C48" s="50"/>
-      <x:c r="D48" s="50"/>
-      <x:c r="E48" s="50"/>
-      <x:c r="F48" s="50"/>
-      <x:c r="G48" s="50"/>
-      <x:c r="H48" s="50"/>
-      <x:c r="I48" s="50"/>
-      <x:c r="J48" s="50"/>
-      <x:c r="K48" s="50"/>
-      <x:c r="L48" s="50"/>
-      <x:c r="M48" s="50"/>
-      <x:c r="N48" s="50"/>
+      <x:c r="A48"/>
+      <x:c r="B48"/>
+      <x:c r="C48"/>
+      <x:c r="D48"/>
+      <x:c r="E48"/>
+      <x:c r="F48"/>
+      <x:c r="G48"/>
+      <x:c r="H48"/>
+      <x:c r="I48"/>
+      <x:c r="J48"/>
+      <x:c r="K48"/>
+      <x:c r="L48"/>
+      <x:c r="M48"/>
+      <x:c r="N48"/>
     </x:row>
     <x:row r="51" ht="16.5">
-      <x:c r="A51" s="47" t="str">
-        <x:v>Social Media Activity — Last 14 Days</x:v>
-      </x:c>
-      <x:c r="B51" s="47"/>
-      <x:c r="C51" s="47"/>
-      <x:c r="D51" s="47"/>
-      <x:c r="E51" s="47"/>
-      <x:c r="F51" s="47"/>
-      <x:c r="G51" s="47"/>
-      <x:c r="H51" s="47"/>
-      <x:c r="I51" s="47"/>
-      <x:c r="J51" s="47"/>
-      <x:c r="K51" s="47"/>
-      <x:c r="L51" s="47"/>
-      <x:c r="M51" s="47"/>
-      <x:c r="N51" s="47"/>
+      <x:c r="A51"/>
+      <x:c r="B51"/>
+      <x:c r="C51"/>
+      <x:c r="D51"/>
+      <x:c r="E51"/>
+      <x:c r="F51"/>
+      <x:c r="G51"/>
+      <x:c r="H51"/>
+      <x:c r="I51"/>
+      <x:c r="J51"/>
+      <x:c r="K51"/>
+      <x:c r="L51"/>
+      <x:c r="M51"/>
+      <x:c r="N51"/>
     </x:row>
     <x:row r="52" ht="20.649999618530273" customHeight="1"/>
     <x:row r="53" ht="28" customHeight="1">
-      <x:c r="A53" s="36" t="str">
-        <x:v>Competitor</x:v>
-      </x:c>
-      <x:c r="B53" s="36" t="str">
-        <x:v>Instagram</x:v>
-      </x:c>
-      <x:c r="C53" s="36" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="D53" s="36" t="str">
-        <x:v>Facebook</x:v>
-      </x:c>
-      <x:c r="E53" s="36" t="str">
-        <x:v>TikTok</x:v>
-      </x:c>
-      <x:c r="F53" s="36" t="str">
-        <x:v>Total Posts</x:v>
-      </x:c>
+      <x:c r="A53"/>
+      <x:c r="B53"/>
+      <x:c r="C53"/>
+      <x:c r="D53"/>
+      <x:c r="E53"/>
+      <x:c r="F53"/>
     </x:row>
     <x:row r="54" ht="18.649999618530273" customHeight="1">
-      <x:c r="A54" s="32" t="str">
-        <x:v>STC Bank</x:v>
-      </x:c>
-      <x:c r="B54" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C54" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D54" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E54" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F54" s="32" t="n">
-        <x:f>SUM(B54:E54)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="A54"/>
+      <x:c r="B54"/>
+      <x:c r="C54"/>
+      <x:c r="D54"/>
+      <x:c r="E54"/>
+      <x:c r="F54"/>
     </x:row>
     <x:row r="55" ht="18.649999618530273" customHeight="1">
-      <x:c r="A55" s="32" t="str">
-        <x:v>barq</x:v>
-      </x:c>
-      <x:c r="B55" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C55" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D55" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E55" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F55" s="32" t="n">
-        <x:f>SUM(B55:E55)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="A55"/>
+      <x:c r="B55"/>
+      <x:c r="C55"/>
+      <x:c r="D55"/>
+      <x:c r="E55"/>
+      <x:c r="F55"/>
     </x:row>
     <x:row r="56" ht="18.649999618530273" customHeight="1">
-      <x:c r="A56" s="32" t="str">
-        <x:v>Mobily Pay</x:v>
-      </x:c>
-      <x:c r="B56" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C56" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D56" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E56" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F56" s="32" t="n">
-        <x:f>SUM(B56:E56)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="A56"/>
+      <x:c r="B56"/>
+      <x:c r="C56"/>
+      <x:c r="D56"/>
+      <x:c r="E56"/>
+      <x:c r="F56"/>
     </x:row>
     <x:row r="57" ht="18.649999618530273" customHeight="1">
-      <x:c r="A57" s="32" t="str">
-        <x:v>tiqmo</x:v>
-      </x:c>
-      <x:c r="B57" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C57" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D57" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E57" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F57" s="32" t="n">
-        <x:f>SUM(B57:E57)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="A57"/>
+      <x:c r="B57"/>
+      <x:c r="C57"/>
+      <x:c r="D57"/>
+      <x:c r="E57"/>
+      <x:c r="F57"/>
     </x:row>
     <x:row r="58" ht="18.649999618530273" customHeight="1">
-      <x:c r="A58" s="32" t="str">
-        <x:v>urpay</x:v>
-      </x:c>
-      <x:c r="B58" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C58" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D58" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E58" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F58" s="32" t="n">
-        <x:f>SUM(B58:E58)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="A58"/>
+      <x:c r="B58"/>
+      <x:c r="C58"/>
+      <x:c r="D58"/>
+      <x:c r="E58"/>
+      <x:c r="F58"/>
     </x:row>
     <x:row r="59" ht="18.649999618530273" customHeight="1">
-      <x:c r="A59" s="32" t="str">
-        <x:v>alinma pay</x:v>
-      </x:c>
-      <x:c r="B59" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C59" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D59" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E59" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F59" s="32" t="n">
-        <x:f>SUM(B59:E59)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="A59"/>
+      <x:c r="B59"/>
+      <x:c r="C59"/>
+      <x:c r="D59"/>
+      <x:c r="E59"/>
+      <x:c r="F59"/>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" s="37" t="str">
-        <x:v>Market Total</x:v>
-      </x:c>
-      <x:c r="B60" s="37" t="n">
+      <x:c r="A60"/>
+      <x:c r="B60">
         <x:f t="shared" ref="B60:F60" si="2">SUM(B54:B59)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C60" s="37" t="n">
-        <x:f t="shared" si="2">SUM(C54:C59)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D60" s="37" t="n">
-        <x:f t="shared" si="2">SUM(D54:D59)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E60" s="37" t="n">
-        <x:f t="shared" si="2">SUM(E54:E59)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F60" s="37" t="n">
-        <x:f t="shared" si="2">SUM(F54:F59)</x:f>
-        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C60">
+        <x:f t="shared" si="2"/>
+      </x:c>
+      <x:c r="D60">
+        <x:f t="shared" si="2"/>
+      </x:c>
+      <x:c r="E60">
+        <x:f t="shared" si="2"/>
+      </x:c>
+      <x:c r="F60">
+        <x:f t="shared" si="2"/>
       </x:c>
     </x:row>
     <x:row r="63" ht="15.5">
-      <x:c r="A63" s="51" t="str">
-        <x:v>Reporting Convention and Rationale</x:v>
-      </x:c>
-      <x:c r="B63" s="51"/>
-      <x:c r="C63" s="51"/>
-      <x:c r="D63" s="51"/>
-      <x:c r="E63" s="51"/>
-      <x:c r="F63" s="51"/>
-      <x:c r="G63" s="51"/>
-      <x:c r="H63" s="51"/>
-      <x:c r="I63" s="51"/>
-      <x:c r="J63" s="51"/>
-      <x:c r="K63" s="51"/>
-      <x:c r="L63" s="51"/>
-      <x:c r="M63" s="51"/>
-      <x:c r="N63" s="51"/>
+      <x:c r="A63"/>
+      <x:c r="B63"/>
+      <x:c r="C63"/>
+      <x:c r="D63"/>
+      <x:c r="E63"/>
+      <x:c r="F63"/>
+      <x:c r="G63"/>
+      <x:c r="H63"/>
+      <x:c r="I63"/>
+      <x:c r="J63"/>
+      <x:c r="K63"/>
+      <x:c r="L63"/>
+      <x:c r="M63"/>
+      <x:c r="N63"/>
     </x:row>
     <x:row r="64" ht="22.649999618530273" customHeight="1">
-      <x:c r="A64" s="50" t="str">
-        <x:v>• Dashboard campaign KPIs include active approved campaigns only; expired campaigns are excluded.</x:v>
-      </x:c>
-      <x:c r="B64" s="50"/>
-      <x:c r="C64" s="50"/>
-      <x:c r="D64" s="50"/>
-      <x:c r="E64" s="50"/>
-      <x:c r="F64" s="50"/>
-      <x:c r="G64" s="50"/>
-      <x:c r="H64" s="50"/>
-      <x:c r="I64" s="50"/>
-      <x:c r="J64" s="50"/>
-      <x:c r="K64" s="50"/>
-      <x:c r="L64" s="50"/>
-      <x:c r="M64" s="50"/>
-      <x:c r="N64" s="50"/>
+      <x:c r="A64"/>
+      <x:c r="B64"/>
+      <x:c r="C64"/>
+      <x:c r="D64"/>
+      <x:c r="E64"/>
+      <x:c r="F64"/>
+      <x:c r="G64"/>
+      <x:c r="H64"/>
+      <x:c r="I64"/>
+      <x:c r="J64"/>
+      <x:c r="K64"/>
+      <x:c r="L64"/>
+      <x:c r="M64"/>
+      <x:c r="N64"/>
     </x:row>
     <x:row r="65" ht="22.649999618530273" customHeight="1">
-      <x:c r="A65" s="48" t="str">
-        <x:v>• Merchant offers are excluded from Dashboard KPIs and appear only as a count in each competitor sheet.</x:v>
-      </x:c>
-      <x:c r="B65" s="48"/>
-      <x:c r="C65" s="48"/>
-      <x:c r="D65" s="48"/>
-      <x:c r="E65" s="48"/>
-      <x:c r="F65" s="48"/>
-      <x:c r="G65" s="48"/>
-      <x:c r="H65" s="48"/>
-      <x:c r="I65" s="48"/>
-      <x:c r="J65" s="48"/>
-      <x:c r="K65" s="48"/>
-      <x:c r="L65" s="48"/>
-      <x:c r="M65" s="48"/>
-      <x:c r="N65" s="48"/>
+      <x:c r="A65"/>
+      <x:c r="B65"/>
+      <x:c r="C65"/>
+      <x:c r="D65"/>
+      <x:c r="E65"/>
+      <x:c r="F65"/>
+      <x:c r="G65"/>
+      <x:c r="H65"/>
+      <x:c r="I65"/>
+      <x:c r="J65"/>
+      <x:c r="K65"/>
+      <x:c r="L65"/>
+      <x:c r="M65"/>
+      <x:c r="N65"/>
     </x:row>
     <x:row r="66" ht="22.649999618530273" customHeight="1">
-      <x:c r="A66" s="61" t="str">
-        <x:v>• Social Media Activity counts unique direct official posts published within the latest 14-day window.</x:v>
-      </x:c>
-      <x:c r="B66" s="50"/>
-      <x:c r="C66" s="50"/>
-      <x:c r="D66" s="50"/>
-      <x:c r="E66" s="50"/>
-      <x:c r="F66" s="50"/>
-      <x:c r="G66" s="50"/>
-      <x:c r="H66" s="50"/>
-      <x:c r="I66" s="50"/>
-      <x:c r="J66" s="50"/>
-      <x:c r="K66" s="50"/>
-      <x:c r="L66" s="50"/>
-      <x:c r="M66" s="50"/>
-      <x:c r="N66" s="50"/>
+      <x:c r="A66"/>
+      <x:c r="B66"/>
+      <x:c r="C66"/>
+      <x:c r="D66"/>
+      <x:c r="E66"/>
+      <x:c r="F66"/>
+      <x:c r="G66"/>
+      <x:c r="H66"/>
+      <x:c r="I66"/>
+      <x:c r="J66"/>
+      <x:c r="K66"/>
+      <x:c r="L66"/>
+      <x:c r="M66"/>
+      <x:c r="N66"/>
     </x:row>
     <x:row r="67" ht="22.649999618530273" customHeight="1">
-      <x:c r="A67" s="49" t="str">
-        <x:v>• Remittance is the priority target category and is highlighted in blue throughout the workbook.</x:v>
-      </x:c>
-      <x:c r="B67" s="49"/>
-      <x:c r="C67" s="49"/>
-      <x:c r="D67" s="49"/>
-      <x:c r="E67" s="49"/>
-      <x:c r="F67" s="49"/>
-      <x:c r="G67" s="49"/>
-      <x:c r="H67" s="49"/>
-      <x:c r="I67" s="49"/>
-      <x:c r="J67" s="49"/>
-      <x:c r="K67" s="49"/>
-      <x:c r="L67" s="49"/>
-      <x:c r="M67" s="49"/>
-      <x:c r="N67" s="49"/>
+      <x:c r="A67"/>
+      <x:c r="B67"/>
+      <x:c r="C67"/>
+      <x:c r="D67"/>
+      <x:c r="E67"/>
+      <x:c r="F67"/>
+      <x:c r="G67"/>
+      <x:c r="H67"/>
+      <x:c r="I67"/>
+      <x:c r="J67"/>
+      <x:c r="K67"/>
+      <x:c r="L67"/>
+      <x:c r="M67"/>
+      <x:c r="N67"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A63:N63"/>
-    <x:mergeCell ref="A64:N64"/>
-    <x:mergeCell ref="A65:N65"/>
-    <x:mergeCell ref="A66:N66"/>
-    <x:mergeCell ref="A67:N67"/>
-    <x:mergeCell ref="A18:N18"/>
-    <x:mergeCell ref="A30:N30"/>
-    <x:mergeCell ref="A51:N51"/>
-    <x:mergeCell ref="A42:N42"/>
-    <x:mergeCell ref="A43:N43"/>
-    <x:mergeCell ref="A44:N44"/>
-    <x:mergeCell ref="A45:N45"/>
-    <x:mergeCell ref="A46:N46"/>
-    <x:mergeCell ref="A47:N47"/>
-    <x:mergeCell ref="A48:N48"/>
+    <x:mergeCell ref="B3:D3"/>
+    <x:mergeCell ref="A5:B5"/>
+    <x:mergeCell ref="A6:B7"/>
+    <x:mergeCell ref="D5:E5"/>
+    <x:mergeCell ref="D6:E7"/>
+    <x:mergeCell ref="G5:H5"/>
+    <x:mergeCell ref="G6:H7"/>
+    <x:mergeCell ref="M5:N5"/>
+    <x:mergeCell ref="M6:N7"/>
     <x:mergeCell ref="A1:N1"/>
     <x:mergeCell ref="A2:N2"/>
-    <x:mergeCell ref="G3:N3"/>
-    <x:mergeCell ref="I5:J5"/>
-    <x:mergeCell ref="I6:J6"/>
+    <x:mergeCell ref="E3:I3"/>
+    <x:mergeCell ref="K3:N3"/>
+    <x:mergeCell ref="J5:K5"/>
+    <x:mergeCell ref="J6:K7"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B33:E38">
     <x:cfRule type="dataBar" priority="8">
@@ -5531,7 +5697,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38ecfa3cc6644f9d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fd6ef60985e444e"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -5650,7 +5816,7 @@
   <x:sheetData>
     <x:row r="1" ht="22.649999618530273" customHeight="1">
       <x:c r="A1" s="52" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="52"/>
       <x:c r="C1" s="52"/>
@@ -5688,7 +5854,7 @@
       <x:c r="K2" s="56"/>
       <x:c r="L2" s="56"/>
       <x:c r="M2" s="57" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N2" s="57"/>
       <x:c r="O2" s="57"/>
@@ -5784,61 +5950,61 @@
     </x:row>
     <x:row r="8" ht="30.649999618530273" customHeight="1">
       <x:c r="A8" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B8" s="3" t="s">
+      <x:c r="D8" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C8" s="3" t="s">
+      <x:c r="E8" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D8" s="3" t="s">
+      <x:c r="F8" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E8" s="3" t="s">
+      <x:c r="G8" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="s">
+      <x:c r="H8" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="s">
+      <x:c r="I8" s="3" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="s">
+      <x:c r="J8" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="s">
+      <x:c r="K8" s="3" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J8" s="3" t="s">
+      <x:c r="L8" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K8" s="3" t="s">
+      <x:c r="M8" s="3" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="L8" s="3" t="s">
+      <x:c r="N8" s="3" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="M8" s="3" t="s">
+      <x:c r="O8" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="N8" s="3" t="s">
+      <x:c r="P8" s="3" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="O8" s="3" t="s">
+      <x:c r="Q8" s="3" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="P8" s="3" t="s">
+      <x:c r="R8" s="3" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="Q8" s="3" t="s">
+      <x:c r="S8" s="3" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="R8" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="S8" s="3" t="s">
-        <x:v>22</x:v>
       </x:c>
       <x:c r="T8" s="3" t="str">
         <x:v>Social Post Count</x:v>
@@ -5853,13 +6019,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C9" s="4" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="C9" s="4" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="s">
-        <x:v>25</x:v>
       </x:c>
       <x:c r="E9" s="5"/>
       <x:c r="F9" s="5">
@@ -5870,39 +6036,39 @@
       </x:c>
       <x:c r="H9" s="7" t="n">
         <x:f t="shared" ref="H9:H53" si="1">IF(OR(C9="",G9=""),"",G9-TODAY())</x:f>
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I9" s="6" t="str">
         <x:f t="shared" ref="I9:I53" si="2">IF(C9="","",IF(G9="","End Date Not Stated",IF(G9&lt;TODAY(),"Expired",IF(G9&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G9&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expiring ≤7 Days</x:v>
       </x:c>
       <x:c r="J9" s="4" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K9" s="4" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L9" s="4" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="K9" s="4" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="L9" s="4" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:f>IF(C9="","",IF(N9&lt;&gt;"",N9,IF(O9&lt;&gt;"",O9,IF(P9&lt;&gt;"",P9,IF(Q9&lt;&gt;"",Q9,IF(R9&lt;&gt;"",R9,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/international-purchases-with-0-fees</x:v>
       </x:c>
       <x:c r="N9" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="O9" s="4" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="P9" s="4" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="O9" s="4" t="s">
+      <x:c r="Q9" s="63" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="P9" s="4" t="s">
+      <x:c r="R9" s="63" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="Q9" s="63" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="R9" s="63" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="S9" s="4" t="str">
         <x:v>0% international POS fee campaign is valid from 17 May to 31 August 2026. International e-commerce purchases are excluded; free withdrawals apply to international ATMs. Digital-wallet purchases are eligible under the official terms.</x:v>
@@ -5921,13 +6087,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E10" s="5"/>
       <x:c r="F10" s="5">
@@ -5938,36 +6104,36 @@
       </x:c>
       <x:c r="H10" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C10="",G10=""),"",G10-TODAY())</x:f>
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I10" s="6" t="str">
         <x:f t="shared" si="2">IF(C10="","",IF(G10="","End Date Not Stated",IF(G10&lt;TODAY(),"Expired",IF(G10&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G10&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
-        <x:v>Expiring 8–30 Days</x:v>
+        <x:v>Expiring ≤7 Days</x:v>
       </x:c>
       <x:c r="J10" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="K10" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="L10" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M10" s="9" t="str">
         <x:f>IF(C10="","",IF(N10&lt;&gt;"",N10,IF(O10&lt;&gt;"",O10,IF(P10&lt;&gt;"",P10,IF(Q10&lt;&gt;"",Q10,IF(R10&lt;&gt;"",R10,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/international-purchases-with-0-fees</x:v>
       </x:c>
       <x:c r="N10" s="63" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="O10" s="4" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="P10" s="4" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="Q10" s="63" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="P10" s="4" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="Q10" s="63" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="R10" s="4"/>
       <x:c r="S10" s="4" t="str">
@@ -5987,13 +6153,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5"/>
@@ -6002,27 +6168,27 @@
       </x:c>
       <x:c r="H11" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C11="",G11=""),"",G11-TODAY())</x:f>
-        <x:v>-6</x:v>
+        <x:v>-7</x:v>
       </x:c>
       <x:c r="I11" s="6" t="str">
         <x:f t="shared" si="2">IF(C11="","",IF(G11="","End Date Not Stated",IF(G11&lt;TODAY(),"Expired",IF(G11&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G11&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K11" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="L11" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:f t="shared" ref="M11:M53" si="4">IF(C11="","",IF(N11&lt;&gt;"",N11,IF(O11&lt;&gt;"",O11,IF(P11&lt;&gt;"",P11,IF(Q11&lt;&gt;"",Q11,IF(R11&lt;&gt;"",R11,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/visa_cards_rewards</x:v>
       </x:c>
       <x:c r="N11" s="63" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="O11" s="4"/>
       <x:c r="P11" s="4"/>
@@ -6045,13 +6211,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E12" s="5">
         <x:v>46217</x:v>
@@ -6066,13 +6232,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J12" s="4" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K12" s="4" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="L12" s="4" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="K12" s="4" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="L12" s="4" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
         <x:f t="shared" si="4">IF(C12="","",IF(N12&lt;&gt;"",N12,IF(O12&lt;&gt;"",O12,IF(P12&lt;&gt;"",P12,IF(Q12&lt;&gt;"",Q12,IF(R12&lt;&gt;"",R12,""))))))</x:f>
@@ -6080,17 +6246,17 @@
       </x:c>
       <x:c r="N12" s="4"/>
       <x:c r="O12" s="63" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="P12" s="63" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="Q12" s="63" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="P12" s="63" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="Q12" s="63" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="R12" s="4"/>
       <x:c r="S12" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="T12" s="5" t="n">
         <x:v>46240</x:v>
@@ -6106,13 +6272,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C13" s="4" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="C13" s="4" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D13" s="4" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="E13" s="5"/>
       <x:c r="F13" s="5"/>
@@ -6121,27 +6287,27 @@
       </x:c>
       <x:c r="H13" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C13="",G13=""),"",G13-TODAY())</x:f>
-        <x:v>492</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="I13" s="6" t="str">
         <x:f t="shared" si="2">IF(C13="","",IF(G13="","End Date Not Stated",IF(G13&lt;TODAY(),"Expired",IF(G13&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G13&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J13" s="4" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="K13" s="4" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L13" s="4" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="K13" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="L13" s="4" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="M13" s="9" t="str">
         <x:f t="shared" si="4">IF(C13="","",IF(N13&lt;&gt;"",N13,IF(O13&lt;&gt;"",O13,IF(P13&lt;&gt;"",P13,IF(Q13&lt;&gt;"",Q13,IF(R13&lt;&gt;"",R13,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/almatar-offer</x:v>
       </x:c>
       <x:c r="N13" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O13" s="4"/>
       <x:c r="P13" s="4"/>
@@ -6164,13 +6330,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B14" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C14" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E14" s="5"/>
       <x:c r="F14" s="5"/>
@@ -6179,27 +6345,27 @@
       </x:c>
       <x:c r="H14" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C14="",G14=""),"",G14-TODAY())</x:f>
-        <x:v>-26</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I14" s="6" t="str">
         <x:f t="shared" si="2">IF(C14="","",IF(G14="","End Date Not Stated",IF(G14&lt;TODAY(),"Expired",IF(G14&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G14&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J14" s="4" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K14" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="L14" s="4" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="K14" s="4" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="L14" s="4" t="s">
-        <x:v>66</x:v>
       </x:c>
       <x:c r="M14" s="9" t="str">
         <x:f t="shared" si="4">IF(C14="","",IF(N14&lt;&gt;"",N14,IF(O14&lt;&gt;"",O14,IF(P14&lt;&gt;"",P14,IF(Q14&lt;&gt;"",Q14,IF(R14&lt;&gt;"",R14,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/whites-offer</x:v>
       </x:c>
       <x:c r="N14" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="O14" s="4"/>
       <x:c r="P14" s="4"/>
@@ -6222,13 +6388,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B15" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C15" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E15" s="5"/>
       <x:c r="F15" s="5"/>
@@ -6237,27 +6403,27 @@
       </x:c>
       <x:c r="H15" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C15="",G15=""),"",G15-TODAY())</x:f>
-        <x:v>-24</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="I15" s="6" t="str">
         <x:f t="shared" si="2">IF(C15="","",IF(G15="","End Date Not Stated",IF(G15&lt;TODAY(),"Expired",IF(G15&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G15&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J15" s="4" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K15" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="L15" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="M15" s="9" t="str">
         <x:f t="shared" si="4">IF(C15="","",IF(N15&lt;&gt;"",N15,IF(O15&lt;&gt;"",O15,IF(P15&lt;&gt;"",P15,IF(Q15&lt;&gt;"",Q15,IF(R15&lt;&gt;"",R15,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/huawei</x:v>
       </x:c>
       <x:c r="N15" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="O15" s="4"/>
       <x:c r="P15" s="4"/>
@@ -6280,13 +6446,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C16" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D16" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E16" s="5"/>
       <x:c r="F16" s="5">
@@ -6297,27 +6463,27 @@
       </x:c>
       <x:c r="H16" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C16="",G16=""),"",G16-TODAY())</x:f>
-        <x:v>-1</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="I16" s="6" t="str">
         <x:f t="shared" si="2">IF(C16="","",IF(G16="","End Date Not Stated",IF(G16&lt;TODAY(),"Expired",IF(G16&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G16&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J16" s="4" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="K16" s="4" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="L16" s="4" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="K16" s="4" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="L16" s="4" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="M16" s="9" t="str">
         <x:f t="shared" si="4">IF(C16="","",IF(N16&lt;&gt;"",N16,IF(O16&lt;&gt;"",O16,IF(P16&lt;&gt;"",P16,IF(Q16&lt;&gt;"",Q16,IF(R16&lt;&gt;"",R16,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/loca</x:v>
       </x:c>
       <x:c r="N16" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="O16" s="4"/>
       <x:c r="P16" s="4"/>
@@ -6340,13 +6506,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B17" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C17" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D17" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E17" s="5"/>
       <x:c r="F17" s="5"/>
@@ -6355,27 +6521,27 @@
       </x:c>
       <x:c r="H17" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C17="",G17=""),"",G17-TODAY())</x:f>
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I17" s="6" t="str">
         <x:f t="shared" si="2">IF(C17="","",IF(G17="","End Date Not Stated",IF(G17&lt;TODAY(),"Expired",IF(G17&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G17&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J17" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="K17" s="4" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="L17" s="4" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="M17" s="9" t="str">
         <x:f t="shared" si="4">IF(C17="","",IF(N17&lt;&gt;"",N17,IF(O17&lt;&gt;"",O17,IF(P17&lt;&gt;"",P17,IF(Q17&lt;&gt;"",Q17,IF(R17&lt;&gt;"",R17,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/canton-offer</x:v>
       </x:c>
       <x:c r="N17" s="4" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="O17" s="4"/>
       <x:c r="P17" s="4"/>
@@ -6398,13 +6564,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B18" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C18" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D18" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E18" s="5"/>
       <x:c r="F18" s="5"/>
@@ -6413,27 +6579,27 @@
       </x:c>
       <x:c r="H18" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C18="",G18=""),"",G18-TODAY())</x:f>
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I18" s="6" t="str">
         <x:f t="shared" si="2">IF(C18="","",IF(G18="","End Date Not Stated",IF(G18&lt;TODAY(),"Expired",IF(G18&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G18&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J18" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K18" s="4" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="L18" s="4" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="M18" s="9" t="str">
         <x:f t="shared" si="4">IF(C18="","",IF(N18&lt;&gt;"",N18,IF(O18&lt;&gt;"",O18,IF(P18&lt;&gt;"",P18,IF(Q18&lt;&gt;"",Q18,IF(R18&lt;&gt;"",R18,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/boost-your-health</x:v>
       </x:c>
       <x:c r="N18" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="O18" s="4"/>
       <x:c r="P18" s="4"/>
@@ -6456,13 +6622,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B19" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C19" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D19" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E19" s="5"/>
       <x:c r="F19" s="5"/>
@@ -6471,27 +6637,27 @@
       </x:c>
       <x:c r="H19" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C19="",G19=""),"",G19-TODAY())</x:f>
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I19" s="6" t="str">
         <x:f t="shared" si="2">IF(C19="","",IF(G19="","End Date Not Stated",IF(G19&lt;TODAY(),"Expired",IF(G19&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G19&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J19" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K19" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="L19" s="4" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="M19" s="9" t="str">
         <x:f t="shared" si="4">IF(C19="","",IF(N19&lt;&gt;"",N19,IF(O19&lt;&gt;"",O19,IF(P19&lt;&gt;"",P19,IF(Q19&lt;&gt;"",Q19,IF(R19&lt;&gt;"",R19,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/shop-workout-and-save-with-10-off-on-gosport</x:v>
       </x:c>
       <x:c r="N19" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="O19" s="4"/>
       <x:c r="P19" s="4"/>
@@ -6514,13 +6680,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B20" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C20" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D20" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E20" s="5"/>
       <x:c r="F20" s="5"/>
@@ -6529,27 +6695,27 @@
       </x:c>
       <x:c r="H20" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C20="",G20=""),"",G20-TODAY())</x:f>
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I20" s="6" t="str">
         <x:f t="shared" si="2">IF(C20="","",IF(G20="","End Date Not Stated",IF(G20&lt;TODAY(),"Expired",IF(G20&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G20&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J20" s="4" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="K20" s="4" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="L20" s="4" t="s">
         <x:v>95</x:v>
-      </x:c>
-      <x:c r="K20" s="4" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="L20" s="4" t="s">
-        <x:v>97</x:v>
       </x:c>
       <x:c r="M20" s="9" t="str">
         <x:f t="shared" si="4">IF(C20="","",IF(N20&lt;&gt;"",N20,IF(O20&lt;&gt;"",O20,IF(P20&lt;&gt;"",P20,IF(Q20&lt;&gt;"",Q20,IF(R20&lt;&gt;"",R20,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/iherb-offer</x:v>
       </x:c>
       <x:c r="N20" s="4" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="O20" s="4"/>
       <x:c r="P20" s="4"/>
@@ -6572,13 +6738,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B21" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C21" s="4" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D21" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E21" s="5"/>
       <x:c r="F21" s="5"/>
@@ -6587,27 +6753,27 @@
       </x:c>
       <x:c r="H21" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C21="",G21=""),"",G21-TODAY())</x:f>
-        <x:v>492</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="I21" s="6" t="str">
         <x:f t="shared" si="2">IF(C21="","",IF(G21="","End Date Not Stated",IF(G21&lt;TODAY(),"Expired",IF(G21&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G21&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J21" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="K21" s="4" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="L21" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M21" s="9" t="str">
         <x:f t="shared" si="4">IF(C21="","",IF(N21&lt;&gt;"",N21,IF(O21&lt;&gt;"",O21,IF(P21&lt;&gt;"",P21,IF(Q21&lt;&gt;"",Q21,IF(R21&lt;&gt;"",R21,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/alothaim-entertainment</x:v>
       </x:c>
       <x:c r="N21" s="4" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="O21" s="4"/>
       <x:c r="P21" s="4"/>
@@ -6630,13 +6796,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B22" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C22" s="4" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D22" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E22" s="5"/>
       <x:c r="F22" s="5"/>
@@ -6645,27 +6811,27 @@
       </x:c>
       <x:c r="H22" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C22="",G22=""),"",G22-TODAY())</x:f>
-        <x:v>492</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="I22" s="6" t="str">
         <x:f t="shared" si="2">IF(C22="","",IF(G22="","End Date Not Stated",IF(G22&lt;TODAY(),"Expired",IF(G22&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G22&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J22" s="4" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="K22" s="4" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="L22" s="4" t="s">
         <x:v>106</x:v>
-      </x:c>
-      <x:c r="K22" s="4" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="L22" s="4" t="s">
-        <x:v>108</x:v>
       </x:c>
       <x:c r="M22" s="9" t="str">
         <x:f t="shared" si="4">IF(C22="","",IF(N22&lt;&gt;"",N22,IF(O22&lt;&gt;"",O22,IF(P22&lt;&gt;"",P22,IF(Q22&lt;&gt;"",Q22,IF(R22&lt;&gt;"",R22,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/yelo</x:v>
       </x:c>
       <x:c r="N22" s="4" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="O22" s="4"/>
       <x:c r="P22" s="4"/>
@@ -6688,13 +6854,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B23" s="4" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C23" s="4" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D23" s="4" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="C23" s="4" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="D23" s="4" t="s">
-        <x:v>112</x:v>
       </x:c>
       <x:c r="E23" s="5"/>
       <x:c r="F23" s="5">
@@ -6705,42 +6871,42 @@
       </x:c>
       <x:c r="H23" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C23="",G23=""),"",G23-TODAY())</x:f>
-        <x:v>-38</x:v>
+        <x:v>-39</x:v>
       </x:c>
       <x:c r="I23" s="6" t="str">
         <x:f t="shared" si="2">IF(C23="","",IF(G23="","End Date Not Stated",IF(G23&lt;TODAY(),"Expired",IF(G23&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G23&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J23" s="4" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="K23" s="4" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="L23" s="4" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="K23" s="4" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="L23" s="4" t="s">
-        <x:v>115</x:v>
       </x:c>
       <x:c r="M23" s="9" t="str">
         <x:f t="shared" si="4">IF(C23="","",IF(N23&lt;&gt;"",N23,IF(O23&lt;&gt;"",O23,IF(P23&lt;&gt;"",P23,IF(Q23&lt;&gt;"",Q23,IF(R23&lt;&gt;"",R23,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/stcbank-championship</x:v>
       </x:c>
       <x:c r="N23" s="4" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="O23" s="4" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="P23" s="4" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="O23" s="4" t="s">
+      <x:c r="Q23" s="63" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="P23" s="4" t="s">
+      <x:c r="R23" s="63" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="Q23" s="63" t="s">
+      <x:c r="S23" s="4" t="s">
         <x:v>119</x:v>
-      </x:c>
-      <x:c r="R23" s="63" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="S23" s="4" t="s">
-        <x:v>121</x:v>
       </x:c>
       <x:c r="T23" s="5" t="n">
         <x:v>46240</x:v>
@@ -6771,7 +6937,7 @@
       </x:c>
       <x:c r="H24" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C24="",G24=""),"",G24-TODAY())</x:f>
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I24" s="6" t="str">
         <x:f t="shared" si="2">IF(C24="","",IF(G24="","End Date Not Stated",IF(G24&lt;TODAY(),"Expired",IF(G24&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G24&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
@@ -7847,7 +8013,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf47724ef1e6e477c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R351f20ef52c0471c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7877,7 +8043,7 @@
   <x:sheetData>
     <x:row r="1" ht="22.649999618530273" customHeight="1">
       <x:c r="A1" s="52" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B1" s="52"/>
       <x:c r="C1" s="52"/>
@@ -7915,7 +8081,7 @@
       <x:c r="K2" s="56"/>
       <x:c r="L2" s="56"/>
       <x:c r="M2" s="57" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N2" s="57"/>
       <x:c r="O2" s="57"/>
@@ -8011,61 +8177,61 @@
     </x:row>
     <x:row r="8" ht="30.649999618530273" customHeight="1">
       <x:c r="A8" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B8" s="3" t="s">
+      <x:c r="D8" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C8" s="3" t="s">
+      <x:c r="E8" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D8" s="3" t="s">
+      <x:c r="F8" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E8" s="3" t="s">
+      <x:c r="G8" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="s">
+      <x:c r="H8" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="s">
+      <x:c r="I8" s="3" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="s">
+      <x:c r="J8" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="s">
+      <x:c r="K8" s="3" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J8" s="3" t="s">
+      <x:c r="L8" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K8" s="3" t="s">
+      <x:c r="M8" s="3" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="L8" s="3" t="s">
+      <x:c r="N8" s="3" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="M8" s="3" t="s">
+      <x:c r="O8" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="N8" s="3" t="s">
+      <x:c r="P8" s="3" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="O8" s="3" t="s">
+      <x:c r="Q8" s="3" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="P8" s="3" t="s">
+      <x:c r="R8" s="3" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="Q8" s="3" t="s">
+      <x:c r="S8" s="3" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="R8" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="S8" s="3" t="s">
-        <x:v>22</x:v>
       </x:c>
       <x:c r="T8" s="3" t="str">
         <x:v>Social Post Count</x:v>
@@ -8080,13 +8246,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E9" s="5"/>
       <x:c r="F9" s="5"/>
@@ -8099,13 +8265,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J9" s="4" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="K9" s="4" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="L9" s="4" t="s">
         <x:v>125</x:v>
-      </x:c>
-      <x:c r="K9" s="4" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="L9" s="4" t="s">
-        <x:v>127</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:f>IF(C9="","",IF(N9&lt;&gt;"",N9,IF(O9&lt;&gt;"",O9,IF(P9&lt;&gt;"",P9,IF(Q9&lt;&gt;"",Q9,IF(R9&lt;&gt;"",R9,""))))))</x:f>
@@ -8113,15 +8279,15 @@
       </x:c>
       <x:c r="N9" s="4"/>
       <x:c r="O9" s="63" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="P9" s="4"/>
       <x:c r="Q9" s="63" t="s">
-        <x:v>129</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="R9" s="4"/>
       <x:c r="S9" s="4" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="T9" s="5" t="n">
         <x:v>46240</x:v>
@@ -8137,13 +8303,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>131</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E10" s="5"/>
       <x:c r="F10" s="5"/>
@@ -8156,13 +8322,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J10" s="4" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="K10" s="4" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="L10" s="4" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="K10" s="4" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="L10" s="4" t="s">
-        <x:v>135</x:v>
       </x:c>
       <x:c r="M10" s="9" t="str">
         <x:f t="shared" ref="M10:M42" si="4">IF(C10="","",IF(N10&lt;&gt;"",N10,IF(O10&lt;&gt;"",O10,IF(P10&lt;&gt;"",P10,IF(Q10&lt;&gt;"",Q10,IF(R10&lt;&gt;"",R10,""))))))</x:f>
@@ -8172,11 +8338,11 @@
       <x:c r="O10" s="4"/>
       <x:c r="P10" s="4"/>
       <x:c r="Q10" s="63" t="s">
-        <x:v>136</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="R10" s="4"/>
       <x:c r="S10" s="4" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="T10" s="5" t="n">
         <x:v>46240</x:v>
@@ -8192,13 +8358,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5"/>
@@ -8211,13 +8377,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K11" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="L11" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:f t="shared" si="4">IF(C11="","",IF(N11&lt;&gt;"",N11,IF(O11&lt;&gt;"",O11,IF(P11&lt;&gt;"",P11,IF(Q11&lt;&gt;"",Q11,IF(R11&lt;&gt;"",R11,""))))))</x:f>
@@ -8227,11 +8393,11 @@
       <x:c r="O11" s="4"/>
       <x:c r="P11" s="4"/>
       <x:c r="Q11" s="63" t="s">
-        <x:v>140</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="R11" s="4"/>
       <x:c r="S11" s="4" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="T11" s="5" t="n">
         <x:v>46240</x:v>
@@ -8247,13 +8413,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C12" s="4" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D12" s="4" t="s">
         <x:v>141</x:v>
-      </x:c>
-      <x:c r="C12" s="4" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="D12" s="4" t="s">
-        <x:v>143</x:v>
       </x:c>
       <x:c r="E12" s="5"/>
       <x:c r="F12" s="5"/>
@@ -8266,13 +8432,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J12" s="4" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="K12" s="4" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="L12" s="4" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="K12" s="4" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="L12" s="4" t="s">
-        <x:v>146</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
         <x:f t="shared" si="4">IF(C12="","",IF(N12&lt;&gt;"",N12,IF(O12&lt;&gt;"",O12,IF(P12&lt;&gt;"",P12,IF(Q12&lt;&gt;"",Q12,IF(R12&lt;&gt;"",R12,""))))))</x:f>
@@ -8280,7 +8446,7 @@
       </x:c>
       <x:c r="N12" s="4"/>
       <x:c r="O12" s="63" t="s">
-        <x:v>147</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="P12" s="4"/>
       <x:c r="Q12" s="63" t="str">
@@ -8304,13 +8470,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>148</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E13" s="5"/>
       <x:c r="F13" s="5"/>
@@ -8323,7 +8489,7 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J13" s="4" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="K13" s="4"/>
       <x:c r="L13" s="4"/>
@@ -8333,16 +8499,16 @@
       </x:c>
       <x:c r="N13" s="4"/>
       <x:c r="O13" s="63" t="s">
-        <x:v>151</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="P13" s="63" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="Q13" s="63" t="str">
         <x:v>https://www.facebook.com/usebarq/videos/%D8%AD%D9%84%D8%A7%D8%AA-%D8%A7%D9%84%D8%B3%D9%81%D8%B1-%D8%A8%D8%A7%D9%84%D8%AA%D8%AC%D8%A7%D8%B1%D8%A8-%D9%88%D8%A8%D8%A8%D8%B7%D8%A7%D9%82%D8%A9-%D8%A8%D8%AF%D9%88%D9%86-%D8%B1%D8%B3%D9%88%D9%85-%D8%AF%D9%88%D9%84%D9%8A%D8%A9%EF%B8%8F/1051539764436915/</x:v>
       </x:c>
       <x:c r="R13" s="63" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="S13" s="4" t="str">
         <x:v>Current official posts continue to position barq Visa as having no international transaction fees. No campaign end date is stated.</x:v>
@@ -8361,10 +8527,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B14" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C14" s="4" t="s">
-        <x:v>154</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D14" s="4"/>
       <x:c r="E14" s="5"/>
@@ -8378,13 +8544,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J14" s="4" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="K14" s="4" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="L14" s="4" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="K14" s="4" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="L14" s="4" t="s">
-        <x:v>157</x:v>
       </x:c>
       <x:c r="M14" s="9" t="str">
         <x:f t="shared" si="4">IF(C14="","",IF(N14&lt;&gt;"",N14,IF(O14&lt;&gt;"",O14,IF(P14&lt;&gt;"",P14,IF(Q14&lt;&gt;"",Q14,IF(R14&lt;&gt;"",R14,""))))))</x:f>
@@ -8392,7 +8558,7 @@
       </x:c>
       <x:c r="N14" s="4"/>
       <x:c r="O14" s="63" t="s">
-        <x:v>158</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="P14" s="4"/>
       <x:c r="Q14" s="4"/>
@@ -9395,7 +9561,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a97a54acd1e4495"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdddcf73619242a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9425,7 +9591,7 @@
   <x:sheetData>
     <x:row r="1" ht="22.649999618530273" customHeight="1">
       <x:c r="A1" s="52" t="s">
-        <x:v>159</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B1" s="52"/>
       <x:c r="C1" s="52"/>
@@ -9463,7 +9629,7 @@
       <x:c r="K2" s="56"/>
       <x:c r="L2" s="56"/>
       <x:c r="M2" s="57" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N2" s="57"/>
       <x:c r="O2" s="57"/>
@@ -9559,61 +9725,61 @@
     </x:row>
     <x:row r="8" ht="30.649999618530273" customHeight="1">
       <x:c r="A8" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B8" s="3" t="s">
+      <x:c r="D8" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C8" s="3" t="s">
+      <x:c r="E8" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D8" s="3" t="s">
+      <x:c r="F8" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E8" s="3" t="s">
+      <x:c r="G8" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="s">
+      <x:c r="H8" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="s">
+      <x:c r="I8" s="3" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="s">
+      <x:c r="J8" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="s">
+      <x:c r="K8" s="3" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J8" s="3" t="s">
+      <x:c r="L8" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K8" s="3" t="s">
+      <x:c r="M8" s="3" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="L8" s="3" t="s">
+      <x:c r="N8" s="3" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="M8" s="3" t="s">
+      <x:c r="O8" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="N8" s="3" t="s">
+      <x:c r="P8" s="3" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="O8" s="3" t="s">
+      <x:c r="Q8" s="3" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="P8" s="3" t="s">
+      <x:c r="R8" s="3" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="Q8" s="3" t="s">
+      <x:c r="S8" s="3" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="R8" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="S8" s="3" t="s">
-        <x:v>22</x:v>
       </x:c>
       <x:c r="T8" s="3" t="str">
         <x:v>Social Post Count</x:v>
@@ -9628,7 +9794,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>International Transfer Prize Draw – SAR 110,000</x:v>
@@ -9645,7 +9811,7 @@
       </x:c>
       <x:c r="H9" s="7" t="n">
         <x:f t="shared" ref="H9:H42" si="1">IF(OR(C9="",G9=""),"",G9-TODAY())</x:f>
-        <x:v>-51</x:v>
+        <x:v>-52</x:v>
       </x:c>
       <x:c r="I9" s="6" t="str">
         <x:f t="shared" ref="I9:I42" si="2">IF(C9="","",IF(G9="","End Date Not Stated",IF(G9&lt;TODAY(),"Expired",IF(G9&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G9&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
@@ -9668,13 +9834,13 @@
         <x:v>https://mobilypay.sa/ar/offers/offer-51.html</x:v>
       </x:c>
       <x:c r="O9" s="63" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="P9" s="63" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="Q9" s="63" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="P9" s="63" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="Q9" s="63" t="s">
-        <x:v>162</x:v>
       </x:c>
       <x:c r="R9" s="4"/>
       <x:c r="S9" s="4" t="str">
@@ -9694,7 +9860,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C10" s="4" t="str">
         <x:v>Zero-Fee International Transfers – Aug–Oct 2026</x:v>
@@ -9711,7 +9877,7 @@
       </x:c>
       <x:c r="H10" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C10="",G10=""),"",G10-TODAY())</x:f>
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="I10" s="6" t="str">
         <x:f t="shared" si="2">IF(C10="","",IF(G10="","End Date Not Stated",IF(G10&lt;TODAY(),"Expired",IF(G10&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G10&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
@@ -9734,11 +9900,11 @@
         <x:v>https://mobilypay.sa/ar/offers/offer-56.html</x:v>
       </x:c>
       <x:c r="O10" s="63" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="P10" s="4"/>
       <x:c r="Q10" s="63" t="s">
-        <x:v>164</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="R10" s="4"/>
       <x:c r="S10" s="4" t="str">
@@ -9758,13 +9924,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
-        <x:v>165</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>166</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5"/>
@@ -9777,13 +9943,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="K11" s="4" t="s">
-        <x:v>167</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="L11" s="4" t="s">
-        <x:v>168</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:f t="shared" si="3">IF(C11="","",IF(N11&lt;&gt;"",N11,IF(O11&lt;&gt;"",O11,IF(P11&lt;&gt;"",P11,IF(Q11&lt;&gt;"",Q11,IF(R11&lt;&gt;"",R11,""))))))</x:f>
@@ -9793,11 +9959,11 @@
       <x:c r="O11" s="4"/>
       <x:c r="P11" s="4"/>
       <x:c r="Q11" s="63" t="s">
-        <x:v>169</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="R11" s="4"/>
       <x:c r="S11" s="4" t="s">
-        <x:v>170</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="T11" s="5" t="n">
         <x:v>46240</x:v>
@@ -9813,13 +9979,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>171</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>172</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E12" s="5"/>
       <x:c r="F12" s="5">
@@ -9830,34 +9996,34 @@
       </x:c>
       <x:c r="H12" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C12="",G12=""),"",G12-TODAY())</x:f>
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="I12" s="6" t="str">
         <x:f t="shared" si="2">IF(C12="","",IF(G12="","End Date Not Stated",IF(G12&lt;TODAY(),"Expired",IF(G12&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G12&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J12" s="4" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="K12" s="4" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="L12" s="4" t="s">
         <x:v>173</x:v>
-      </x:c>
-      <x:c r="K12" s="4" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="L12" s="4" t="s">
-        <x:v>175</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
         <x:f t="shared" si="3">IF(C12="","",IF(N12&lt;&gt;"",N12,IF(O12&lt;&gt;"",O12,IF(P12&lt;&gt;"",P12,IF(Q12&lt;&gt;"",Q12,IF(R12&lt;&gt;"",R12,""))))))</x:f>
         <x:v>https://mobilypay.sa/offer-details.html?id=offer-6</x:v>
       </x:c>
       <x:c r="N12" s="4" t="s">
-        <x:v>176</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="O12" s="4"/>
       <x:c r="P12" s="4"/>
       <x:c r="Q12" s="4"/>
       <x:c r="R12" s="4"/>
       <x:c r="S12" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="T12" s="5" t="n">
         <x:v>46240</x:v>
@@ -9873,13 +10039,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>178</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E13" s="5"/>
       <x:c r="F13" s="5">
@@ -9890,17 +10056,17 @@
       </x:c>
       <x:c r="H13" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C13="",G13=""),"",G13-TODAY())</x:f>
-        <x:v>-7</x:v>
+        <x:v>-8</x:v>
       </x:c>
       <x:c r="I13" s="6" t="str">
         <x:f t="shared" si="2">IF(C13="","",IF(G13="","End Date Not Stated",IF(G13&lt;TODAY(),"Expired",IF(G13&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G13&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J13" s="4" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="K13" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="L13" s="4"/>
       <x:c r="M13" s="9" t="str">
@@ -9908,17 +10074,17 @@
         <x:v>https://mobilypay.sa/offer-details.html?id=offer-53</x:v>
       </x:c>
       <x:c r="N13" s="63" t="s">
-        <x:v>182</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="O13" s="4"/>
       <x:c r="P13" s="63" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="Q13" s="63" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="R13" s="63" t="s">
         <x:v>183</x:v>
-      </x:c>
-      <x:c r="Q13" s="63" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="R13" s="63" t="s">
-        <x:v>185</x:v>
       </x:c>
       <x:c r="S13" s="4" t="str">
         <x:v>Campaign is valid from 19 July to 19 August 2026. It includes 0% international transaction fees for eligible newly issued Platinum and Signature Visa cards, free plastic-card issuance, and eligible POS/e-commerce purchases.</x:v>
@@ -9937,13 +10103,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B14" s="4" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="C14" s="4" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D14" s="4" t="s">
         <x:v>186</x:v>
-      </x:c>
-      <x:c r="C14" s="4" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="D14" s="4" t="s">
-        <x:v>188</x:v>
       </x:c>
       <x:c r="E14" s="5"/>
       <x:c r="F14" s="5">
@@ -9954,36 +10120,36 @@
       </x:c>
       <x:c r="H14" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C14="",G14=""),"",G14-TODAY())</x:f>
-        <x:v>-26</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I14" s="6" t="str">
         <x:f t="shared" si="2">IF(C14="","",IF(G14="","End Date Not Stated",IF(G14&lt;TODAY(),"Expired",IF(G14&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G14&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J14" s="4" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="K14" s="4" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="L14" s="4" t="s">
         <x:v>189</x:v>
-      </x:c>
-      <x:c r="K14" s="4" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="L14" s="4" t="s">
-        <x:v>191</x:v>
       </x:c>
       <x:c r="M14" s="9" t="str">
         <x:f t="shared" si="3">IF(C14="","",IF(N14&lt;&gt;"",N14,IF(O14&lt;&gt;"",O14,IF(P14&lt;&gt;"",P14,IF(Q14&lt;&gt;"",Q14,IF(R14&lt;&gt;"",R14,""))))))</x:f>
         <x:v>https://mobilypay.sa/offer-details.html?id=offer-54</x:v>
       </x:c>
       <x:c r="N14" s="63" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="O14" s="63" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="P14" s="63" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="O14" s="63" t="s">
+      <x:c r="Q14" s="63" t="s">
         <x:v>193</x:v>
-      </x:c>
-      <x:c r="P14" s="63" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="Q14" s="63" t="s">
-        <x:v>195</x:v>
       </x:c>
       <x:c r="R14" s="4"/>
       <x:c r="S14" s="4" t="str">
@@ -11003,7 +11169,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc510448c70f14db5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31321246c6b94b69"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11033,7 +11199,7 @@
   <x:sheetData>
     <x:row r="1" ht="22.649999618530273" customHeight="1">
       <x:c r="A1" s="52" t="s">
-        <x:v>196</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B1" s="52"/>
       <x:c r="C1" s="52"/>
@@ -11071,7 +11237,7 @@
       <x:c r="K2" s="56"/>
       <x:c r="L2" s="56"/>
       <x:c r="M2" s="57" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N2" s="57"/>
       <x:c r="O2" s="57"/>
@@ -11167,61 +11333,61 @@
     </x:row>
     <x:row r="8" ht="30.649999618530273" customHeight="1">
       <x:c r="A8" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B8" s="3" t="s">
+      <x:c r="D8" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C8" s="3" t="s">
+      <x:c r="E8" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D8" s="3" t="s">
+      <x:c r="F8" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E8" s="3" t="s">
+      <x:c r="G8" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="s">
+      <x:c r="H8" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="s">
+      <x:c r="I8" s="3" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="s">
+      <x:c r="J8" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="s">
+      <x:c r="K8" s="3" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J8" s="3" t="s">
+      <x:c r="L8" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K8" s="3" t="s">
+      <x:c r="M8" s="3" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="L8" s="3" t="s">
+      <x:c r="N8" s="3" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="M8" s="3" t="s">
+      <x:c r="O8" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="N8" s="3" t="s">
+      <x:c r="P8" s="3" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="O8" s="3" t="s">
+      <x:c r="Q8" s="3" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="P8" s="3" t="s">
+      <x:c r="R8" s="3" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="Q8" s="3" t="s">
+      <x:c r="S8" s="3" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="R8" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="S8" s="3" t="s">
-        <x:v>22</x:v>
       </x:c>
       <x:c r="T8" s="3" t="str">
         <x:v>Social Post Count</x:v>
@@ -11236,13 +11402,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="C9" s="4" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="s">
         <x:v>197</x:v>
-      </x:c>
-      <x:c r="C9" s="4" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="s">
-        <x:v>199</x:v>
       </x:c>
       <x:c r="E9" s="5">
         <x:v>46227</x:v>
@@ -11257,13 +11423,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J9" s="4" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="K9" s="4" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="L9" s="4" t="s">
         <x:v>200</x:v>
-      </x:c>
-      <x:c r="K9" s="4" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="L9" s="4" t="s">
-        <x:v>202</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:f t="shared" ref="M9:M42" si="3">IF(C9="","",IF(N9&lt;&gt;"",N9,IF(O9&lt;&gt;"",O9,IF(P9&lt;&gt;"",P9,IF(Q9&lt;&gt;"",Q9,IF(R9&lt;&gt;"",R9,""))))))</x:f>
@@ -11271,17 +11437,17 @@
       </x:c>
       <x:c r="N9" s="4"/>
       <x:c r="O9" s="4" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="P9" s="63" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="Q9" s="63" t="s">
         <x:v>203</x:v>
-      </x:c>
-      <x:c r="P9" s="63" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="Q9" s="63" t="s">
-        <x:v>205</x:v>
       </x:c>
       <x:c r="R9" s="4"/>
       <x:c r="S9" s="4" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="T9" s="5" t="n">
         <x:v>46240</x:v>
@@ -11297,13 +11463,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>206</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>207</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="E10" s="5">
         <x:v>46226</x:v>
@@ -11316,20 +11482,20 @@
       </x:c>
       <x:c r="H10" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C10="",G10=""),"",G10-TODAY())</x:f>
-        <x:v>-26</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I10" s="6" t="str">
         <x:f t="shared" si="2">IF(C10="","",IF(G10="","End Date Not Stated",IF(G10&lt;TODAY(),"Expired",IF(G10&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G10&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J10" s="4" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="K10" s="4" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="L10" s="4" t="s">
         <x:v>208</x:v>
-      </x:c>
-      <x:c r="K10" s="4" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="L10" s="4" t="s">
-        <x:v>210</x:v>
       </x:c>
       <x:c r="M10" s="9" t="str">
         <x:f t="shared" si="3">IF(C10="","",IF(N10&lt;&gt;"",N10,IF(O10&lt;&gt;"",O10,IF(P10&lt;&gt;"",P10,IF(Q10&lt;&gt;"",Q10,IF(R10&lt;&gt;"",R10,""))))))</x:f>
@@ -11337,7 +11503,7 @@
       </x:c>
       <x:c r="N10" s="4"/>
       <x:c r="O10" s="4" t="s">
-        <x:v>211</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="P10" s="4"/>
       <x:c r="Q10" s="4"/>
@@ -11359,13 +11525,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
-        <x:v>212</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>213</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5"/>
@@ -11374,20 +11540,20 @@
       </x:c>
       <x:c r="H11" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C11="",G11=""),"",G11-TODAY())</x:f>
-        <x:v>-87</x:v>
+        <x:v>-88</x:v>
       </x:c>
       <x:c r="I11" s="6" t="str">
         <x:f t="shared" si="2">IF(C11="","",IF(G11="","End Date Not Stated",IF(G11&lt;TODAY(),"Expired",IF(G11&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G11&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="K11" s="4" t="s">
-        <x:v>214</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="L11" s="4" t="s">
-        <x:v>215</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:f t="shared" si="3">IF(C11="","",IF(N11&lt;&gt;"",N11,IF(O11&lt;&gt;"",O11,IF(P11&lt;&gt;"",P11,IF(Q11&lt;&gt;"",Q11,IF(R11&lt;&gt;"",R11,""))))))</x:f>
@@ -11395,13 +11561,13 @@
       </x:c>
       <x:c r="N11" s="4"/>
       <x:c r="O11" s="4" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="P11" s="63" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="Q11" s="4" t="s">
         <x:v>216</x:v>
-      </x:c>
-      <x:c r="P11" s="63" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="Q11" s="4" t="s">
-        <x:v>218</x:v>
       </x:c>
       <x:c r="R11" s="4"/>
       <x:c r="S11" s="4" t="str">
@@ -11421,13 +11587,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>219</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>220</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="E12" s="5"/>
       <x:c r="F12" s="5"/>
@@ -11440,13 +11606,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J12" s="4" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="K12" s="4" t="s">
-        <x:v>221</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="L12" s="4" t="s">
-        <x:v>222</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
         <x:f t="shared" si="3">IF(C12="","",IF(N12&lt;&gt;"",N12,IF(O12&lt;&gt;"",O12,IF(P12&lt;&gt;"",P12,IF(Q12&lt;&gt;"",Q12,IF(R12&lt;&gt;"",R12,""))))))</x:f>
@@ -11454,17 +11620,17 @@
       </x:c>
       <x:c r="N12" s="4"/>
       <x:c r="O12" s="4" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="P12" s="63" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="Q12" s="63" t="s">
         <x:v>223</x:v>
-      </x:c>
-      <x:c r="P12" s="63" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="Q12" s="63" t="s">
-        <x:v>225</x:v>
       </x:c>
       <x:c r="R12" s="4"/>
       <x:c r="S12" s="4" t="s">
-        <x:v>226</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="T12" s="5" t="n">
         <x:v>46240</x:v>
@@ -11480,7 +11646,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
         <x:v>Zero International Card Transaction Fees</x:v>
@@ -11497,7 +11663,7 @@
       </x:c>
       <x:c r="H13" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C13="",G13=""),"",G13-TODAY())</x:f>
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="I13" s="6" t="str">
         <x:f t="shared" si="2">IF(C13="","",IF(G13="","End Date Not Stated",IF(G13&lt;TODAY(),"Expired",IF(G13&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G13&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
@@ -11520,16 +11686,16 @@
         <x:v>https://www.tiqmo.com/ar/offers</x:v>
       </x:c>
       <x:c r="O13" s="63" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="P13" s="63" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="Q13" s="63" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="P13" s="63" t="s">
+      <x:c r="R13" s="63" t="s">
         <x:v>228</x:v>
-      </x:c>
-      <x:c r="Q13" s="63" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="R13" s="63" t="s">
-        <x:v>230</x:v>
       </x:c>
       <x:c r="S13" s="4" t="str">
         <x:v>Offer is valid from 1 May to 31 December 2026. It applies outside Saudi Arabia and excludes international online stores, websites and mobile applications. tiqmo standard terms apply.</x:v>
@@ -11563,7 +11729,7 @@
       </x:c>
       <x:c r="H14" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C14="",G14=""),"",G14-TODAY())</x:f>
-        <x:v>-26</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I14" s="6" t="str">
         <x:f t="shared" si="2">IF(C14="","",IF(G14="","End Date Not Stated",IF(G14&lt;TODAY(),"Expired",IF(G14&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G14&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
@@ -12610,7 +12776,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec33113ccc264e56"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08fbabd9ad8d42ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12640,7 +12806,7 @@
   <x:sheetData>
     <x:row r="1" ht="22.649999618530273" customHeight="1">
       <x:c r="A1" s="52" t="s">
-        <x:v>231</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B1" s="52"/>
       <x:c r="C1" s="52"/>
@@ -12678,7 +12844,7 @@
       <x:c r="K2" s="56"/>
       <x:c r="L2" s="56"/>
       <x:c r="M2" s="57" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N2" s="57"/>
       <x:c r="O2" s="57"/>
@@ -12774,61 +12940,61 @@
     </x:row>
     <x:row r="8" ht="30.649999618530273" customHeight="1">
       <x:c r="A8" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B8" s="3" t="s">
+      <x:c r="D8" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C8" s="3" t="s">
+      <x:c r="E8" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D8" s="3" t="s">
+      <x:c r="F8" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E8" s="3" t="s">
+      <x:c r="G8" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="s">
+      <x:c r="H8" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="s">
+      <x:c r="I8" s="3" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="s">
+      <x:c r="J8" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="s">
+      <x:c r="K8" s="3" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J8" s="3" t="s">
+      <x:c r="L8" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K8" s="3" t="s">
+      <x:c r="M8" s="3" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="L8" s="3" t="s">
+      <x:c r="N8" s="3" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="M8" s="3" t="s">
+      <x:c r="O8" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="N8" s="3" t="s">
+      <x:c r="P8" s="3" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="O8" s="3" t="s">
+      <x:c r="Q8" s="3" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="P8" s="3" t="s">
+      <x:c r="R8" s="3" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="Q8" s="3" t="s">
+      <x:c r="S8" s="3" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="R8" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="S8" s="3" t="s">
-        <x:v>22</x:v>
       </x:c>
       <x:c r="T8" s="3" t="str">
         <x:v>Social Post Count</x:v>
@@ -12843,13 +13009,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>232</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>233</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="E9" s="5"/>
       <x:c r="F9" s="5"/>
@@ -12862,31 +13028,31 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J9" s="4" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="K9" s="4" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="L9" s="4" t="s">
         <x:v>234</x:v>
-      </x:c>
-      <x:c r="K9" s="4" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="L9" s="4" t="s">
-        <x:v>236</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:f t="shared" ref="M9:M46" si="3">IF(C9="","",IF(N9&lt;&gt;"",N9,IF(O9&lt;&gt;"",O9,IF(P9&lt;&gt;"",P9,IF(Q9&lt;&gt;"",Q9,IF(R9&lt;&gt;"",R9,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/cashback-system</x:v>
       </x:c>
       <x:c r="N9" s="63" t="s">
-        <x:v>237</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="O9" s="4"/>
       <x:c r="P9" s="63" t="s">
-        <x:v>238</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="Q9" s="4" t="s">
-        <x:v>239</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="R9" s="4"/>
       <x:c r="S9" s="4" t="s">
-        <x:v>240</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="T9" s="5" t="n">
         <x:v>46240</x:v>
@@ -12902,13 +13068,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>241</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>242</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E10" s="5"/>
       <x:c r="F10" s="5"/>
@@ -12917,34 +13083,34 @@
       </x:c>
       <x:c r="H10" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C10="",G10=""),"",G10-TODAY())</x:f>
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="I10" s="6" t="str">
         <x:f t="shared" si="2">IF(C10="","",IF(G10="","End Date Not Stated",IF(G10&lt;TODAY(),"Expired",IF(G10&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G10&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J10" s="4" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="K10" s="4" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="L10" s="4" t="s">
         <x:v>243</x:v>
-      </x:c>
-      <x:c r="K10" s="4" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="L10" s="4" t="s">
-        <x:v>245</x:v>
       </x:c>
       <x:c r="M10" s="9" t="str">
         <x:f t="shared" si="3">IF(C10="","",IF(N10&lt;&gt;"",N10,IF(O10&lt;&gt;"",O10,IF(P10&lt;&gt;"",P10,IF(Q10&lt;&gt;"",Q10,IF(R10&lt;&gt;"",R10,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/urpay-offers/alhabibbedding</x:v>
       </x:c>
       <x:c r="N10" s="4" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="O10" s="4"/>
       <x:c r="P10" s="4"/>
       <x:c r="Q10" s="4"/>
       <x:c r="R10" s="4"/>
       <x:c r="S10" s="4" t="s">
-        <x:v>247</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="T10" s="5" t="n">
         <x:v>46240</x:v>
@@ -12960,13 +13126,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
-        <x:v>248</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>249</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5"/>
@@ -12975,34 +13141,34 @@
       </x:c>
       <x:c r="H11" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C11="",G11=""),"",G11-TODAY())</x:f>
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="I11" s="6" t="str">
         <x:f t="shared" si="2">IF(C11="","",IF(G11="","End Date Not Stated",IF(G11&lt;TODAY(),"Expired",IF(G11&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G11&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="K11" s="4" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="L11" s="4" t="s">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="K11" s="4" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="L11" s="4" t="s">
-        <x:v>252</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:f t="shared" si="3">IF(C11="","",IF(N11&lt;&gt;"",N11,IF(O11&lt;&gt;"",O11,IF(P11&lt;&gt;"",P11,IF(Q11&lt;&gt;"",Q11,IF(R11&lt;&gt;"",R11,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/urpay-offers/squatwolf</x:v>
       </x:c>
       <x:c r="N11" s="4" t="s">
-        <x:v>253</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="O11" s="4"/>
       <x:c r="P11" s="4"/>
       <x:c r="Q11" s="4"/>
       <x:c r="R11" s="4"/>
       <x:c r="S11" s="4" t="s">
-        <x:v>254</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="T11" s="5" t="n">
         <x:v>46240</x:v>
@@ -13018,13 +13184,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>255</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>256</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E12" s="5"/>
       <x:c r="F12" s="5"/>
@@ -13033,34 +13199,34 @@
       </x:c>
       <x:c r="H12" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C12="",G12=""),"",G12-TODAY())</x:f>
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="I12" s="6" t="str">
         <x:f t="shared" si="2">IF(C12="","",IF(G12="","End Date Not Stated",IF(G12&lt;TODAY(),"Expired",IF(G12&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G12&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J12" s="4" t="s">
-        <x:v>257</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="K12" s="4" t="s">
-        <x:v>258</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="L12" s="4" t="s">
-        <x:v>245</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
         <x:f t="shared" si="3">IF(C12="","",IF(N12&lt;&gt;"",N12,IF(O12&lt;&gt;"",O12,IF(P12&lt;&gt;"",P12,IF(Q12&lt;&gt;"",Q12,IF(R12&lt;&gt;"",R12,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/urpay-offers/mag</x:v>
       </x:c>
       <x:c r="N12" s="4" t="s">
-        <x:v>259</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="O12" s="4"/>
       <x:c r="P12" s="4"/>
       <x:c r="Q12" s="4"/>
       <x:c r="R12" s="4"/>
       <x:c r="S12" s="4" t="s">
-        <x:v>260</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="T12" s="5" t="n">
         <x:v>46240</x:v>
@@ -13076,13 +13242,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>261</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>262</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="E13" s="5"/>
       <x:c r="F13" s="5"/>
@@ -13091,34 +13257,34 @@
       </x:c>
       <x:c r="H13" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C13="",G13=""),"",G13-TODAY())</x:f>
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="I13" s="6" t="str">
         <x:f t="shared" si="2">IF(C13="","",IF(G13="","End Date Not Stated",IF(G13&lt;TODAY(),"Expired",IF(G13&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G13&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J13" s="4" t="s">
-        <x:v>263</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="K13" s="4" t="s">
-        <x:v>264</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="L13" s="4" t="s">
-        <x:v>252</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="M13" s="9" t="str">
         <x:f t="shared" si="3">IF(C13="","",IF(N13&lt;&gt;"",N13,IF(O13&lt;&gt;"",O13,IF(P13&lt;&gt;"",P13,IF(Q13&lt;&gt;"",Q13,IF(R13&lt;&gt;"",R13,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/urpay-offers/b-bw</x:v>
       </x:c>
       <x:c r="N13" s="4" t="s">
-        <x:v>265</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O13" s="4"/>
       <x:c r="P13" s="4"/>
       <x:c r="Q13" s="4"/>
       <x:c r="R13" s="4"/>
       <x:c r="S13" s="4" t="s">
-        <x:v>266</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="T13" s="5" t="n">
         <x:v>46240</x:v>
@@ -13134,13 +13300,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B14" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C14" s="4" t="s">
-        <x:v>267</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>268</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E14" s="5"/>
       <x:c r="F14" s="5"/>
@@ -13149,34 +13315,34 @@
       </x:c>
       <x:c r="H14" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C14="",G14=""),"",G14-TODAY())</x:f>
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="I14" s="6" t="str">
         <x:f t="shared" si="2">IF(C14="","",IF(G14="","End Date Not Stated",IF(G14&lt;TODAY(),"Expired",IF(G14&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G14&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J14" s="4" t="s">
-        <x:v>269</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="K14" s="4" t="s">
-        <x:v>270</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="L14" s="4" t="s">
-        <x:v>245</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="M14" s="9" t="str">
         <x:f t="shared" si="3">IF(C14="","",IF(N14&lt;&gt;"",N14,IF(O14&lt;&gt;"",O14,IF(P14&lt;&gt;"",P14,IF(Q14&lt;&gt;"",Q14,IF(R14&lt;&gt;"",R14,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/urpay-offers/nadi-ph</x:v>
       </x:c>
       <x:c r="N14" s="4" t="s">
-        <x:v>271</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="O14" s="4"/>
       <x:c r="P14" s="4"/>
       <x:c r="Q14" s="4"/>
       <x:c r="R14" s="4"/>
       <x:c r="S14" s="4" t="s">
-        <x:v>272</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="T14" s="5" t="n">
         <x:v>46240</x:v>
@@ -13192,13 +13358,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B15" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C15" s="4" t="s">
-        <x:v>273</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>274</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="E15" s="5"/>
       <x:c r="F15" s="5"/>
@@ -13207,34 +13373,34 @@
       </x:c>
       <x:c r="H15" s="7" t="n">
         <x:f t="shared" si="1">IF(OR(C15="",G15=""),"",G15-TODAY())</x:f>
-        <x:v>-57</x:v>
+        <x:v>-58</x:v>
       </x:c>
       <x:c r="I15" s="6" t="str">
         <x:f t="shared" si="2">IF(C15="","",IF(G15="","End Date Not Stated",IF(G15&lt;TODAY(),"Expired",IF(G15&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G15&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J15" s="4" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="K15" s="4" t="s">
-        <x:v>275</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="L15" s="4" t="s">
-        <x:v>276</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="M15" s="9" t="str">
         <x:f t="shared" si="3">IF(C15="","",IF(N15&lt;&gt;"",N15,IF(O15&lt;&gt;"",O15,IF(P15&lt;&gt;"",P15,IF(Q15&lt;&gt;"",Q15,IF(R15&lt;&gt;"",R15,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/urpay-offers/iherb</x:v>
       </x:c>
       <x:c r="N15" s="4" t="s">
-        <x:v>277</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="O15" s="4"/>
       <x:c r="P15" s="4"/>
       <x:c r="Q15" s="4"/>
       <x:c r="R15" s="4"/>
       <x:c r="S15" s="4" t="s">
-        <x:v>278</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="T15" s="5" t="n">
         <x:v>46240</x:v>
@@ -13250,13 +13416,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="4" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="C16" s="4" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="D16" s="4" t="s">
         <x:v>279</x:v>
-      </x:c>
-      <x:c r="C16" s="4" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="D16" s="4" t="s">
-        <x:v>281</x:v>
       </x:c>
       <x:c r="E16" s="5"/>
       <x:c r="F16" s="5"/>
@@ -13269,13 +13435,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J16" s="4" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="K16" s="4" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="L16" s="4" t="s">
         <x:v>282</x:v>
-      </x:c>
-      <x:c r="K16" s="4" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="L16" s="4" t="s">
-        <x:v>284</x:v>
       </x:c>
       <x:c r="M16" s="9" t="str">
         <x:f t="shared" si="3">IF(C16="","",IF(N16&lt;&gt;"",N16,IF(O16&lt;&gt;"",O16,IF(P16&lt;&gt;"",P16,IF(Q16&lt;&gt;"",Q16,IF(R16&lt;&gt;"",R16,""))))))</x:f>
@@ -13284,12 +13450,12 @@
       <x:c r="N16" s="4"/>
       <x:c r="O16" s="4"/>
       <x:c r="P16" s="4" t="s">
-        <x:v>285</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="Q16" s="4"/>
       <x:c r="R16" s="4"/>
       <x:c r="S16" s="4" t="s">
-        <x:v>286</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="T16" s="5" t="n">
         <x:v>46240</x:v>
@@ -14393,7 +14559,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9f047b21d434be4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e0a4e84398a4ea6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14423,7 +14589,7 @@
   <x:sheetData>
     <x:row r="1" ht="22.649999618530273" customHeight="1">
       <x:c r="A1" s="52" t="s">
-        <x:v>287</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B1" s="52"/>
       <x:c r="C1" s="52"/>
@@ -14461,7 +14627,7 @@
       <x:c r="K2" s="56"/>
       <x:c r="L2" s="56"/>
       <x:c r="M2" s="57" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N2" s="57"/>
       <x:c r="O2" s="57"/>
@@ -14557,61 +14723,61 @@
     </x:row>
     <x:row r="8" ht="30.649999618530273" customHeight="1">
       <x:c r="A8" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B8" s="3" t="s">
+      <x:c r="D8" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C8" s="3" t="s">
+      <x:c r="E8" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D8" s="3" t="s">
+      <x:c r="F8" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E8" s="3" t="s">
+      <x:c r="G8" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="s">
+      <x:c r="H8" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="s">
+      <x:c r="I8" s="3" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="s">
+      <x:c r="J8" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="s">
+      <x:c r="K8" s="3" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J8" s="3" t="s">
+      <x:c r="L8" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K8" s="3" t="s">
+      <x:c r="M8" s="3" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="L8" s="3" t="s">
+      <x:c r="N8" s="3" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="M8" s="3" t="s">
+      <x:c r="O8" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="N8" s="3" t="s">
+      <x:c r="P8" s="3" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="O8" s="3" t="s">
+      <x:c r="Q8" s="3" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="P8" s="3" t="s">
+      <x:c r="R8" s="3" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="Q8" s="3" t="s">
+      <x:c r="S8" s="3" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="R8" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="S8" s="3" t="s">
-        <x:v>22</x:v>
       </x:c>
       <x:c r="T8" s="3" t="str">
         <x:v>Social Post Count</x:v>
@@ -14626,13 +14792,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>288</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>289</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="E9" s="5"/>
       <x:c r="F9" s="5">
@@ -14643,20 +14809,20 @@
       </x:c>
       <x:c r="H9" s="7" t="n">
         <x:f t="shared" ref="H9:H42" si="1">IF(OR(C9="",G9=""),"",G9-TODAY())</x:f>
-        <x:v>-19</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="I9" s="6" t="str">
         <x:f t="shared" ref="I9:I42" si="2">IF(C9="","",IF(G9="","End Date Not Stated",IF(G9&lt;TODAY(),"Expired",IF(G9&lt;=TODAY()+7,"Expiring ≤7 Days",IF(G9&lt;=TODAY()+30,"Expiring 8–30 Days","Active")))))</x:f>
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J9" s="4" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="K9" s="4" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="L9" s="4" t="s">
         <x:v>290</x:v>
-      </x:c>
-      <x:c r="K9" s="4" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="L9" s="4" t="s">
-        <x:v>292</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:f t="shared" ref="M9:M42" si="3">IF(C9="","",IF(N9&lt;&gt;"",N9,IF(O9&lt;&gt;"",O9,IF(P9&lt;&gt;"",P9,IF(Q9&lt;&gt;"",Q9,IF(R9&lt;&gt;"",R9,""))))))</x:f>
@@ -14664,17 +14830,17 @@
       </x:c>
       <x:c r="N9" s="4"/>
       <x:c r="O9" s="63" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="P9" s="4" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="Q9" s="63" t="s">
         <x:v>293</x:v>
-      </x:c>
-      <x:c r="P9" s="4" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="Q9" s="63" t="s">
-        <x:v>295</x:v>
       </x:c>
       <x:c r="R9" s="4"/>
       <x:c r="S9" s="4" t="s">
-        <x:v>296</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="T9" s="5" t="n">
         <x:v>46240</x:v>
@@ -14690,10 +14856,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>297</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="D10" s="4" t="str">
         <x:v>Use alinma pay Cashback Cards internationally with no foreign transaction fees, no fees on the first two international cash withdrawals, and cashback on eligible purchases.</x:v>
@@ -14715,7 +14881,7 @@
         <x:v>Zero international transaction fees, first two international cash withdrawals free, plus cashback on eligible purchases</x:v>
       </x:c>
       <x:c r="L10" s="4" t="s">
-        <x:v>298</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="M10" s="9" t="str">
         <x:f t="shared" si="3">IF(C10="","",IF(N10&lt;&gt;"",N10,IF(O10&lt;&gt;"",O10,IF(P10&lt;&gt;"",P10,IF(Q10&lt;&gt;"",Q10,IF(R10&lt;&gt;"",R10,""))))))</x:f>
@@ -14725,7 +14891,7 @@
       <x:c r="O10" s="4"/>
       <x:c r="P10" s="4"/>
       <x:c r="Q10" s="63" t="s">
-        <x:v>299</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="R10" s="4"/>
       <x:c r="S10" s="4" t="str">
@@ -14745,13 +14911,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
-        <x:v>300</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>301</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5"/>
@@ -14764,13 +14930,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="K11" s="4" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="L11" s="4" t="s">
         <x:v>302</x:v>
-      </x:c>
-      <x:c r="K11" s="4" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="L11" s="4" t="s">
-        <x:v>304</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:f t="shared" si="3">IF(C11="","",IF(N11&lt;&gt;"",N11,IF(O11&lt;&gt;"",O11,IF(P11&lt;&gt;"",P11,IF(Q11&lt;&gt;"",Q11,IF(R11&lt;&gt;"",R11,""))))))</x:f>
@@ -14778,17 +14944,17 @@
       </x:c>
       <x:c r="N11" s="4"/>
       <x:c r="O11" s="63" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="P11" s="4" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="Q11" s="63" t="s">
         <x:v>305</x:v>
-      </x:c>
-      <x:c r="P11" s="4" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="Q11" s="63" t="s">
-        <x:v>307</x:v>
       </x:c>
       <x:c r="R11" s="4"/>
       <x:c r="S11" s="4" t="s">
-        <x:v>308</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="T11" s="5" t="n">
         <x:v>46240</x:v>
@@ -14804,13 +14970,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>309</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>310</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="E12" s="5">
         <x:v>46068</x:v>
@@ -14825,13 +14991,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J12" s="4" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="K12" s="4" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="L12" s="4" t="s">
         <x:v>311</x:v>
-      </x:c>
-      <x:c r="K12" s="4" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="L12" s="4" t="s">
-        <x:v>313</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
         <x:f t="shared" si="3">IF(C12="","",IF(N12&lt;&gt;"",N12,IF(O12&lt;&gt;"",O12,IF(P12&lt;&gt;"",P12,IF(Q12&lt;&gt;"",Q12,IF(R12&lt;&gt;"",R12,""))))))</x:f>
@@ -14841,11 +15007,11 @@
       <x:c r="O12" s="4"/>
       <x:c r="P12" s="4"/>
       <x:c r="Q12" s="63" t="s">
-        <x:v>314</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="R12" s="4"/>
       <x:c r="S12" s="4" t="s">
-        <x:v>170</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="T12" s="5" t="n">
         <x:v>46240</x:v>
@@ -15953,7 +16119,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f406d3836b54fc3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b9c17226a4e4a7d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15974,7 +16140,7 @@
   <x:sheetData>
     <x:row r="1" ht="21.5">
       <x:c r="A1" s="58" t="s">
-        <x:v>315</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B1" s="58"/>
       <x:c r="C1" s="58"/>
@@ -15998,119 +16164,119 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="26" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="B4" s="26" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="C4" s="26" t="s">
         <x:v>316</x:v>
       </x:c>
-      <x:c r="B4" s="26" t="s">
+      <x:c r="D4" s="26" t="s">
         <x:v>317</x:v>
-      </x:c>
-      <x:c r="C4" s="26" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="D4" s="26" t="s">
-        <x:v>319</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="38.650001525878906" customHeight="1">
       <x:c r="A5" s="27" t="s">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B5" s="27" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="C5" s="27" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="D5" s="27" t="s">
         <x:v>320</x:v>
-      </x:c>
-      <x:c r="C5" s="27" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="D5" s="27" t="s">
-        <x:v>322</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="38.650001525878906" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>279</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>320</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>323</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>324</x:v>
+        <x:v>322</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="38.650001525878906" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>197</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>320</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>325</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>326</x:v>
+        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="38.650001525878906" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>320</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="C8" s="4" t="s">
-        <x:v>327</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>328</x:v>
+        <x:v>326</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="38.650001525878906" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>320</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>329</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>330</x:v>
+        <x:v>328</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="38.650001525878906" customHeight="1">
       <x:c r="A10" s="28" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B10" s="28" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="C10" s="28" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="s">
         <x:v>331</x:v>
-      </x:c>
-      <x:c r="C10" s="28" t="s">
-        <x:v>332</x:v>
-      </x:c>
-      <x:c r="D10" s="28" t="s">
-        <x:v>333</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="38.650001525878906" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>186</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="C11" s="4" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="s">
         <x:v>334</x:v>
-      </x:c>
-      <x:c r="C11" s="4" t="s">
-        <x:v>335</x:v>
-      </x:c>
-      <x:c r="D11" s="4" t="s">
-        <x:v>336</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="16.5">
       <x:c r="A14" s="46" t="s">
-        <x:v>337</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B14" s="46"/>
       <x:c r="C14" s="46"/>
@@ -16184,7 +16350,7 @@
     <x:row r="21" ht="36.650001525878906" customHeight="1"/>
     <x:row r="22" ht="36.650001525878906" customHeight="1">
       <x:c r="A22" s="45" t="s">
-        <x:v>338</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B22" s="45"/>
       <x:c r="C22" s="45"/>
@@ -16197,99 +16363,99 @@
     <x:row r="23" ht="32" customHeight="1"/>
     <x:row r="24" ht="32" customHeight="1">
       <x:c r="A24" s="21" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="B24" s="21" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="D24" s="29" t="s">
         <x:v>339</x:v>
       </x:c>
-      <x:c r="B24" s="21" t="s">
+      <x:c r="E24" s="29" t="s">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="D24" s="29" t="s">
+      <x:c r="F24" s="29" t="s">
         <x:v>341</x:v>
       </x:c>
-      <x:c r="E24" s="29" t="s">
+      <x:c r="G24" s="29" t="s">
         <x:v>342</x:v>
       </x:c>
-      <x:c r="F24" s="29" t="s">
+      <x:c r="H24" s="29" t="s">
         <x:v>343</x:v>
-      </x:c>
-      <x:c r="G24" s="29" t="s">
-        <x:v>344</x:v>
-      </x:c>
-      <x:c r="H24" s="29" t="s">
-        <x:v>345</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="46.650001525878906" customHeight="1">
       <x:c r="A25" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B25" s="1" t="str">
         <x:v>Campaign rows are populated automatically from approved monitoring data.</x:v>
       </x:c>
       <x:c r="D25" s="4" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="E25" s="4" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="F25" s="4" t="s">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="E25" s="4" t="s">
+      <x:c r="G25" s="4" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="F25" s="4" t="s">
+      <x:c r="H25" s="4" t="s">
         <x:v>349</x:v>
-      </x:c>
-      <x:c r="G25" s="4" t="s">
-        <x:v>350</x:v>
-      </x:c>
-      <x:c r="H25" s="4" t="s">
-        <x:v>351</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="46.650001525878906" customHeight="1">
       <x:c r="A26" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B26" s="1" t="str">
         <x:v>Merchant offers are shown only as an active approved count in each competitor sheet.</x:v>
       </x:c>
       <x:c r="D26" s="4" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="E26" s="4" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="F26" s="4" t="s">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="E26" s="4" t="s">
+      <x:c r="G26" s="4" t="s">
         <x:v>354</x:v>
       </x:c>
-      <x:c r="F26" s="4" t="s">
+      <x:c r="H26" s="4" t="s">
         <x:v>355</x:v>
-      </x:c>
-      <x:c r="G26" s="4" t="s">
-        <x:v>356</x:v>
-      </x:c>
-      <x:c r="H26" s="4" t="s">
-        <x:v>357</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="46.650001525878906" customHeight="1">
       <x:c r="A27" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B27" s="1" t="str">
         <x:v>Use Remittance for all international-transfer campaigns; these rows are highlighted automatically.</x:v>
       </x:c>
       <x:c r="D27" s="4" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="E27" s="4" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="F27" s="4" t="s">
         <x:v>359</x:v>
       </x:c>
-      <x:c r="E27" s="4" t="s">
+      <x:c r="G27" s="4" t="s">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="F27" s="4" t="s">
+      <x:c r="H27" s="4" t="s">
         <x:v>361</x:v>
-      </x:c>
-      <x:c r="G27" s="4" t="s">
-        <x:v>362</x:v>
-      </x:c>
-      <x:c r="H27" s="4" t="s">
-        <x:v>363</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="30.649999618530273" customHeight="1">
       <x:c r="A28" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B28" s="1" t="str">
         <x:v>Each listed campaign must retain a direct official campaign page or confirmed official social source.</x:v>
@@ -16297,7 +16463,7 @@
     </x:row>
     <x:row r="29" ht="30.649999618530273" customHeight="1">
       <x:c r="A29" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B29" s="1" t="str">
         <x:v>Expired campaigns are excluded; leave End Date blank only when the official source does not state it.</x:v>
@@ -16305,7 +16471,7 @@
     </x:row>
     <x:row r="30" ht="30.649999618530273" customHeight="1">
       <x:c r="A30" s="1" t="s">
-        <x:v>366</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B30" s="1" t="str">
         <x:v>Campaigns are sorted newest first using Start Date, Published Date, and detection date.</x:v>
@@ -16313,7 +16479,7 @@
     </x:row>
     <x:row r="31" ht="30.649999618530273" customHeight="1">
       <x:c r="A31" s="1" t="s">
-        <x:v>367</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B31" s="1" t="str">
         <x:v>Dashboard campaign KPIs, category mix, remittance analysis, and the 14-day social Bar Chart update automatically.</x:v>
@@ -16321,7 +16487,7 @@
     </x:row>
     <x:row r="32" ht="30.649999618530273" customHeight="1">
       <x:c r="A32" s="1" t="s">
-        <x:v>368</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B32" s="1" t="str">
         <x:v>Social Post Count includes confirmed posts linked to the campaign; Published Platforms lists the relevant channels.</x:v>

--- a/competitor_campaigns_template.xlsx
+++ b/competitor_campaigns_template.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Dashboard" sheetId="1" r:id="R93a0e4df54b04dc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STC Bank" sheetId="2" r:id="R0f4b2a310a5d4cbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="barq" sheetId="3" r:id="Rccaebdff65664c1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobily Pay" sheetId="4" r:id="Rd395576924ac4b0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tiqmo" sheetId="5" r:id="R6462069155004c18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="urpay" sheetId="6" r:id="Rd4613b455b3d4e0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="alinma pay" sheetId="7" r:id="Rf6067ccee45942f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Guide" sheetId="8" r:id="R9cd53a35de31429f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Dashboard" sheetId="1" r:id="R5f1577cb48344911"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STC Bank" sheetId="2" r:id="R4397643bb0234d49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="barq" sheetId="3" r:id="R12300eafff044100"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobily Pay" sheetId="4" r:id="Rebfd25cee29947ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tiqmo" sheetId="5" r:id="Rdd72ea7ed1ef43d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="urpay" sheetId="6" r:id="Rc78d7a8474e2417b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="alinma pay" sheetId="7" r:id="Rb9242eb315bf4d34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Guide" sheetId="8" r:id="R14f34643664643b0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -33,9 +33,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Summary</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Published Date</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Start Date</x:t>
@@ -3853,7 +3850,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rec83b2805158415e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R86800e536a1e482d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3883,7 +3880,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R78fe1c7190874992"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R982afbaaab63415d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3913,7 +3910,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7361499901e04baa"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb9b4cbebddbb4e95"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3943,7 +3940,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3c903b4bd7cd4313"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfe392f48126b48c5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5019,8 +5016,9 @@
     </x:row>
     <x:row r="27" ht="19" customHeight="1">
       <x:c r="A27" s="211"/>
-      <x:c r="B27" s="211">
+      <x:c r="B27" s="211" t="n">
         <x:f t="shared" ref="B27:G27" si="0">SUM(B21:B26)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C27" s="211">
         <x:f t="shared" si="0"/>
@@ -5116,8 +5114,9 @@
       <x:c r="L31" s="211"/>
       <x:c r="M31" s="211"/>
       <x:c r="N31" s="211"/>
-      <x:c r="X31">
+      <x:c r="X31" t="n">
         <x:f t="shared" ref="X31:X36" si="1">A10</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Y31"/>
     </x:row>
@@ -5411,8 +5410,9 @@
     </x:row>
     <x:row r="60">
       <x:c r="A60"/>
-      <x:c r="B60">
+      <x:c r="B60" t="n">
         <x:f t="shared" ref="B60:F60" si="2">SUM(B54:B59)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C60">
         <x:f t="shared" si="2"/>
@@ -5697,7 +5697,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fd6ef60985e444e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34cd1ca6c38d4eb5"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -5812,6 +5812,7 @@
     <x:col min="19" max="19" width="50" customWidth="1"/>
     <x:col min="20" max="20" width="13" customWidth="1"/>
     <x:col min="21" max="21" width="30" customWidth="1"/>
+    <x:col min="5" max="5" width="0.10999999940395355" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22.649999618530273" customHeight="1">
@@ -5961,50 +5962,50 @@
       <x:c r="D8" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E8" s="3" t="s">
+      <x:c r="E8" s="3" t="str">
+        <x:v> </x:v>
+      </x:c>
+      <x:c r="F8" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="s">
+      <x:c r="G8" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="s">
+      <x:c r="H8" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="s">
+      <x:c r="I8" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="s">
+      <x:c r="J8" s="3" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J8" s="3" t="s">
+      <x:c r="K8" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K8" s="3" t="s">
+      <x:c r="L8" s="3" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L8" s="3" t="s">
+      <x:c r="M8" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="M8" s="3" t="s">
+      <x:c r="N8" s="3" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="N8" s="3" t="s">
+      <x:c r="O8" s="3" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="O8" s="3" t="s">
+      <x:c r="P8" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="P8" s="3" t="s">
+      <x:c r="Q8" s="3" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="Q8" s="3" t="s">
+      <x:c r="R8" s="3" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="R8" s="3" t="s">
+      <x:c r="S8" s="3" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="S8" s="3" t="s">
-        <x:v>20</x:v>
       </x:c>
       <x:c r="T8" s="3" t="str">
         <x:v>Social Post Count</x:v>
@@ -6019,13 +6020,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C9" s="4" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C9" s="4" t="s">
+      <x:c r="D9" s="4" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="E9" s="5"/>
       <x:c r="F9" s="5">
@@ -6043,32 +6044,32 @@
         <x:v>Expiring ≤7 Days</x:v>
       </x:c>
       <x:c r="J9" s="4" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K9" s="4" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="K9" s="4" t="s">
+      <x:c r="L9" s="4" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="L9" s="4" t="s">
-        <x:v>26</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:f>IF(C9="","",IF(N9&lt;&gt;"",N9,IF(O9&lt;&gt;"",O9,IF(P9&lt;&gt;"",P9,IF(Q9&lt;&gt;"",Q9,IF(R9&lt;&gt;"",R9,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/international-purchases-with-0-fees</x:v>
       </x:c>
       <x:c r="N9" s="4" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="O9" s="4" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="O9" s="4" t="s">
+      <x:c r="P9" s="4" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="P9" s="4" t="s">
+      <x:c r="Q9" s="63" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="Q9" s="63" t="s">
+      <x:c r="R9" s="63" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="R9" s="63" t="s">
-        <x:v>31</x:v>
       </x:c>
       <x:c r="S9" s="4" t="str">
         <x:v>0% international POS fee campaign is valid from 17 May to 31 August 2026. International e-commerce purchases are excluded; free withdrawals apply to international ATMs. Digital-wallet purchases are eligible under the official terms.</x:v>
@@ -6087,13 +6088,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D10" s="4" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="D10" s="4" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="E10" s="5"/>
       <x:c r="F10" s="5">
@@ -6111,29 +6112,29 @@
         <x:v>Expiring ≤7 Days</x:v>
       </x:c>
       <x:c r="J10" s="4" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K10" s="4" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="K10" s="4" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="L10" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="M10" s="9" t="str">
         <x:f>IF(C10="","",IF(N10&lt;&gt;"",N10,IF(O10&lt;&gt;"",O10,IF(P10&lt;&gt;"",P10,IF(Q10&lt;&gt;"",Q10,IF(R10&lt;&gt;"",R10,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/international-purchases-with-0-fees</x:v>
       </x:c>
       <x:c r="N10" s="63" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O10" s="4" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="P10" s="4" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="P10" s="4" t="s">
+      <x:c r="Q10" s="63" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="Q10" s="63" t="s">
-        <x:v>38</x:v>
       </x:c>
       <x:c r="R10" s="4"/>
       <x:c r="S10" s="4" t="str">
@@ -6153,13 +6154,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="D11" s="4" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5"/>
@@ -6175,20 +6176,20 @@
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K11" s="4" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="K11" s="4" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="L11" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:f t="shared" ref="M11:M53" si="4">IF(C11="","",IF(N11&lt;&gt;"",N11,IF(O11&lt;&gt;"",O11,IF(P11&lt;&gt;"",P11,IF(Q11&lt;&gt;"",Q11,IF(R11&lt;&gt;"",R11,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/visa_cards_rewards</x:v>
       </x:c>
       <x:c r="N11" s="63" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="O11" s="4"/>
       <x:c r="P11" s="4"/>
@@ -6211,17 +6212,15 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D12" s="4" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D12" s="4" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E12" s="5">
-        <x:v>46217</x:v>
-      </x:c>
+      <x:c r="E12" s="5"/>
       <x:c r="F12" s="5"/>
       <x:c r="G12" s="5"/>
       <x:c r="H12" s="7" t="str">
@@ -6232,13 +6231,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J12" s="4" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K12" s="4" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="K12" s="4" t="s">
+      <x:c r="L12" s="4" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="L12" s="4" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
         <x:f t="shared" si="4">IF(C12="","",IF(N12&lt;&gt;"",N12,IF(O12&lt;&gt;"",O12,IF(P12&lt;&gt;"",P12,IF(Q12&lt;&gt;"",Q12,IF(R12&lt;&gt;"",R12,""))))))</x:f>
@@ -6246,17 +6245,17 @@
       </x:c>
       <x:c r="N12" s="4"/>
       <x:c r="O12" s="63" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="P12" s="63" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="P12" s="63" t="s">
+      <x:c r="Q12" s="63" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="Q12" s="63" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="R12" s="4"/>
       <x:c r="S12" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="T12" s="5" t="n">
         <x:v>46240</x:v>
@@ -6272,13 +6271,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C13" s="4" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C13" s="4" t="s">
+      <x:c r="D13" s="4" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="D13" s="4" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="E13" s="5"/>
       <x:c r="F13" s="5"/>
@@ -6294,20 +6293,20 @@
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J13" s="4" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="K13" s="4" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="K13" s="4" t="s">
+      <x:c r="L13" s="4" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="L13" s="4" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="M13" s="9" t="str">
         <x:f t="shared" si="4">IF(C13="","",IF(N13&lt;&gt;"",N13,IF(O13&lt;&gt;"",O13,IF(P13&lt;&gt;"",P13,IF(Q13&lt;&gt;"",Q13,IF(R13&lt;&gt;"",R13,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/almatar-offer</x:v>
       </x:c>
       <x:c r="N13" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="O13" s="4"/>
       <x:c r="P13" s="4"/>
@@ -6330,13 +6329,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B14" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C14" s="4" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D14" s="4" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="D14" s="4" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="E14" s="5"/>
       <x:c r="F14" s="5"/>
@@ -6352,20 +6351,20 @@
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J14" s="4" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K14" s="4" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="K14" s="4" t="s">
+      <x:c r="L14" s="4" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="L14" s="4" t="s">
-        <x:v>64</x:v>
       </x:c>
       <x:c r="M14" s="9" t="str">
         <x:f t="shared" si="4">IF(C14="","",IF(N14&lt;&gt;"",N14,IF(O14&lt;&gt;"",O14,IF(P14&lt;&gt;"",P14,IF(Q14&lt;&gt;"",Q14,IF(R14&lt;&gt;"",R14,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/whites-offer</x:v>
       </x:c>
       <x:c r="N14" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="O14" s="4"/>
       <x:c r="P14" s="4"/>
@@ -6388,13 +6387,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B15" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C15" s="4" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D15" s="4" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="D15" s="4" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="E15" s="5"/>
       <x:c r="F15" s="5"/>
@@ -6410,20 +6409,20 @@
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J15" s="4" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="K15" s="4" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="K15" s="4" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="L15" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M15" s="9" t="str">
         <x:f t="shared" si="4">IF(C15="","",IF(N15&lt;&gt;"",N15,IF(O15&lt;&gt;"",O15,IF(P15&lt;&gt;"",P15,IF(Q15&lt;&gt;"",Q15,IF(R15&lt;&gt;"",R15,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/huawei</x:v>
       </x:c>
       <x:c r="N15" s="4" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="O15" s="4"/>
       <x:c r="P15" s="4"/>
@@ -6446,13 +6445,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C16" s="4" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D16" s="4" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="D16" s="4" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="E16" s="5"/>
       <x:c r="F16" s="5">
@@ -6470,20 +6469,20 @@
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J16" s="4" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="K16" s="4" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="K16" s="4" t="s">
+      <x:c r="L16" s="4" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="L16" s="4" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="M16" s="9" t="str">
         <x:f t="shared" si="4">IF(C16="","",IF(N16&lt;&gt;"",N16,IF(O16&lt;&gt;"",O16,IF(P16&lt;&gt;"",P16,IF(Q16&lt;&gt;"",Q16,IF(R16&lt;&gt;"",R16,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/loca</x:v>
       </x:c>
       <x:c r="N16" s="4" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="O16" s="4"/>
       <x:c r="P16" s="4"/>
@@ -6506,13 +6505,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B17" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C17" s="4" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D17" s="4" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="D17" s="4" t="s">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="E17" s="5"/>
       <x:c r="F17" s="5"/>
@@ -6528,20 +6527,20 @@
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J17" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K17" s="4" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="L17" s="4" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="L17" s="4" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="M17" s="9" t="str">
         <x:f t="shared" si="4">IF(C17="","",IF(N17&lt;&gt;"",N17,IF(O17&lt;&gt;"",O17,IF(P17&lt;&gt;"",P17,IF(Q17&lt;&gt;"",Q17,IF(R17&lt;&gt;"",R17,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/canton-offer</x:v>
       </x:c>
       <x:c r="N17" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="O17" s="4"/>
       <x:c r="P17" s="4"/>
@@ -6564,13 +6563,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B18" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C18" s="4" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D18" s="4" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="D18" s="4" t="s">
-        <x:v>82</x:v>
       </x:c>
       <x:c r="E18" s="5"/>
       <x:c r="F18" s="5"/>
@@ -6586,20 +6585,20 @@
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J18" s="4" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="K18" s="4" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="K18" s="4" t="s">
-        <x:v>84</x:v>
-      </x:c>
       <x:c r="L18" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="M18" s="9" t="str">
         <x:f t="shared" si="4">IF(C18="","",IF(N18&lt;&gt;"",N18,IF(O18&lt;&gt;"",O18,IF(P18&lt;&gt;"",P18,IF(Q18&lt;&gt;"",Q18,IF(R18&lt;&gt;"",R18,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/boost-your-health</x:v>
       </x:c>
       <x:c r="N18" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="O18" s="4"/>
       <x:c r="P18" s="4"/>
@@ -6622,13 +6621,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B19" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C19" s="4" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D19" s="4" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="D19" s="4" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="E19" s="5"/>
       <x:c r="F19" s="5"/>
@@ -6644,20 +6643,20 @@
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J19" s="4" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="K19" s="4" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="K19" s="4" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="L19" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="M19" s="9" t="str">
         <x:f t="shared" si="4">IF(C19="","",IF(N19&lt;&gt;"",N19,IF(O19&lt;&gt;"",O19,IF(P19&lt;&gt;"",P19,IF(Q19&lt;&gt;"",Q19,IF(R19&lt;&gt;"",R19,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/shop-workout-and-save-with-10-off-on-gosport</x:v>
       </x:c>
       <x:c r="N19" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="O19" s="4"/>
       <x:c r="P19" s="4"/>
@@ -6680,13 +6679,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B20" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C20" s="4" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D20" s="4" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="D20" s="4" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="E20" s="5"/>
       <x:c r="F20" s="5"/>
@@ -6702,20 +6701,20 @@
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J20" s="4" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="K20" s="4" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="K20" s="4" t="s">
+      <x:c r="L20" s="4" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="L20" s="4" t="s">
-        <x:v>95</x:v>
       </x:c>
       <x:c r="M20" s="9" t="str">
         <x:f t="shared" si="4">IF(C20="","",IF(N20&lt;&gt;"",N20,IF(O20&lt;&gt;"",O20,IF(P20&lt;&gt;"",P20,IF(Q20&lt;&gt;"",Q20,IF(R20&lt;&gt;"",R20,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/iherb-offer</x:v>
       </x:c>
       <x:c r="N20" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="O20" s="4"/>
       <x:c r="P20" s="4"/>
@@ -6738,13 +6737,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B21" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C21" s="4" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D21" s="4" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="D21" s="4" t="s">
-        <x:v>98</x:v>
       </x:c>
       <x:c r="E21" s="5"/>
       <x:c r="F21" s="5"/>
@@ -6760,20 +6759,20 @@
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J21" s="4" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="K21" s="4" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="K21" s="4" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="L21" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="M21" s="9" t="str">
         <x:f t="shared" si="4">IF(C21="","",IF(N21&lt;&gt;"",N21,IF(O21&lt;&gt;"",O21,IF(P21&lt;&gt;"",P21,IF(Q21&lt;&gt;"",Q21,IF(R21&lt;&gt;"",R21,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/alothaim-entertainment</x:v>
       </x:c>
       <x:c r="N21" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="O21" s="4"/>
       <x:c r="P21" s="4"/>
@@ -6796,13 +6795,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B22" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C22" s="4" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D22" s="4" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="D22" s="4" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="E22" s="5"/>
       <x:c r="F22" s="5"/>
@@ -6818,20 +6817,20 @@
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J22" s="4" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="K22" s="4" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="K22" s="4" t="s">
+      <x:c r="L22" s="4" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="L22" s="4" t="s">
-        <x:v>106</x:v>
       </x:c>
       <x:c r="M22" s="9" t="str">
         <x:f t="shared" si="4">IF(C22="","",IF(N22&lt;&gt;"",N22,IF(O22&lt;&gt;"",O22,IF(P22&lt;&gt;"",P22,IF(Q22&lt;&gt;"",Q22,IF(R22&lt;&gt;"",R22,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/yelo</x:v>
       </x:c>
       <x:c r="N22" s="4" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="O22" s="4"/>
       <x:c r="P22" s="4"/>
@@ -6854,13 +6853,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B23" s="4" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C23" s="4" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="C23" s="4" t="s">
+      <x:c r="D23" s="4" t="s">
         <x:v>109</x:v>
-      </x:c>
-      <x:c r="D23" s="4" t="s">
-        <x:v>110</x:v>
       </x:c>
       <x:c r="E23" s="5"/>
       <x:c r="F23" s="5">
@@ -6878,35 +6877,35 @@
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J23" s="4" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="K23" s="4" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="K23" s="4" t="s">
+      <x:c r="L23" s="4" t="s">
         <x:v>112</x:v>
-      </x:c>
-      <x:c r="L23" s="4" t="s">
-        <x:v>113</x:v>
       </x:c>
       <x:c r="M23" s="9" t="str">
         <x:f t="shared" si="4">IF(C23="","",IF(N23&lt;&gt;"",N23,IF(O23&lt;&gt;"",O23,IF(P23&lt;&gt;"",P23,IF(Q23&lt;&gt;"",Q23,IF(R23&lt;&gt;"",R23,""))))))</x:f>
         <x:v>https://stcbank.com.sa/en/web/guest/w/stcbank-championship</x:v>
       </x:c>
       <x:c r="N23" s="4" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="O23" s="4" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="O23" s="4" t="s">
+      <x:c r="P23" s="4" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="P23" s="4" t="s">
+      <x:c r="Q23" s="63" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="Q23" s="63" t="s">
+      <x:c r="R23" s="63" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="R23" s="63" t="s">
+      <x:c r="S23" s="4" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="S23" s="4" t="s">
-        <x:v>119</x:v>
       </x:c>
       <x:c r="T23" s="5" t="n">
         <x:v>46240</x:v>
@@ -8013,7 +8012,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R351f20ef52c0471c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4236429e2e8341d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8039,11 +8038,12 @@
     <x:col min="19" max="19" width="50" customWidth="1"/>
     <x:col min="20" max="20" width="13" customWidth="1"/>
     <x:col min="21" max="21" width="30" customWidth="1"/>
+    <x:col min="5" max="5" width="0.10999999940395355" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22.649999618530273" customHeight="1">
       <x:c r="A1" s="52" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B1" s="52"/>
       <x:c r="C1" s="52"/>
@@ -8188,50 +8188,50 @@
       <x:c r="D8" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E8" s="3" t="s">
+      <x:c r="E8" s="3" t="str">
+        <x:v> </x:v>
+      </x:c>
+      <x:c r="F8" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="s">
+      <x:c r="G8" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="s">
+      <x:c r="H8" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="s">
+      <x:c r="I8" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="s">
+      <x:c r="J8" s="3" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J8" s="3" t="s">
+      <x:c r="K8" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K8" s="3" t="s">
+      <x:c r="L8" s="3" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L8" s="3" t="s">
+      <x:c r="M8" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="M8" s="3" t="s">
+      <x:c r="N8" s="3" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="N8" s="3" t="s">
+      <x:c r="O8" s="3" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="O8" s="3" t="s">
+      <x:c r="P8" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="P8" s="3" t="s">
+      <x:c r="Q8" s="3" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="Q8" s="3" t="s">
+      <x:c r="R8" s="3" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="R8" s="3" t="s">
+      <x:c r="S8" s="3" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="S8" s="3" t="s">
-        <x:v>20</x:v>
       </x:c>
       <x:c r="T8" s="3" t="str">
         <x:v>Social Post Count</x:v>
@@ -8246,13 +8246,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="E9" s="5"/>
       <x:c r="F9" s="5"/>
@@ -8265,13 +8265,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J9" s="4" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="K9" s="4" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="K9" s="4" t="s">
+      <x:c r="L9" s="4" t="s">
         <x:v>124</x:v>
-      </x:c>
-      <x:c r="L9" s="4" t="s">
-        <x:v>125</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:f>IF(C9="","",IF(N9&lt;&gt;"",N9,IF(O9&lt;&gt;"",O9,IF(P9&lt;&gt;"",P9,IF(Q9&lt;&gt;"",Q9,IF(R9&lt;&gt;"",R9,""))))))</x:f>
@@ -8279,15 +8279,15 @@
       </x:c>
       <x:c r="N9" s="4"/>
       <x:c r="O9" s="63" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="P9" s="4"/>
       <x:c r="Q9" s="63" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="R9" s="4"/>
       <x:c r="S9" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="T9" s="5" t="n">
         <x:v>46240</x:v>
@@ -8303,13 +8303,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D10" s="4" t="s">
         <x:v>129</x:v>
-      </x:c>
-      <x:c r="D10" s="4" t="s">
-        <x:v>130</x:v>
       </x:c>
       <x:c r="E10" s="5"/>
       <x:c r="F10" s="5"/>
@@ -8322,13 +8322,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J10" s="4" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="K10" s="4" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="K10" s="4" t="s">
+      <x:c r="L10" s="4" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="L10" s="4" t="s">
-        <x:v>133</x:v>
       </x:c>
       <x:c r="M10" s="9" t="str">
         <x:f t="shared" ref="M10:M42" si="4">IF(C10="","",IF(N10&lt;&gt;"",N10,IF(O10&lt;&gt;"",O10,IF(P10&lt;&gt;"",P10,IF(Q10&lt;&gt;"",Q10,IF(R10&lt;&gt;"",R10,""))))))</x:f>
@@ -8338,11 +8338,11 @@
       <x:c r="O10" s="4"/>
       <x:c r="P10" s="4"/>
       <x:c r="Q10" s="63" t="s">
-        <x:v>134</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="R10" s="4"/>
       <x:c r="S10" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="T10" s="5" t="n">
         <x:v>46240</x:v>
@@ -8358,13 +8358,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="D11" s="4" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5"/>
@@ -8377,13 +8377,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K11" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="L11" s="4" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:f t="shared" si="4">IF(C11="","",IF(N11&lt;&gt;"",N11,IF(O11&lt;&gt;"",O11,IF(P11&lt;&gt;"",P11,IF(Q11&lt;&gt;"",Q11,IF(R11&lt;&gt;"",R11,""))))))</x:f>
@@ -8393,11 +8393,11 @@
       <x:c r="O11" s="4"/>
       <x:c r="P11" s="4"/>
       <x:c r="Q11" s="63" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="R11" s="4"/>
       <x:c r="S11" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="T11" s="5" t="n">
         <x:v>46240</x:v>
@@ -8413,13 +8413,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="C12" s="4" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="C12" s="4" t="s">
+      <x:c r="D12" s="4" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="D12" s="4" t="s">
-        <x:v>141</x:v>
       </x:c>
       <x:c r="E12" s="5"/>
       <x:c r="F12" s="5"/>
@@ -8432,13 +8432,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J12" s="4" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="K12" s="4" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="K12" s="4" t="s">
+      <x:c r="L12" s="4" t="s">
         <x:v>143</x:v>
-      </x:c>
-      <x:c r="L12" s="4" t="s">
-        <x:v>144</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
         <x:f t="shared" si="4">IF(C12="","",IF(N12&lt;&gt;"",N12,IF(O12&lt;&gt;"",O12,IF(P12&lt;&gt;"",P12,IF(Q12&lt;&gt;"",Q12,IF(R12&lt;&gt;"",R12,""))))))</x:f>
@@ -8446,7 +8446,7 @@
       </x:c>
       <x:c r="N12" s="4"/>
       <x:c r="O12" s="63" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="P12" s="4"/>
       <x:c r="Q12" s="63" t="str">
@@ -8470,13 +8470,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="s">
         <x:v>146</x:v>
-      </x:c>
-      <x:c r="D13" s="4" t="s">
-        <x:v>147</x:v>
       </x:c>
       <x:c r="E13" s="5"/>
       <x:c r="F13" s="5"/>
@@ -8489,7 +8489,7 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J13" s="4" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="K13" s="4"/>
       <x:c r="L13" s="4"/>
@@ -8499,16 +8499,16 @@
       </x:c>
       <x:c r="N13" s="4"/>
       <x:c r="O13" s="63" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="P13" s="63" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="P13" s="63" t="s">
-        <x:v>150</x:v>
       </x:c>
       <x:c r="Q13" s="63" t="str">
         <x:v>https://www.facebook.com/usebarq/videos/%D8%AD%D9%84%D8%A7%D8%AA-%D8%A7%D9%84%D8%B3%D9%81%D8%B1-%D8%A8%D8%A7%D9%84%D8%AA%D8%AC%D8%A7%D8%B1%D8%A8-%D9%88%D8%A8%D8%A8%D8%B7%D8%A7%D9%82%D8%A9-%D8%A8%D8%AF%D9%88%D9%86-%D8%B1%D8%B3%D9%88%D9%85-%D8%AF%D9%88%D9%84%D9%8A%D8%A9%EF%B8%8F/1051539764436915/</x:v>
       </x:c>
       <x:c r="R13" s="63" t="s">
-        <x:v>151</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="S13" s="4" t="str">
         <x:v>Current official posts continue to position barq Visa as having no international transaction fees. No campaign end date is stated.</x:v>
@@ -8527,10 +8527,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B14" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C14" s="4" t="s">
-        <x:v>152</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D14" s="4"/>
       <x:c r="E14" s="5"/>
@@ -8544,13 +8544,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J14" s="4" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="K14" s="4" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="K14" s="4" t="s">
+      <x:c r="L14" s="4" t="s">
         <x:v>154</x:v>
-      </x:c>
-      <x:c r="L14" s="4" t="s">
-        <x:v>155</x:v>
       </x:c>
       <x:c r="M14" s="9" t="str">
         <x:f t="shared" si="4">IF(C14="","",IF(N14&lt;&gt;"",N14,IF(O14&lt;&gt;"",O14,IF(P14&lt;&gt;"",P14,IF(Q14&lt;&gt;"",Q14,IF(R14&lt;&gt;"",R14,""))))))</x:f>
@@ -8558,7 +8558,7 @@
       </x:c>
       <x:c r="N14" s="4"/>
       <x:c r="O14" s="63" t="s">
-        <x:v>156</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="P14" s="4"/>
       <x:c r="Q14" s="4"/>
@@ -9561,7 +9561,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdddcf73619242a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ece700b5b7643cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9587,11 +9587,12 @@
     <x:col min="19" max="19" width="50" customWidth="1"/>
     <x:col min="20" max="20" width="13" customWidth="1"/>
     <x:col min="21" max="21" width="30" customWidth="1"/>
+    <x:col min="5" max="5" width="0.10999999940395355" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22.649999618530273" customHeight="1">
       <x:c r="A1" s="52" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B1" s="52"/>
       <x:c r="C1" s="52"/>
@@ -9736,50 +9737,50 @@
       <x:c r="D8" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E8" s="3" t="s">
+      <x:c r="E8" s="3" t="str">
+        <x:v> </x:v>
+      </x:c>
+      <x:c r="F8" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="s">
+      <x:c r="G8" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="s">
+      <x:c r="H8" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="s">
+      <x:c r="I8" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="s">
+      <x:c r="J8" s="3" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J8" s="3" t="s">
+      <x:c r="K8" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K8" s="3" t="s">
+      <x:c r="L8" s="3" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L8" s="3" t="s">
+      <x:c r="M8" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="M8" s="3" t="s">
+      <x:c r="N8" s="3" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="N8" s="3" t="s">
+      <x:c r="O8" s="3" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="O8" s="3" t="s">
+      <x:c r="P8" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="P8" s="3" t="s">
+      <x:c r="Q8" s="3" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="Q8" s="3" t="s">
+      <x:c r="R8" s="3" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="R8" s="3" t="s">
+      <x:c r="S8" s="3" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="S8" s="3" t="s">
-        <x:v>20</x:v>
       </x:c>
       <x:c r="T8" s="3" t="str">
         <x:v>Social Post Count</x:v>
@@ -9794,7 +9795,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>International Transfer Prize Draw – SAR 110,000</x:v>
@@ -9834,13 +9835,13 @@
         <x:v>https://mobilypay.sa/ar/offers/offer-51.html</x:v>
       </x:c>
       <x:c r="O9" s="63" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="P9" s="63" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="P9" s="63" t="s">
+      <x:c r="Q9" s="63" t="s">
         <x:v>159</x:v>
-      </x:c>
-      <x:c r="Q9" s="63" t="s">
-        <x:v>160</x:v>
       </x:c>
       <x:c r="R9" s="4"/>
       <x:c r="S9" s="4" t="str">
@@ -9860,7 +9861,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C10" s="4" t="str">
         <x:v>Zero-Fee International Transfers – Aug–Oct 2026</x:v>
@@ -9900,11 +9901,11 @@
         <x:v>https://mobilypay.sa/ar/offers/offer-56.html</x:v>
       </x:c>
       <x:c r="O10" s="63" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="P10" s="4"/>
       <x:c r="Q10" s="63" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="R10" s="4"/>
       <x:c r="S10" s="4" t="str">
@@ -9924,13 +9925,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="s">
         <x:v>163</x:v>
-      </x:c>
-      <x:c r="D11" s="4" t="s">
-        <x:v>164</x:v>
       </x:c>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5"/>
@@ -9943,13 +9944,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
-        <x:v>142</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="K11" s="4" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="L11" s="4" t="s">
         <x:v>165</x:v>
-      </x:c>
-      <x:c r="L11" s="4" t="s">
-        <x:v>166</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:f t="shared" si="3">IF(C11="","",IF(N11&lt;&gt;"",N11,IF(O11&lt;&gt;"",O11,IF(P11&lt;&gt;"",P11,IF(Q11&lt;&gt;"",Q11,IF(R11&lt;&gt;"",R11,""))))))</x:f>
@@ -9959,11 +9960,11 @@
       <x:c r="O11" s="4"/>
       <x:c r="P11" s="4"/>
       <x:c r="Q11" s="63" t="s">
-        <x:v>167</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="R11" s="4"/>
       <x:c r="S11" s="4" t="s">
-        <x:v>168</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="T11" s="5" t="n">
         <x:v>46240</x:v>
@@ -9979,13 +9980,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D12" s="4" t="s">
         <x:v>169</x:v>
-      </x:c>
-      <x:c r="D12" s="4" t="s">
-        <x:v>170</x:v>
       </x:c>
       <x:c r="E12" s="5"/>
       <x:c r="F12" s="5">
@@ -10003,27 +10004,27 @@
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J12" s="4" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="K12" s="4" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="K12" s="4" t="s">
+      <x:c r="L12" s="4" t="s">
         <x:v>172</x:v>
-      </x:c>
-      <x:c r="L12" s="4" t="s">
-        <x:v>173</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
         <x:f t="shared" si="3">IF(C12="","",IF(N12&lt;&gt;"",N12,IF(O12&lt;&gt;"",O12,IF(P12&lt;&gt;"",P12,IF(Q12&lt;&gt;"",Q12,IF(R12&lt;&gt;"",R12,""))))))</x:f>
         <x:v>https://mobilypay.sa/offer-details.html?id=offer-6</x:v>
       </x:c>
       <x:c r="N12" s="4" t="s">
-        <x:v>174</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="O12" s="4"/>
       <x:c r="P12" s="4"/>
       <x:c r="Q12" s="4"/>
       <x:c r="R12" s="4"/>
       <x:c r="S12" s="4" t="s">
-        <x:v>175</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="T12" s="5" t="n">
         <x:v>46240</x:v>
@@ -10039,13 +10040,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="s">
         <x:v>176</x:v>
-      </x:c>
-      <x:c r="D13" s="4" t="s">
-        <x:v>177</x:v>
       </x:c>
       <x:c r="E13" s="5"/>
       <x:c r="F13" s="5">
@@ -10063,10 +10064,10 @@
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J13" s="4" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="K13" s="1" t="s">
         <x:v>178</x:v>
-      </x:c>
-      <x:c r="K13" s="1" t="s">
-        <x:v>179</x:v>
       </x:c>
       <x:c r="L13" s="4"/>
       <x:c r="M13" s="9" t="str">
@@ -10074,17 +10075,17 @@
         <x:v>https://mobilypay.sa/offer-details.html?id=offer-53</x:v>
       </x:c>
       <x:c r="N13" s="63" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="O13" s="4"/>
       <x:c r="P13" s="63" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="Q13" s="63" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="Q13" s="63" t="s">
+      <x:c r="R13" s="63" t="s">
         <x:v>182</x:v>
-      </x:c>
-      <x:c r="R13" s="63" t="s">
-        <x:v>183</x:v>
       </x:c>
       <x:c r="S13" s="4" t="str">
         <x:v>Campaign is valid from 19 July to 19 August 2026. It includes 0% international transaction fees for eligible newly issued Platinum and Signature Visa cards, free plastic-card issuance, and eligible POS/e-commerce purchases.</x:v>
@@ -10103,13 +10104,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B14" s="4" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="C14" s="4" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="C14" s="4" t="s">
+      <x:c r="D14" s="4" t="s">
         <x:v>185</x:v>
-      </x:c>
-      <x:c r="D14" s="4" t="s">
-        <x:v>186</x:v>
       </x:c>
       <x:c r="E14" s="5"/>
       <x:c r="F14" s="5">
@@ -10127,29 +10128,29 @@
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J14" s="4" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="K14" s="4" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="K14" s="4" t="s">
+      <x:c r="L14" s="4" t="s">
         <x:v>188</x:v>
-      </x:c>
-      <x:c r="L14" s="4" t="s">
-        <x:v>189</x:v>
       </x:c>
       <x:c r="M14" s="9" t="str">
         <x:f t="shared" si="3">IF(C14="","",IF(N14&lt;&gt;"",N14,IF(O14&lt;&gt;"",O14,IF(P14&lt;&gt;"",P14,IF(Q14&lt;&gt;"",Q14,IF(R14&lt;&gt;"",R14,""))))))</x:f>
         <x:v>https://mobilypay.sa/offer-details.html?id=offer-54</x:v>
       </x:c>
       <x:c r="N14" s="63" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="O14" s="63" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="O14" s="63" t="s">
+      <x:c r="P14" s="63" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="P14" s="63" t="s">
+      <x:c r="Q14" s="63" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="Q14" s="63" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="R14" s="4"/>
       <x:c r="S14" s="4" t="str">
@@ -11169,7 +11170,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31321246c6b94b69"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fe976c1cd51462f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11195,11 +11196,12 @@
     <x:col min="19" max="19" width="50" customWidth="1"/>
     <x:col min="20" max="20" width="13" customWidth="1"/>
     <x:col min="21" max="21" width="30" customWidth="1"/>
+    <x:col min="5" max="5" width="0.10999999940395355" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22.649999618530273" customHeight="1">
       <x:c r="A1" s="52" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B1" s="52"/>
       <x:c r="C1" s="52"/>
@@ -11344,50 +11346,50 @@
       <x:c r="D8" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E8" s="3" t="s">
+      <x:c r="E8" s="3" t="str">
+        <x:v> </x:v>
+      </x:c>
+      <x:c r="F8" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="s">
+      <x:c r="G8" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="s">
+      <x:c r="H8" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="s">
+      <x:c r="I8" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="s">
+      <x:c r="J8" s="3" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J8" s="3" t="s">
+      <x:c r="K8" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K8" s="3" t="s">
+      <x:c r="L8" s="3" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L8" s="3" t="s">
+      <x:c r="M8" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="M8" s="3" t="s">
+      <x:c r="N8" s="3" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="N8" s="3" t="s">
+      <x:c r="O8" s="3" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="O8" s="3" t="s">
+      <x:c r="P8" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="P8" s="3" t="s">
+      <x:c r="Q8" s="3" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="Q8" s="3" t="s">
+      <x:c r="R8" s="3" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="R8" s="3" t="s">
+      <x:c r="S8" s="3" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="S8" s="3" t="s">
-        <x:v>20</x:v>
       </x:c>
       <x:c r="T8" s="3" t="str">
         <x:v>Social Post Count</x:v>
@@ -11402,17 +11404,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="C9" s="4" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="C9" s="4" t="s">
+      <x:c r="D9" s="4" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="D9" s="4" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="E9" s="5">
-        <x:v>46227</x:v>
-      </x:c>
+      <x:c r="E9" s="5"/>
       <x:c r="F9" s="5"/>
       <x:c r="G9" s="5"/>
       <x:c r="H9" s="7" t="str">
@@ -11423,13 +11423,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J9" s="4" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="K9" s="4" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="K9" s="4" t="s">
+      <x:c r="L9" s="4" t="s">
         <x:v>199</x:v>
-      </x:c>
-      <x:c r="L9" s="4" t="s">
-        <x:v>200</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:f t="shared" ref="M9:M42" si="3">IF(C9="","",IF(N9&lt;&gt;"",N9,IF(O9&lt;&gt;"",O9,IF(P9&lt;&gt;"",P9,IF(Q9&lt;&gt;"",Q9,IF(R9&lt;&gt;"",R9,""))))))</x:f>
@@ -11437,17 +11437,17 @@
       </x:c>
       <x:c r="N9" s="4"/>
       <x:c r="O9" s="4" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="P9" s="63" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="P9" s="63" t="s">
+      <x:c r="Q9" s="63" t="s">
         <x:v>202</x:v>
-      </x:c>
-      <x:c r="Q9" s="63" t="s">
-        <x:v>203</x:v>
       </x:c>
       <x:c r="R9" s="4"/>
       <x:c r="S9" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="T9" s="5" t="n">
         <x:v>46240</x:v>
@@ -11463,17 +11463,15 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="D10" s="4" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="D10" s="4" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="E10" s="5">
-        <x:v>46226</x:v>
-      </x:c>
+      <x:c r="E10" s="5"/>
       <x:c r="F10" s="5">
         <x:v>46204</x:v>
       </x:c>
@@ -11489,13 +11487,13 @@
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J10" s="4" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="K10" s="4" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="K10" s="4" t="s">
+      <x:c r="L10" s="4" t="s">
         <x:v>207</x:v>
-      </x:c>
-      <x:c r="L10" s="4" t="s">
-        <x:v>208</x:v>
       </x:c>
       <x:c r="M10" s="9" t="str">
         <x:f t="shared" si="3">IF(C10="","",IF(N10&lt;&gt;"",N10,IF(O10&lt;&gt;"",O10,IF(P10&lt;&gt;"",P10,IF(Q10&lt;&gt;"",Q10,IF(R10&lt;&gt;"",R10,""))))))</x:f>
@@ -11503,7 +11501,7 @@
       </x:c>
       <x:c r="N10" s="4"/>
       <x:c r="O10" s="4" t="s">
-        <x:v>209</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="P10" s="4"/>
       <x:c r="Q10" s="4"/>
@@ -11525,13 +11523,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="s">
         <x:v>210</x:v>
-      </x:c>
-      <x:c r="D11" s="4" t="s">
-        <x:v>211</x:v>
       </x:c>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5"/>
@@ -11547,13 +11545,13 @@
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
-        <x:v>142</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="K11" s="4" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="L11" s="4" t="s">
         <x:v>212</x:v>
-      </x:c>
-      <x:c r="L11" s="4" t="s">
-        <x:v>213</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:f t="shared" si="3">IF(C11="","",IF(N11&lt;&gt;"",N11,IF(O11&lt;&gt;"",O11,IF(P11&lt;&gt;"",P11,IF(Q11&lt;&gt;"",Q11,IF(R11&lt;&gt;"",R11,""))))))</x:f>
@@ -11561,13 +11559,13 @@
       </x:c>
       <x:c r="N11" s="4"/>
       <x:c r="O11" s="4" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="P11" s="63" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="P11" s="63" t="s">
+      <x:c r="Q11" s="4" t="s">
         <x:v>215</x:v>
-      </x:c>
-      <x:c r="Q11" s="4" t="s">
-        <x:v>216</x:v>
       </x:c>
       <x:c r="R11" s="4"/>
       <x:c r="S11" s="4" t="str">
@@ -11587,13 +11585,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D12" s="4" t="s">
         <x:v>217</x:v>
-      </x:c>
-      <x:c r="D12" s="4" t="s">
-        <x:v>218</x:v>
       </x:c>
       <x:c r="E12" s="5"/>
       <x:c r="F12" s="5"/>
@@ -11606,13 +11604,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J12" s="4" t="s">
-        <x:v>142</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="K12" s="4" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="L12" s="4" t="s">
         <x:v>219</x:v>
-      </x:c>
-      <x:c r="L12" s="4" t="s">
-        <x:v>220</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
         <x:f t="shared" si="3">IF(C12="","",IF(N12&lt;&gt;"",N12,IF(O12&lt;&gt;"",O12,IF(P12&lt;&gt;"",P12,IF(Q12&lt;&gt;"",Q12,IF(R12&lt;&gt;"",R12,""))))))</x:f>
@@ -11620,17 +11618,17 @@
       </x:c>
       <x:c r="N12" s="4"/>
       <x:c r="O12" s="4" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="P12" s="63" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="P12" s="63" t="s">
+      <x:c r="Q12" s="63" t="s">
         <x:v>222</x:v>
-      </x:c>
-      <x:c r="Q12" s="63" t="s">
-        <x:v>223</x:v>
       </x:c>
       <x:c r="R12" s="4"/>
       <x:c r="S12" s="4" t="s">
-        <x:v>224</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="T12" s="5" t="n">
         <x:v>46240</x:v>
@@ -11646,7 +11644,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
         <x:v>Zero International Card Transaction Fees</x:v>
@@ -11686,16 +11684,16 @@
         <x:v>https://www.tiqmo.com/ar/offers</x:v>
       </x:c>
       <x:c r="O13" s="63" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="P13" s="63" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="P13" s="63" t="s">
+      <x:c r="Q13" s="63" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="Q13" s="63" t="s">
+      <x:c r="R13" s="63" t="s">
         <x:v>227</x:v>
-      </x:c>
-      <x:c r="R13" s="63" t="s">
-        <x:v>228</x:v>
       </x:c>
       <x:c r="S13" s="4" t="str">
         <x:v>Offer is valid from 1 May to 31 December 2026. It applies outside Saudi Arabia and excludes international online stores, websites and mobile applications. tiqmo standard terms apply.</x:v>
@@ -12776,7 +12774,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08fbabd9ad8d42ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e9d564994ea49a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12802,11 +12800,12 @@
     <x:col min="19" max="19" width="50" customWidth="1"/>
     <x:col min="20" max="20" width="13" customWidth="1"/>
     <x:col min="21" max="21" width="30" customWidth="1"/>
+    <x:col min="5" max="5" width="0.10999999940395355" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22.649999618530273" customHeight="1">
       <x:c r="A1" s="52" t="s">
-        <x:v>229</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B1" s="52"/>
       <x:c r="C1" s="52"/>
@@ -12951,50 +12950,50 @@
       <x:c r="D8" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E8" s="3" t="s">
+      <x:c r="E8" s="3" t="str">
+        <x:v> </x:v>
+      </x:c>
+      <x:c r="F8" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="s">
+      <x:c r="G8" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="s">
+      <x:c r="H8" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="s">
+      <x:c r="I8" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="s">
+      <x:c r="J8" s="3" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J8" s="3" t="s">
+      <x:c r="K8" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K8" s="3" t="s">
+      <x:c r="L8" s="3" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L8" s="3" t="s">
+      <x:c r="M8" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="M8" s="3" t="s">
+      <x:c r="N8" s="3" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="N8" s="3" t="s">
+      <x:c r="O8" s="3" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="O8" s="3" t="s">
+      <x:c r="P8" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="P8" s="3" t="s">
+      <x:c r="Q8" s="3" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="Q8" s="3" t="s">
+      <x:c r="R8" s="3" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="R8" s="3" t="s">
+      <x:c r="S8" s="3" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="S8" s="3" t="s">
-        <x:v>20</x:v>
       </x:c>
       <x:c r="T8" s="3" t="str">
         <x:v>Social Post Count</x:v>
@@ -13009,13 +13008,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="s">
         <x:v>230</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="s">
-        <x:v>231</x:v>
       </x:c>
       <x:c r="E9" s="5"/>
       <x:c r="F9" s="5"/>
@@ -13028,31 +13027,31 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J9" s="4" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="K9" s="4" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="K9" s="4" t="s">
+      <x:c r="L9" s="4" t="s">
         <x:v>233</x:v>
-      </x:c>
-      <x:c r="L9" s="4" t="s">
-        <x:v>234</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:f t="shared" ref="M9:M46" si="3">IF(C9="","",IF(N9&lt;&gt;"",N9,IF(O9&lt;&gt;"",O9,IF(P9&lt;&gt;"",P9,IF(Q9&lt;&gt;"",Q9,IF(R9&lt;&gt;"",R9,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/cashback-system</x:v>
       </x:c>
       <x:c r="N9" s="63" t="s">
-        <x:v>235</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="O9" s="4"/>
       <x:c r="P9" s="63" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="Q9" s="4" t="s">
         <x:v>236</x:v>
-      </x:c>
-      <x:c r="Q9" s="4" t="s">
-        <x:v>237</x:v>
       </x:c>
       <x:c r="R9" s="4"/>
       <x:c r="S9" s="4" t="s">
-        <x:v>238</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="T9" s="5" t="n">
         <x:v>46240</x:v>
@@ -13068,13 +13067,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="D10" s="4" t="s">
         <x:v>239</x:v>
-      </x:c>
-      <x:c r="D10" s="4" t="s">
-        <x:v>240</x:v>
       </x:c>
       <x:c r="E10" s="5"/>
       <x:c r="F10" s="5"/>
@@ -13090,27 +13089,27 @@
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J10" s="4" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="K10" s="4" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="K10" s="4" t="s">
+      <x:c r="L10" s="4" t="s">
         <x:v>242</x:v>
-      </x:c>
-      <x:c r="L10" s="4" t="s">
-        <x:v>243</x:v>
       </x:c>
       <x:c r="M10" s="9" t="str">
         <x:f t="shared" si="3">IF(C10="","",IF(N10&lt;&gt;"",N10,IF(O10&lt;&gt;"",O10,IF(P10&lt;&gt;"",P10,IF(Q10&lt;&gt;"",Q10,IF(R10&lt;&gt;"",R10,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/urpay-offers/alhabibbedding</x:v>
       </x:c>
       <x:c r="N10" s="4" t="s">
-        <x:v>244</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="O10" s="4"/>
       <x:c r="P10" s="4"/>
       <x:c r="Q10" s="4"/>
       <x:c r="R10" s="4"/>
       <x:c r="S10" s="4" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="T10" s="5" t="n">
         <x:v>46240</x:v>
@@ -13126,13 +13125,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="s">
         <x:v>246</x:v>
-      </x:c>
-      <x:c r="D11" s="4" t="s">
-        <x:v>247</x:v>
       </x:c>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5"/>
@@ -13148,27 +13147,27 @@
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="K11" s="4" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="K11" s="4" t="s">
+      <x:c r="L11" s="4" t="s">
         <x:v>249</x:v>
-      </x:c>
-      <x:c r="L11" s="4" t="s">
-        <x:v>250</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:f t="shared" si="3">IF(C11="","",IF(N11&lt;&gt;"",N11,IF(O11&lt;&gt;"",O11,IF(P11&lt;&gt;"",P11,IF(Q11&lt;&gt;"",Q11,IF(R11&lt;&gt;"",R11,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/urpay-offers/squatwolf</x:v>
       </x:c>
       <x:c r="N11" s="4" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="O11" s="4"/>
       <x:c r="P11" s="4"/>
       <x:c r="Q11" s="4"/>
       <x:c r="R11" s="4"/>
       <x:c r="S11" s="4" t="s">
-        <x:v>252</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="T11" s="5" t="n">
         <x:v>46240</x:v>
@@ -13184,13 +13183,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D12" s="4" t="s">
         <x:v>253</x:v>
-      </x:c>
-      <x:c r="D12" s="4" t="s">
-        <x:v>254</x:v>
       </x:c>
       <x:c r="E12" s="5"/>
       <x:c r="F12" s="5"/>
@@ -13206,27 +13205,27 @@
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J12" s="4" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="K12" s="4" t="s">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="K12" s="4" t="s">
-        <x:v>256</x:v>
-      </x:c>
       <x:c r="L12" s="4" t="s">
-        <x:v>243</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
         <x:f t="shared" si="3">IF(C12="","",IF(N12&lt;&gt;"",N12,IF(O12&lt;&gt;"",O12,IF(P12&lt;&gt;"",P12,IF(Q12&lt;&gt;"",Q12,IF(R12&lt;&gt;"",R12,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/urpay-offers/mag</x:v>
       </x:c>
       <x:c r="N12" s="4" t="s">
-        <x:v>257</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="O12" s="4"/>
       <x:c r="P12" s="4"/>
       <x:c r="Q12" s="4"/>
       <x:c r="R12" s="4"/>
       <x:c r="S12" s="4" t="s">
-        <x:v>258</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="T12" s="5" t="n">
         <x:v>46240</x:v>
@@ -13242,13 +13241,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="s">
         <x:v>259</x:v>
-      </x:c>
-      <x:c r="D13" s="4" t="s">
-        <x:v>260</x:v>
       </x:c>
       <x:c r="E13" s="5"/>
       <x:c r="F13" s="5"/>
@@ -13264,27 +13263,27 @@
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J13" s="4" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="K13" s="4" t="s">
         <x:v>261</x:v>
       </x:c>
-      <x:c r="K13" s="4" t="s">
-        <x:v>262</x:v>
-      </x:c>
       <x:c r="L13" s="4" t="s">
-        <x:v>250</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="M13" s="9" t="str">
         <x:f t="shared" si="3">IF(C13="","",IF(N13&lt;&gt;"",N13,IF(O13&lt;&gt;"",O13,IF(P13&lt;&gt;"",P13,IF(Q13&lt;&gt;"",Q13,IF(R13&lt;&gt;"",R13,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/urpay-offers/b-bw</x:v>
       </x:c>
       <x:c r="N13" s="4" t="s">
-        <x:v>263</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="O13" s="4"/>
       <x:c r="P13" s="4"/>
       <x:c r="Q13" s="4"/>
       <x:c r="R13" s="4"/>
       <x:c r="S13" s="4" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="T13" s="5" t="n">
         <x:v>46240</x:v>
@@ -13300,13 +13299,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B14" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C14" s="4" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="D14" s="4" t="s">
         <x:v>265</x:v>
-      </x:c>
-      <x:c r="D14" s="4" t="s">
-        <x:v>266</x:v>
       </x:c>
       <x:c r="E14" s="5"/>
       <x:c r="F14" s="5"/>
@@ -13322,27 +13321,27 @@
         <x:v>Active</x:v>
       </x:c>
       <x:c r="J14" s="4" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="K14" s="4" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="K14" s="4" t="s">
-        <x:v>268</x:v>
-      </x:c>
       <x:c r="L14" s="4" t="s">
-        <x:v>243</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="M14" s="9" t="str">
         <x:f t="shared" si="3">IF(C14="","",IF(N14&lt;&gt;"",N14,IF(O14&lt;&gt;"",O14,IF(P14&lt;&gt;"",P14,IF(Q14&lt;&gt;"",Q14,IF(R14&lt;&gt;"",R14,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/urpay-offers/nadi-ph</x:v>
       </x:c>
       <x:c r="N14" s="4" t="s">
-        <x:v>269</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="O14" s="4"/>
       <x:c r="P14" s="4"/>
       <x:c r="Q14" s="4"/>
       <x:c r="R14" s="4"/>
       <x:c r="S14" s="4" t="s">
-        <x:v>270</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="T14" s="5" t="n">
         <x:v>46240</x:v>
@@ -13358,13 +13357,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B15" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C15" s="4" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="D15" s="4" t="s">
         <x:v>271</x:v>
-      </x:c>
-      <x:c r="D15" s="4" t="s">
-        <x:v>272</x:v>
       </x:c>
       <x:c r="E15" s="5"/>
       <x:c r="F15" s="5"/>
@@ -13380,27 +13379,27 @@
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J15" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="K15" s="4" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="L15" s="4" t="s">
         <x:v>273</x:v>
-      </x:c>
-      <x:c r="L15" s="4" t="s">
-        <x:v>274</x:v>
       </x:c>
       <x:c r="M15" s="9" t="str">
         <x:f t="shared" si="3">IF(C15="","",IF(N15&lt;&gt;"",N15,IF(O15&lt;&gt;"",O15,IF(P15&lt;&gt;"",P15,IF(Q15&lt;&gt;"",Q15,IF(R15&lt;&gt;"",R15,""))))))</x:f>
         <x:v>https://www.urpay.com.sa/en/urpay-offers/iherb</x:v>
       </x:c>
       <x:c r="N15" s="4" t="s">
-        <x:v>275</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="O15" s="4"/>
       <x:c r="P15" s="4"/>
       <x:c r="Q15" s="4"/>
       <x:c r="R15" s="4"/>
       <x:c r="S15" s="4" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="T15" s="5" t="n">
         <x:v>46240</x:v>
@@ -13416,13 +13415,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="4" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="C16" s="4" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="C16" s="4" t="s">
+      <x:c r="D16" s="4" t="s">
         <x:v>278</x:v>
-      </x:c>
-      <x:c r="D16" s="4" t="s">
-        <x:v>279</x:v>
       </x:c>
       <x:c r="E16" s="5"/>
       <x:c r="F16" s="5"/>
@@ -13435,13 +13434,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J16" s="4" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="K16" s="4" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="K16" s="4" t="s">
+      <x:c r="L16" s="4" t="s">
         <x:v>281</x:v>
-      </x:c>
-      <x:c r="L16" s="4" t="s">
-        <x:v>282</x:v>
       </x:c>
       <x:c r="M16" s="9" t="str">
         <x:f t="shared" si="3">IF(C16="","",IF(N16&lt;&gt;"",N16,IF(O16&lt;&gt;"",O16,IF(P16&lt;&gt;"",P16,IF(Q16&lt;&gt;"",Q16,IF(R16&lt;&gt;"",R16,""))))))</x:f>
@@ -13450,12 +13449,12 @@
       <x:c r="N16" s="4"/>
       <x:c r="O16" s="4"/>
       <x:c r="P16" s="4" t="s">
-        <x:v>283</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="Q16" s="4"/>
       <x:c r="R16" s="4"/>
       <x:c r="S16" s="4" t="s">
-        <x:v>284</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="T16" s="5" t="n">
         <x:v>46240</x:v>
@@ -14559,7 +14558,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e0a4e84398a4ea6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e3eef9596a941a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14585,11 +14584,12 @@
     <x:col min="19" max="19" width="50" customWidth="1"/>
     <x:col min="20" max="20" width="13" customWidth="1"/>
     <x:col min="21" max="21" width="30" customWidth="1"/>
+    <x:col min="5" max="5" width="0.10999999940395355" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22.649999618530273" customHeight="1">
       <x:c r="A1" s="52" t="s">
-        <x:v>285</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B1" s="52"/>
       <x:c r="C1" s="52"/>
@@ -14734,50 +14734,50 @@
       <x:c r="D8" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E8" s="3" t="s">
+      <x:c r="E8" s="3" t="str">
+        <x:v> </x:v>
+      </x:c>
+      <x:c r="F8" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="s">
+      <x:c r="G8" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="s">
+      <x:c r="H8" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="s">
+      <x:c r="I8" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="s">
+      <x:c r="J8" s="3" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J8" s="3" t="s">
+      <x:c r="K8" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K8" s="3" t="s">
+      <x:c r="L8" s="3" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L8" s="3" t="s">
+      <x:c r="M8" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="M8" s="3" t="s">
+      <x:c r="N8" s="3" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="N8" s="3" t="s">
+      <x:c r="O8" s="3" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="O8" s="3" t="s">
+      <x:c r="P8" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="P8" s="3" t="s">
+      <x:c r="Q8" s="3" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="Q8" s="3" t="s">
+      <x:c r="R8" s="3" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="R8" s="3" t="s">
+      <x:c r="S8" s="3" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="S8" s="3" t="s">
-        <x:v>20</x:v>
       </x:c>
       <x:c r="T8" s="3" t="str">
         <x:v>Social Post Count</x:v>
@@ -14792,13 +14792,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="s">
         <x:v>286</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="s">
-        <x:v>287</x:v>
       </x:c>
       <x:c r="E9" s="5"/>
       <x:c r="F9" s="5">
@@ -14816,13 +14816,13 @@
         <x:v>Expired</x:v>
       </x:c>
       <x:c r="J9" s="4" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="K9" s="4" t="s">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="K9" s="4" t="s">
+      <x:c r="L9" s="4" t="s">
         <x:v>289</x:v>
-      </x:c>
-      <x:c r="L9" s="4" t="s">
-        <x:v>290</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:f t="shared" ref="M9:M42" si="3">IF(C9="","",IF(N9&lt;&gt;"",N9,IF(O9&lt;&gt;"",O9,IF(P9&lt;&gt;"",P9,IF(Q9&lt;&gt;"",Q9,IF(R9&lt;&gt;"",R9,""))))))</x:f>
@@ -14830,17 +14830,17 @@
       </x:c>
       <x:c r="N9" s="4"/>
       <x:c r="O9" s="63" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="P9" s="4" t="s">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="P9" s="4" t="s">
+      <x:c r="Q9" s="63" t="s">
         <x:v>292</x:v>
-      </x:c>
-      <x:c r="Q9" s="63" t="s">
-        <x:v>293</x:v>
       </x:c>
       <x:c r="R9" s="4"/>
       <x:c r="S9" s="4" t="s">
-        <x:v>294</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="T9" s="5" t="n">
         <x:v>46240</x:v>
@@ -14856,10 +14856,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>295</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="D10" s="4" t="str">
         <x:v>Use alinma pay Cashback Cards internationally with no foreign transaction fees, no fees on the first two international cash withdrawals, and cashback on eligible purchases.</x:v>
@@ -14881,7 +14881,7 @@
         <x:v>Zero international transaction fees, first two international cash withdrawals free, plus cashback on eligible purchases</x:v>
       </x:c>
       <x:c r="L10" s="4" t="s">
-        <x:v>296</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="M10" s="9" t="str">
         <x:f t="shared" si="3">IF(C10="","",IF(N10&lt;&gt;"",N10,IF(O10&lt;&gt;"",O10,IF(P10&lt;&gt;"",P10,IF(Q10&lt;&gt;"",Q10,IF(R10&lt;&gt;"",R10,""))))))</x:f>
@@ -14891,7 +14891,7 @@
       <x:c r="O10" s="4"/>
       <x:c r="P10" s="4"/>
       <x:c r="Q10" s="63" t="s">
-        <x:v>297</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="R10" s="4"/>
       <x:c r="S10" s="4" t="str">
@@ -14911,13 +14911,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="s">
         <x:v>298</x:v>
-      </x:c>
-      <x:c r="D11" s="4" t="s">
-        <x:v>299</x:v>
       </x:c>
       <x:c r="E11" s="5"/>
       <x:c r="F11" s="5"/>
@@ -14930,13 +14930,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="K11" s="4" t="s">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="K11" s="4" t="s">
+      <x:c r="L11" s="4" t="s">
         <x:v>301</x:v>
-      </x:c>
-      <x:c r="L11" s="4" t="s">
-        <x:v>302</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:f t="shared" si="3">IF(C11="","",IF(N11&lt;&gt;"",N11,IF(O11&lt;&gt;"",O11,IF(P11&lt;&gt;"",P11,IF(Q11&lt;&gt;"",Q11,IF(R11&lt;&gt;"",R11,""))))))</x:f>
@@ -14944,17 +14944,17 @@
       </x:c>
       <x:c r="N11" s="4"/>
       <x:c r="O11" s="63" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="P11" s="4" t="s">
         <x:v>303</x:v>
       </x:c>
-      <x:c r="P11" s="4" t="s">
+      <x:c r="Q11" s="63" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="Q11" s="63" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="R11" s="4"/>
       <x:c r="S11" s="4" t="s">
-        <x:v>306</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="T11" s="5" t="n">
         <x:v>46240</x:v>
@@ -14970,17 +14970,15 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="D12" s="4" t="s">
         <x:v>307</x:v>
       </x:c>
-      <x:c r="D12" s="4" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="E12" s="5">
-        <x:v>46068</x:v>
-      </x:c>
+      <x:c r="E12" s="5"/>
       <x:c r="F12" s="5"/>
       <x:c r="G12" s="5"/>
       <x:c r="H12" s="7" t="str">
@@ -14991,13 +14989,13 @@
         <x:v>End Date Not Stated</x:v>
       </x:c>
       <x:c r="J12" s="4" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="K12" s="4" t="s">
         <x:v>309</x:v>
       </x:c>
-      <x:c r="K12" s="4" t="s">
+      <x:c r="L12" s="4" t="s">
         <x:v>310</x:v>
-      </x:c>
-      <x:c r="L12" s="4" t="s">
-        <x:v>311</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
         <x:f t="shared" si="3">IF(C12="","",IF(N12&lt;&gt;"",N12,IF(O12&lt;&gt;"",O12,IF(P12&lt;&gt;"",P12,IF(Q12&lt;&gt;"",Q12,IF(R12&lt;&gt;"",R12,""))))))</x:f>
@@ -15007,11 +15005,11 @@
       <x:c r="O12" s="4"/>
       <x:c r="P12" s="4"/>
       <x:c r="Q12" s="63" t="s">
-        <x:v>312</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="R12" s="4"/>
       <x:c r="S12" s="4" t="s">
-        <x:v>168</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="T12" s="5" t="n">
         <x:v>46240</x:v>
@@ -15035,9 +15033,7 @@
       <x:c r="D13" s="4" t="str">
         <x:v>Transfer a domestic worker's salary through Musaned in alinma pay for a chance to win 100% cashback.</x:v>
       </x:c>
-      <x:c r="E13" s="5" t="n">
-        <x:v>46239</x:v>
-      </x:c>
+      <x:c r="E13" s="5"/>
       <x:c r="F13" s="5"/>
       <x:c r="G13" s="5"/>
       <x:c r="H13" s="7" t="str">
@@ -16119,7 +16115,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b9c17226a4e4a7d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a5aaf585c294709"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16140,7 +16136,7 @@
   <x:sheetData>
     <x:row r="1" ht="21.5">
       <x:c r="A1" s="58" t="s">
-        <x:v>313</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B1" s="58"/>
       <x:c r="C1" s="58"/>
@@ -16164,119 +16160,119 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="26" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B4" s="26" t="s">
         <x:v>314</x:v>
       </x:c>
-      <x:c r="B4" s="26" t="s">
+      <x:c r="C4" s="26" t="s">
         <x:v>315</x:v>
       </x:c>
-      <x:c r="C4" s="26" t="s">
+      <x:c r="D4" s="26" t="s">
         <x:v>316</x:v>
-      </x:c>
-      <x:c r="D4" s="26" t="s">
-        <x:v>317</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="38.650001525878906" customHeight="1">
       <x:c r="A5" s="27" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B5" s="27" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="C5" s="27" t="s">
         <x:v>318</x:v>
       </x:c>
-      <x:c r="C5" s="27" t="s">
+      <x:c r="D5" s="27" t="s">
         <x:v>319</x:v>
-      </x:c>
-      <x:c r="D5" s="27" t="s">
-        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="38.650001525878906" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>277</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>318</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="D6" s="4" t="s">
         <x:v>321</x:v>
-      </x:c>
-      <x:c r="D6" s="4" t="s">
-        <x:v>322</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="38.650001525878906" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>195</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>318</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="D7" s="4" t="s">
         <x:v>323</x:v>
-      </x:c>
-      <x:c r="D7" s="4" t="s">
-        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="38.650001525878906" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>318</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C8" s="4" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="D8" s="4" t="s">
         <x:v>325</x:v>
-      </x:c>
-      <x:c r="D8" s="4" t="s">
-        <x:v>326</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="38.650001525878906" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>318</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="s">
         <x:v>327</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="s">
-        <x:v>328</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="38.650001525878906" customHeight="1">
       <x:c r="A10" s="28" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B10" s="28" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="C10" s="28" t="s">
         <x:v>329</x:v>
       </x:c>
-      <x:c r="C10" s="28" t="s">
+      <x:c r="D10" s="28" t="s">
         <x:v>330</x:v>
-      </x:c>
-      <x:c r="D10" s="28" t="s">
-        <x:v>331</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="38.650001525878906" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>184</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="C11" s="4" t="s">
         <x:v>332</x:v>
       </x:c>
-      <x:c r="C11" s="4" t="s">
+      <x:c r="D11" s="4" t="s">
         <x:v>333</x:v>
-      </x:c>
-      <x:c r="D11" s="4" t="s">
-        <x:v>334</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="16.5">
       <x:c r="A14" s="46" t="s">
-        <x:v>335</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B14" s="46"/>
       <x:c r="C14" s="46"/>
@@ -16350,7 +16346,7 @@
     <x:row r="21" ht="36.650001525878906" customHeight="1"/>
     <x:row r="22" ht="36.650001525878906" customHeight="1">
       <x:c r="A22" s="45" t="s">
-        <x:v>336</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B22" s="45"/>
       <x:c r="C22" s="45"/>
@@ -16363,99 +16359,99 @@
     <x:row r="23" ht="32" customHeight="1"/>
     <x:row r="24" ht="32" customHeight="1">
       <x:c r="A24" s="21" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B24" s="21" t="s">
         <x:v>337</x:v>
       </x:c>
-      <x:c r="B24" s="21" t="s">
+      <x:c r="D24" s="29" t="s">
         <x:v>338</x:v>
       </x:c>
-      <x:c r="D24" s="29" t="s">
+      <x:c r="E24" s="29" t="s">
         <x:v>339</x:v>
       </x:c>
-      <x:c r="E24" s="29" t="s">
+      <x:c r="F24" s="29" t="s">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="F24" s="29" t="s">
+      <x:c r="G24" s="29" t="s">
         <x:v>341</x:v>
       </x:c>
-      <x:c r="G24" s="29" t="s">
+      <x:c r="H24" s="29" t="s">
         <x:v>342</x:v>
-      </x:c>
-      <x:c r="H24" s="29" t="s">
-        <x:v>343</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="46.650001525878906" customHeight="1">
       <x:c r="A25" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B25" s="1" t="str">
         <x:v>Campaign rows are populated automatically from approved monitoring data.</x:v>
       </x:c>
       <x:c r="D25" s="4" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="E25" s="4" t="s">
         <x:v>345</x:v>
       </x:c>
-      <x:c r="E25" s="4" t="s">
+      <x:c r="F25" s="4" t="s">
         <x:v>346</x:v>
       </x:c>
-      <x:c r="F25" s="4" t="s">
+      <x:c r="G25" s="4" t="s">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="G25" s="4" t="s">
+      <x:c r="H25" s="4" t="s">
         <x:v>348</x:v>
-      </x:c>
-      <x:c r="H25" s="4" t="s">
-        <x:v>349</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="46.650001525878906" customHeight="1">
       <x:c r="A26" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B26" s="1" t="str">
         <x:v>Merchant offers are shown only as an active approved count in each competitor sheet.</x:v>
       </x:c>
       <x:c r="D26" s="4" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="E26" s="4" t="s">
         <x:v>351</x:v>
       </x:c>
-      <x:c r="E26" s="4" t="s">
+      <x:c r="F26" s="4" t="s">
         <x:v>352</x:v>
       </x:c>
-      <x:c r="F26" s="4" t="s">
+      <x:c r="G26" s="4" t="s">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="G26" s="4" t="s">
+      <x:c r="H26" s="4" t="s">
         <x:v>354</x:v>
-      </x:c>
-      <x:c r="H26" s="4" t="s">
-        <x:v>355</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="46.650001525878906" customHeight="1">
       <x:c r="A27" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B27" s="1" t="str">
         <x:v>Use Remittance for all international-transfer campaigns; these rows are highlighted automatically.</x:v>
       </x:c>
       <x:c r="D27" s="4" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="E27" s="4" t="s">
         <x:v>357</x:v>
       </x:c>
-      <x:c r="E27" s="4" t="s">
+      <x:c r="F27" s="4" t="s">
         <x:v>358</x:v>
       </x:c>
-      <x:c r="F27" s="4" t="s">
+      <x:c r="G27" s="4" t="s">
         <x:v>359</x:v>
       </x:c>
-      <x:c r="G27" s="4" t="s">
+      <x:c r="H27" s="4" t="s">
         <x:v>360</x:v>
-      </x:c>
-      <x:c r="H27" s="4" t="s">
-        <x:v>361</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="30.649999618530273" customHeight="1">
       <x:c r="A28" s="1" t="s">
-        <x:v>362</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B28" s="1" t="str">
         <x:v>Each listed campaign must retain a direct official campaign page or confirmed official social source.</x:v>
@@ -16463,7 +16459,7 @@
     </x:row>
     <x:row r="29" ht="30.649999618530273" customHeight="1">
       <x:c r="A29" s="1" t="s">
-        <x:v>363</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B29" s="1" t="str">
         <x:v>Expired campaigns are excluded; leave End Date blank only when the official source does not state it.</x:v>
@@ -16471,7 +16467,7 @@
     </x:row>
     <x:row r="30" ht="30.649999618530273" customHeight="1">
       <x:c r="A30" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B30" s="1" t="str">
         <x:v>Campaigns are sorted newest first using Start Date, Published Date, and detection date.</x:v>
@@ -16479,7 +16475,7 @@
     </x:row>
     <x:row r="31" ht="30.649999618530273" customHeight="1">
       <x:c r="A31" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B31" s="1" t="str">
         <x:v>Dashboard campaign KPIs, category mix, remittance analysis, and the 14-day social Bar Chart update automatically.</x:v>
@@ -16487,7 +16483,7 @@
     </x:row>
     <x:row r="32" ht="30.649999618530273" customHeight="1">
       <x:c r="A32" s="1" t="s">
-        <x:v>366</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B32" s="1" t="str">
         <x:v>Social Post Count includes confirmed posts linked to the campaign; Published Platforms lists the relevant channels.</x:v>
